--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -5438,13 +5438,13 @@
         <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J20" t="n">
         <v>5.9</v>
       </c>
       <c r="K20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q20" t="n">
         <v>1.48</v>
@@ -5486,13 +5486,13 @@
         <v>36</v>
       </c>
       <c r="Y20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z20" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA20" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AB20" t="n">
         <v>14</v>
@@ -5501,10 +5501,10 @@
         <v>18</v>
       </c>
       <c r="AD20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AE20" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF20" t="n">
         <v>12</v>
@@ -5516,7 +5516,7 @@
         <v>32</v>
       </c>
       <c r="AI20" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ20" t="n">
         <v>13.5</v>
@@ -5528,25 +5528,25 @@
         <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN20" t="n">
         <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ20" t="n">
         <v>4.1</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
@@ -5555,10 +5555,10 @@
         <v>12.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX20" t="n">
         <v>8.6</v>
@@ -5567,10 +5567,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB20" t="n">
         <v>9.800000000000001</v>
@@ -5579,16 +5579,16 @@
         <v>11.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF20" t="n">
         <v>3.35</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -1114,19 +1114,19 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
         <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
         <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
         <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
         <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
         <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -3146,19 +3146,19 @@
         <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
         <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
         <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
         <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
         <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -3908,19 +3908,19 @@
         <v>1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
         <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>1.01</v>
       </c>
       <c r="G15" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
         <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
         <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -4422,13 +4422,13 @@
         <v>1.01</v>
       </c>
       <c r="I16" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
         <v>1.02</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
         <v>2.82</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q17" t="n">
         <v>1.98</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -4924,19 +4924,19 @@
         <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
         <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
         <v>1.03</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G19" t="n">
         <v>3.15</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -5438,13 +5438,13 @@
         <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
         <v>5.9</v>
       </c>
       <c r="K20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,7 +5459,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="Q20" t="n">
         <v>1.48</v>
@@ -5486,25 +5486,25 @@
         <v>36</v>
       </c>
       <c r="Y20" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA20" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AB20" t="n">
         <v>14</v>
       </c>
       <c r="AC20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="AE20" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AF20" t="n">
         <v>12</v>
@@ -5513,10 +5513,10 @@
         <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI20" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
         <v>13.5</v>
@@ -5525,52 +5525,52 @@
         <v>16.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM20" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AO20" t="n">
         <v>180</v>
       </c>
       <c r="AP20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.1</v>
+        <v>26</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB20" t="n">
         <v>9.800000000000001</v>
@@ -5579,16 +5579,16 @@
         <v>11.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.1</v>
+        <v>27</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF20" t="n">
         <v>3.35</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -5686,19 +5686,19 @@
         <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="n">
         <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
         <v>1.01</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>06:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,17 +1351,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:15:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Jonkopings Sodra</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:15:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1631,225 +1631,225 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,244 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
         <v>1.04</v>
       </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
         <v>1.04</v>
       </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0</v>
-      </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IFK Stocksund</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>IFK Stocksund</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,17 +3637,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3663,225 +3663,225 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,27 +3891,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Central Cordoba</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportivo Espanol</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,27 +4145,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Leandro N Alem</t>
+          <t>IF Karlstad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Victoriano Arenas</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,33 +4399,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CA Deportivo Paraguayo</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Justo Jose de Urquiza</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4440,19 +4440,19 @@
         <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="P16" t="n">
         <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="R16" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.56</v>
+        <v>1.19</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4461,10 +4461,10 @@
         <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.44</v>
+        <v>3.55</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.74</v>
+        <v>1.95</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,33 +4907,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Club Indep Petrolero</t>
+          <t>Central Cordoba</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Deportivo Espanol</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,36 +5161,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Everton De Vina</t>
+          <t>Leandro N Alem</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Victoriano Arenas</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="I19" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,498 +5415,1514 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Colo Colo</t>
+          <t>CA Deportivo Paraguayo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Justo Jose de Urquiza</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="G20" t="n">
-        <v>1.36</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>5.9</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T20" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Longford</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K21" t="n">
+        <v>950</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-11 07:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Club Indep Petrolero</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-11 07:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Everton De Vina</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-11 07:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Colo Colo</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" t="n">
+        <v>12</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>400</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-11 07:05:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>CD Gualberto Villarroel</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>The Strongest</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F25" t="n">
         <v>1.04</v>
       </c>
-      <c r="G21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="G25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H25" t="n">
         <v>1.04</v>
       </c>
-      <c r="I21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="I25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>2026-06-11 04:56:51</t>
+      <c r="Q25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,25 +863,25 @@
         <v>2.32</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
         <v>3.65</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
@@ -890,16 +890,16 @@
         <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
         <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="U2" t="n">
         <v>2.3</v>
@@ -911,10 +911,10 @@
         <v>1.75</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
         <v>32</v>
@@ -926,7 +926,7 @@
         <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
         <v>18</v>
@@ -935,13 +935,13 @@
         <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
         <v>13.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
         <v>55</v>
@@ -959,67 +959,67 @@
         <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
         <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
         <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
         <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
         <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI2" t="n">
         <v>3</v>
@@ -1028,13 +1028,13 @@
         <v>11</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>120</v>
       </c>
       <c r="BM2" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
         <v>6.2</v>
@@ -1046,48 +1046,48 @@
         <v>18.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
         <v>32</v>
       </c>
       <c r="BS2" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
         <v>32</v>
       </c>
       <c r="BW2" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
         <v>42</v>
       </c>
       <c r="BY2" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>25</v>
       </c>
       <c r="CA2" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tobol Kostanay</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>FK Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1123,225 +1123,225 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tvaakers</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jonkopings Sodra</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1377,225 +1377,225 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08:15:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>Tvaakers</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Jonkopings Sodra</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1631,22 +1631,22 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
@@ -1655,201 +1655,201 @@
         <v>1.01</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:15:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nomme Utd</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>2.72</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,36 +2113,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SC Grobina</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Nomme Utd</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.19</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.22</v>
+        <v>2.78</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J7" t="n">
-        <v>1.11</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,34 +2151,34 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>2.16</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2292,72 +2292,72 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,36 +2621,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2665,10 +2665,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,48 +2875,48 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IFK Stocksund</t>
+          <t>FC Zhetysu</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
@@ -2925,201 +2925,201 @@
         <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,251 +3129,251 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>Kairat Almaty</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>FK Atyrau</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
         <v>1.04</v>
       </c>
-      <c r="G11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
         <v>1.04</v>
       </c>
-      <c r="I11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0</v>
-      </c>
       <c r="BL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3383,251 +3383,251 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>SC Grobina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
         <v>1.04</v>
       </c>
-      <c r="G12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
         <v>1.04</v>
       </c>
-      <c r="I12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,12 +3896,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,17 +4399,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>IFK Stocksund</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4425,225 +4425,225 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>IF Karlstad</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,27 +4907,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Central Cordoba</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportivo Espanol</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,27 +5161,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Leandro N Alem</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Victoriano Arenas</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,251 +5415,251 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CA Deportivo Paraguayo</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Justo Jose de Urquiza</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>1.96</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BN20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,36 +5669,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.44</v>
+        <v>3.45</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="H21" t="n">
-        <v>2.74</v>
+        <v>2.18</v>
       </c>
       <c r="I21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.3</v>
       </c>
-      <c r="J21" t="n">
-        <v>2.82</v>
-      </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,17 +5923,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Club Indep Petrolero</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -5949,7 +5949,7 @@
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,251 +6177,251 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Everton De Vina</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P23" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.06</v>
+        <v>1.19</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,42 +6431,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Colo Colo</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.31</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
-        <v>1.36</v>
+        <v>4.1</v>
       </c>
       <c r="H24" t="n">
-        <v>10</v>
+        <v>1.95</v>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.74</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6487,10 +6487,10 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -6499,112 +6499,112 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BH24" t="n">
         <v>0</v>
@@ -6668,261 +6668,2293 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IFK Mariehamn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Argentinian Primera C</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Central Cordoba</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Deportivo Espanol</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Argentinian Primera C</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Leandro N Alem</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Victoriano Arenas</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Argentinian Primera C</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CA Deportivo Paraguayo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Justo Jose de Urquiza</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Longford</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K30" t="n">
+        <v>950</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Everton De Vina</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB31" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Colo Colo</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" t="n">
+        <v>12</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>440</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB32" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>CD Gualberto Villarroel</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>The Strongest</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="F33" t="n">
         <v>1.04</v>
       </c>
-      <c r="G25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="G33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H33" t="n">
         <v>1.04</v>
       </c>
-      <c r="I25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="I33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>2026-06-11 07:05:44</t>
+      <c r="Q33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB33" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB33"/>
+  <dimension ref="A1:CB41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,7 +881,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
@@ -890,7 +890,7 @@
         <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
         <v>1.45</v>
@@ -932,7 +932,7 @@
         <v>18</v>
       </c>
       <c r="AE2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
         <v>16</v>
@@ -1025,7 +1025,7 @@
         <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BK2" t="n">
         <v>1.01</v>
@@ -1037,10 +1037,10 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP2" t="n">
         <v>18.5</v>
@@ -1055,7 +1055,7 @@
         <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BU2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1132,25 +1132,25 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.25</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
         <v>1.01</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1873,112 +1873,112 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>2.74</v>
       </c>
       <c r="O6" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.38</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.38</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP6" t="n">
         <v>1.01</v>
@@ -2035,13 +2035,13 @@
         <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BK6" t="n">
         <v>1.01</v>
@@ -2053,50 +2053,50 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS6" t="n">
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BU6" t="n">
         <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW6" t="n">
         <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA6" t="n">
         <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H7" t="n">
         <v>2.78</v>
@@ -2151,22 +2151,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
         <v>1.14</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2175,10 +2175,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -2372,246 +2372,246 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,246 +2626,246 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>FC Zhetysu</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>2.64</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,239 +2880,239 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Zhetysu</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.92</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>3.1</v>
+        <v>1.84</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>2.64</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
-        <v>1.05</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V10" t="n">
-        <v>1.61</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK10" t="n">
         <v>1.01</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM10" t="n">
         <v>1.01</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ10" t="n">
         <v>1.01</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS10" t="n">
         <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU10" t="n">
         <v>1.01</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW10" t="n">
         <v>1.01</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY10" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA10" t="n">
         <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -3149,13 +3149,13 @@
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3170,19 +3170,19 @@
         <v>1.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -3403,13 +3403,13 @@
         <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="I12" t="n">
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
       </c>
       <c r="P12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Q12" t="n">
         <v>1.17</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,36 +3637,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>Huracan del Paso</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>Tacuarembo</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>IF Karlstad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3923,212 +3923,212 @@
         <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4171,218 +4171,218 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -4404,12 +4404,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IFK Stocksund</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4425,218 +4425,218 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -4658,12 +4658,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4679,218 +4679,218 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -4933,225 +4933,225 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>IFK Stocksund</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -5187,218 +5187,218 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H20" t="n">
         <v>1.6</v>
@@ -5447,16 +5447,16 @@
         <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
         <v>1.92</v>
@@ -5465,201 +5465,201 @@
         <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,246 +5674,246 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>1.12</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,246 +5928,246 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,17 +6177,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,34 +6215,34 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="O23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P23" t="n">
         <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R23" t="n">
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6356,72 +6356,72 @@
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN23" t="n">
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT23" t="n">
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,251 +6431,251 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.4</v>
       </c>
-      <c r="G24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>1.51</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.66</v>
+        <v>2.52</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,251 +6685,251 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.89</v>
+        <v>1.19</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6944,31 +6944,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="G26" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H26" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="I26" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,36 +7193,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Central Cordoba</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportivo Espanol</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="H27" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J27" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,36 +7447,36 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Leandro N Alem</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Victoriano Arenas</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="J28" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -7491,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,36 +7701,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CA Deportivo Paraguayo</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Justo Jose de Urquiza</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H29" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,34 +7739,34 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="O29" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S29" t="n">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -7880,72 +7880,72 @@
         <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN29" t="n">
         <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,251 +7955,251 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>OHiggins</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.46</v>
+        <v>1.82</v>
       </c>
       <c r="G30" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="H30" t="n">
-        <v>2.74</v>
+        <v>4.7</v>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="J30" t="n">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T30" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8209,36 +8209,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Everton De Vina</t>
+          <t>Central Cordoba</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Espanol</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.76</v>
+        <v>1.02</v>
       </c>
       <c r="G31" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="I31" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="K31" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8463,42 +8463,42 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Colo Colo</t>
+          <t>Leandro N Alem</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Victoriano Arenas</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="G32" t="n">
-        <v>1.36</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>1.02</v>
       </c>
       <c r="I32" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="K32" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8519,10 +8519,10 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -8531,112 +8531,112 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
         <v>0</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,48 +8717,48 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>CA Deportivo Paraguayo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Justo Jose de Urquiza</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G33" t="n">
         <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I33" t="n">
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P33" t="n">
         <v>1.24</v>
@@ -8767,194 +8767,2226 @@
         <v>1.01</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Longford</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:32:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Club Indep Petrolero</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Real Potosi</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:32:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Amazonas FC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Anapolis GO</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:32:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Everton De Vina</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:32:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Colon FC</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Centro Atletico Fenix</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB38" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:32:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Colo Colo</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cobresal</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H39" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" t="n">
+        <v>12</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>430</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB39" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:32:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CD Gualberto Villarroel</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:32:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Club Oriental de La Paz</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CA Rentistas</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB41" t="inlineStr">
+        <is>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB41"/>
+  <dimension ref="A1:CB40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>23</v>
       </c>
       <c r="Y2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z2" t="n">
         <v>32</v>
@@ -935,7 +935,7 @@
         <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
         <v>13.5</v>
@@ -1025,7 +1025,7 @@
         <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
         <v>1.01</v>
@@ -1037,10 +1037,10 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
         <v>18.5</v>
@@ -1055,7 +1055,7 @@
         <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU2" t="n">
         <v>1.01</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1153,16 +1153,16 @@
         <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1670,7 +1670,7 @@
         <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1876,22 +1876,22 @@
         <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
@@ -1900,13 +1900,13 @@
         <v>2.74</v>
       </c>
       <c r="O6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P6" t="n">
         <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
         <v>1.23</v>
@@ -1915,16 +1915,16 @@
         <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -1933,10 +1933,10 @@
         <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB6" t="n">
         <v>970</v>
@@ -1948,7 +1948,7 @@
         <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
         <v>970</v>
@@ -1960,10 +1960,10 @@
         <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ6" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
         <v>38</v>
@@ -1975,10 +1975,10 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
         <v>1.01</v>
@@ -2038,7 +2038,7 @@
         <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ6" t="n">
         <v>970</v>
@@ -2053,7 +2053,7 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>970</v>
+        <v>5.8</v>
       </c>
       <c r="BO6" t="n">
         <v>4.3</v>
@@ -2071,13 +2071,13 @@
         <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>3.9</v>
@@ -2408,19 +2408,19 @@
         <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
         <v>1.61</v>
@@ -2432,13 +2432,13 @@
         <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
         <v>21</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Z8" t="n">
         <v>38</v>
@@ -2495,52 +2495,52 @@
         <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV8" t="n">
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ8" t="n">
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BC8" t="n">
         <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="n">
         <v>4.3</v>
@@ -2585,13 +2585,13 @@
         <v>6</v>
       </c>
       <c r="BV8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW8" t="n">
         <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BY8" t="n">
         <v>1.01</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -2659,13 +2659,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O9" t="n">
         <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q9" t="n">
         <v>1.84</v>
@@ -2674,7 +2674,7 @@
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2698,7 +2698,7 @@
         <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
         <v>16</v>
@@ -2707,43 +2707,43 @@
         <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF9" t="n">
         <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AI9" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AJ9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>470</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO9" t="n">
         <v>100</v>
       </c>
-      <c r="AK9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>210</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>600</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>190</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>130</v>
-      </c>
       <c r="AP9" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AQ9" t="n">
         <v>5.3</v>
@@ -2755,7 +2755,7 @@
         <v>28</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
         <v>5.8</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -2931,10 +2931,10 @@
         <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
         <v>1.21</v>
@@ -2943,7 +2943,7 @@
         <v>2.2</v>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
         <v>20</v>
@@ -2976,7 +2976,7 @@
         <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
         <v>22</v>
@@ -2985,10 +2985,10 @@
         <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
         <v>14.5</v>
@@ -3003,10 +3003,10 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT10" t="n">
         <v>7.2</v>
@@ -3018,10 +3018,10 @@
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10" t="n">
         <v>9</v>
@@ -3048,7 +3048,7 @@
         <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BH10" t="n">
         <v>3.75</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3173,7 +3173,7 @@
         <v>1.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Q11" t="n">
         <v>1.3</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>1.39</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -3669,16 +3669,16 @@
         <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
         <v>1.39</v>
@@ -3687,194 +3687,194 @@
         <v>2.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3929,7 +3929,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
         <v>1.18</v>
@@ -3944,7 +3944,7 @@
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,13 +4183,13 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
         <v>1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q15" t="n">
         <v>1.16</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q16" t="n">
         <v>1.23</v>
@@ -4452,13 +4452,13 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O17" t="n">
         <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q17" t="n">
         <v>1.2</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -4945,7 +4945,7 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O18" t="n">
         <v>1.15</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
@@ -5199,13 +5199,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O19" t="n">
         <v>1.13</v>
       </c>
       <c r="P19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q19" t="n">
         <v>1.13</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G20" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="H20" t="n">
         <v>1.6</v>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.25</v>
@@ -5480,7 +5480,7 @@
         <v>2.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5537,52 +5537,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5707,13 +5707,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O21" t="n">
         <v>1.12</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q21" t="n">
         <v>1.12</v>
@@ -5722,7 +5722,7 @@
         <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -5958,10 +5958,10 @@
         <v>1.35</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.33</v>
@@ -5973,10 +5973,10 @@
         <v>2.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -5994,37 +5994,37 @@
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB22" t="n">
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG22" t="n">
         <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ22" t="n">
         <v>1000</v>
@@ -6033,7 +6033,7 @@
         <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
@@ -6045,58 +6045,58 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AU22" t="n">
-        <v>6</v>
+        <v>1.45</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13.5</v>
+        <v>1.58</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BE22" t="n">
-        <v>40</v>
+        <v>1.68</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,7 +6215,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.18</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -6445,175 +6445,175 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="G24" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J24" t="n">
         <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>1.51</v>
+        <v>2.52</v>
       </c>
       <c r="O24" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="P24" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="R24" t="n">
         <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V24" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>90</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BE24" t="n">
         <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK24" t="n">
         <v>1.01</v>
@@ -6625,50 +6625,50 @@
         <v>1.01</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ24" t="n">
         <v>1.01</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS24" t="n">
         <v>1.01</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU24" t="n">
         <v>1.01</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW24" t="n">
         <v>1.01</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY24" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA24" t="n">
         <v>1.01</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -6953,230 +6953,230 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G26" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="H26" t="n">
         <v>1.95</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
         <v>4.3</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BM26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN26" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BP26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BS26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT26" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BU26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BX26" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BY26" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G27" t="n">
         <v>2.5</v>
@@ -7225,16 +7225,16 @@
         <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
@@ -7243,194 +7243,194 @@
         <v>1.89</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>3.95</v>
       </c>
       <c r="G28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H28" t="n">
         <v>1.99</v>
@@ -7479,212 +7479,212 @@
         <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P28" t="n">
         <v>1.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
         <v>2.14</v>
       </c>
       <c r="O29" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="P29" t="n">
         <v>1.4</v>
@@ -7754,7 +7754,7 @@
         <v>1.14</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -7990,49 +7990,49 @@
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>1.77</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P30" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>2.04</v>
+        <v>3.9</v>
       </c>
       <c r="T30" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="U30" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="V30" t="n">
         <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB30" t="n">
         <v>9</v>
@@ -8041,94 +8041,94 @@
         <v>9.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.27</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.27</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.27</v>
+        <v>5</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.11</v>
+        <v>6.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.27</v>
+        <v>15</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.27</v>
+        <v>4.9</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.27</v>
+        <v>8.4</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.27</v>
+        <v>8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.27</v>
+        <v>4.3</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.27</v>
+        <v>4.9</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.27</v>
+        <v>16</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.27</v>
+        <v>16.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.27</v>
+        <v>4.7</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.27</v>
+        <v>5</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.27</v>
+        <v>11.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.27</v>
+        <v>5</v>
       </c>
       <c r="BH30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
         <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K33" t="n">
         <v>1000</v>
@@ -8755,7 +8755,7 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -9747,16 +9747,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G37" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H37" t="n">
         <v>2.72</v>
       </c>
       <c r="I37" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J37" t="n">
         <v>3.25</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
         <v>1.53</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -10478,14 +10478,14 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10495,36 +10495,36 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="G40" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H40" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="I40" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="K40" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -10539,10 +10539,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -10732,261 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Uruguayan Segunda Division</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Club Oriental de La Paz</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>CA Rentistas</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="G41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB41" t="inlineStr">
-        <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -881,7 +881,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
@@ -896,13 +896,13 @@
         <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
         <v>1.65</v>
       </c>
       <c r="U2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
@@ -914,7 +914,7 @@
         <v>23</v>
       </c>
       <c r="Y2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z2" t="n">
         <v>32</v>
@@ -935,7 +935,7 @@
         <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
         <v>13.5</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,22 +1135,22 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
         <v>1.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.92</v>
+        <v>1.35</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>1.35</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -1407,10 +1407,10 @@
         <v>1.09</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -1888,10 +1888,10 @@
         <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
@@ -1903,7 +1903,7 @@
         <v>1.44</v>
       </c>
       <c r="P6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q6" t="n">
         <v>2.2</v>
@@ -1918,7 +1918,7 @@
         <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="V6" t="n">
         <v>1.36</v>
@@ -1996,7 +1996,7 @@
         <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV6" t="n">
         <v>1.01</v>
@@ -2038,7 +2038,7 @@
         <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6" t="n">
         <v>970</v>
@@ -2053,13 +2053,13 @@
         <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ6" t="n">
         <v>1.01</v>
@@ -2083,7 +2083,7 @@
         <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
         <v>1.01</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -2169,10 +2169,10 @@
         <v>2.18</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.41</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -2396,10 +2396,10 @@
         <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -2408,25 +2408,25 @@
         <v>4.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
         <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T8" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="V8" t="n">
         <v>1.28</v>
@@ -2456,13 +2456,13 @@
         <v>20</v>
       </c>
       <c r="AE8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
         <v>15</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>20</v>
@@ -2474,34 +2474,34 @@
         <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>95</v>
       </c>
       <c r="AN8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO8" t="n">
         <v>55</v>
       </c>
       <c r="AP8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>13</v>
-      </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU8" t="n">
         <v>7.8</v>
@@ -2510,37 +2510,37 @@
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BC8" t="n">
         <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH8" t="n">
         <v>4.3</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>600</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
         <v>2.64</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="K9" t="n">
         <v>3.75</v>
@@ -2659,34 +2659,34 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="X9" t="n">
         <v>17</v>
@@ -2698,7 +2698,7 @@
         <v>20</v>
       </c>
       <c r="AA9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB9" t="n">
         <v>16</v>
@@ -2707,46 +2707,46 @@
         <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF9" t="n">
         <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ9" t="n">
         <v>90</v>
       </c>
       <c r="AK9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL9" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AM9" t="n">
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="AN9" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO9" t="n">
         <v>100</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR9" t="n">
         <v>12.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -2892,49 +2892,49 @@
         <v>1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
         <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
         <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
         <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V10" t="n">
         <v>1.21</v>
@@ -2946,7 +2946,7 @@
         <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
         <v>50</v>
@@ -2955,7 +2955,7 @@
         <v>170</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AC10" t="n">
         <v>10</v>
@@ -2988,10 +2988,10 @@
         <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
         <v>120</v>
@@ -3000,28 +3000,28 @@
         <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
         <v>7.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY10" t="n">
         <v>9</v>
@@ -3030,7 +3030,7 @@
         <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
         <v>14.5</v>
@@ -3039,16 +3039,16 @@
         <v>17</v>
       </c>
       <c r="BD10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.3</v>
       </c>
       <c r="BF10" t="n">
         <v>10.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="n">
         <v>3.75</v>
@@ -3072,13 +3072,13 @@
         <v>4.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BP10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BR10" t="n">
         <v>34</v>
@@ -3087,7 +3087,7 @@
         <v>1.01</v>
       </c>
       <c r="BT10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU10" t="n">
         <v>1.01</v>
@@ -3105,14 +3105,14 @@
         <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA10" t="n">
         <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -3149,13 +3149,13 @@
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
         <v>1.18</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -3669,40 +3669,40 @@
         <v>3.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>1.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P13" t="n">
         <v>1.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
         <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O14" t="n">
         <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q14" t="n">
         <v>1.18</v>
@@ -3947,16 +3947,16 @@
         <v>1.19</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,13 +4183,13 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q15" t="n">
         <v>1.16</v>
@@ -4198,19 +4198,19 @@
         <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -4437,13 +4437,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Q16" t="n">
         <v>1.23</v>
@@ -4452,7 +4452,7 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q17" t="n">
         <v>1.2</v>
@@ -4709,16 +4709,16 @@
         <v>1.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -4945,13 +4945,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.15</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q18" t="n">
         <v>1.15</v>
@@ -4963,10 +4963,10 @@
         <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K19" t="n">
         <v>1000</v>
@@ -5199,13 +5199,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O19" t="n">
         <v>1.13</v>
       </c>
       <c r="P19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q19" t="n">
         <v>1.13</v>
@@ -5217,16 +5217,16 @@
         <v>1.13</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -5429,166 +5429,166 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G20" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="I20" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.31</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V20" t="n">
         <v>2.2</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>2.04</v>
-      </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5707,28 +5707,28 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O21" t="n">
         <v>1.12</v>
       </c>
       <c r="P21" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="R21" t="n">
         <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>3.45</v>
       </c>
       <c r="G22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H22" t="n">
         <v>2.2</v>
@@ -5955,148 +5955,148 @@
         <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q22" t="n">
         <v>2.02</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W22" t="n">
         <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF22" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
         <v>60</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL22" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.68</v>
+        <v>9.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AS22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW22" t="n">
         <v>18</v>
       </c>
-      <c r="AT22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AX22" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.68</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.58</v>
+        <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.64</v>
+        <v>24</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.68</v>
+        <v>5.9</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.68</v>
+        <v>5.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.65</v>
+        <v>5.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.68</v>
+        <v>6</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.68</v>
+        <v>5.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.68</v>
+        <v>14</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6105,7 +6105,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK22" t="n">
         <v>1.01</v>
@@ -6117,28 +6117,28 @@
         <v>1.01</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ22" t="n">
         <v>1.01</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS22" t="n">
         <v>1.01</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6215,13 +6215,13 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O23" t="n">
         <v>1.18</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q23" t="n">
         <v>1.18</v>
@@ -6233,16 +6233,16 @@
         <v>1.18</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -6445,55 +6445,55 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="G24" t="n">
         <v>2.14</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L24" t="n">
         <v>1.57</v>
       </c>
       <c r="M24" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="P24" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R24" t="n">
         <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T24" t="n">
         <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W24" t="n">
         <v>1.87</v>
@@ -6502,7 +6502,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z24" t="n">
         <v>42</v>
@@ -6523,10 +6523,10 @@
         <v>120</v>
       </c>
       <c r="AF24" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH24" t="n">
         <v>32</v>
@@ -6559,10 +6559,10 @@
         <v>9.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
         <v>5</v>
@@ -6571,10 +6571,10 @@
         <v>6</v>
       </c>
       <c r="AV24" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
         <v>8.4</v>
@@ -6583,28 +6583,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
         <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
         <v>2.92</v>
@@ -6613,7 +6613,7 @@
         <v>2.24</v>
       </c>
       <c r="BJ24" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="BK24" t="n">
         <v>1.01</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O25" t="n">
         <v>1.19</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G26" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="H26" t="n">
         <v>1.95</v>
@@ -6977,13 +6977,13 @@
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.23</v>
       </c>
       <c r="P26" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q26" t="n">
         <v>1.66</v>
@@ -6995,16 +6995,16 @@
         <v>2.66</v>
       </c>
       <c r="T26" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="U26" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W26" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X26" t="n">
         <v>24</v>
@@ -7019,7 +7019,7 @@
         <v>28</v>
       </c>
       <c r="AB26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AC26" t="n">
         <v>9.6</v>
@@ -7028,7 +7028,7 @@
         <v>11</v>
       </c>
       <c r="AE26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="n">
         <v>36</v>
@@ -7037,7 +7037,7 @@
         <v>16.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
         <v>34</v>
@@ -7061,40 +7061,40 @@
         <v>11</v>
       </c>
       <c r="AP26" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
         <v>1.01</v>
@@ -7109,74 +7109,74 @@
         <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
         <v>4.6</v>
       </c>
       <c r="BI26" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26" t="n">
         <v>10.5</v>
       </c>
       <c r="BK26" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL26" t="n">
         <v>100</v>
       </c>
       <c r="BM26" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BN26" t="n">
         <v>8.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP26" t="n">
         <v>34</v>
       </c>
       <c r="BQ26" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR26" t="n">
         <v>40</v>
       </c>
       <c r="BS26" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BT26" t="n">
         <v>5.7</v>
       </c>
       <c r="BU26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV26" t="n">
         <v>15.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX26" t="n">
         <v>27</v>
       </c>
       <c r="BY26" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
         <v>21</v>
       </c>
       <c r="CA26" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
         <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>3.5</v>
@@ -7225,16 +7225,16 @@
         <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="M27" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
@@ -7243,130 +7243,130 @@
         <v>1.89</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF27" t="n">
         <v>17</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL27" t="n">
         <v>44</v>
       </c>
-      <c r="AF27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.18</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.18</v>
+        <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.18</v>
+        <v>19</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.18</v>
+        <v>4.9</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.18</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.18</v>
+        <v>6.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.15</v>
+        <v>4.7</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.11</v>
+        <v>12</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.18</v>
+        <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.18</v>
+        <v>4.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.15</v>
+        <v>4.7</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.18</v>
+        <v>21</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.18</v>
+        <v>4.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.18</v>
+        <v>5</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.18</v>
+        <v>14.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.18</v>
+        <v>4.7</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7375,7 +7375,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK27" t="n">
         <v>1.01</v>
@@ -7387,50 +7387,50 @@
         <v>1.01</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ27" t="n">
         <v>1.01</v>
       </c>
       <c r="BR27" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS27" t="n">
         <v>1.01</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW27" t="n">
         <v>1.01</v>
       </c>
       <c r="BX27" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY27" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA27" t="n">
         <v>1.01</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -7473,154 +7473,154 @@
         <v>2.14</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
         <v>1.97</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V28" t="n">
         <v>1.88</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE28" t="n">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
         <v>5.9</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
@@ -7757,10 +7757,10 @@
         <v>2.78</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
         <v>1.35</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -7972,13 +7972,13 @@
         <v>1.82</v>
       </c>
       <c r="G30" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H30" t="n">
         <v>4.7</v>
       </c>
       <c r="I30" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
@@ -7987,13 +7987,13 @@
         <v>3.9</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
         <v>1.37</v>
@@ -8005,19 +8005,19 @@
         <v>2.08</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
         <v>3.9</v>
       </c>
       <c r="T30" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U30" t="n">
         <v>1.92</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W30" t="n">
         <v>2.06</v>
@@ -8092,7 +8092,7 @@
         <v>6.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV30" t="n">
         <v>15</v>
@@ -8101,10 +8101,10 @@
         <v>4.9</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ30" t="n">
         <v>4.3</v>
@@ -8131,68 +8131,68 @@
         <v>5</v>
       </c>
       <c r="BH30" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ30" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK30" t="n">
         <v>1.01</v>
       </c>
       <c r="BL30" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BM30" t="n">
         <v>1.01</v>
       </c>
       <c r="BN30" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP30" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ30" t="n">
         <v>1.01</v>
       </c>
       <c r="BR30" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS30" t="n">
         <v>1.01</v>
       </c>
       <c r="BT30" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BU30" t="n">
         <v>1.01</v>
       </c>
       <c r="BV30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW30" t="n">
         <v>1.01</v>
       </c>
       <c r="BX30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY30" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA30" t="n">
         <v>1.01</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -8241,16 +8241,16 @@
         <v>1000</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
         <v>1.24</v>
@@ -8259,184 +8259,184 @@
         <v>1.01</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31" t="n">
         <v>0</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -8495,16 +8495,16 @@
         <v>1000</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P32" t="n">
         <v>1.24</v>
@@ -8513,194 +8513,194 @@
         <v>1.01</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
         <v>1.01</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Q33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -9003,16 +9003,16 @@
         <v>4.5</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P34" t="n">
         <v>1.8</v>
@@ -9021,194 +9021,194 @@
         <v>1.98</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -9747,22 +9747,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H37" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I37" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J37" t="n">
         <v>3.25</v>
       </c>
       <c r="K37" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -10363,16 +10363,16 @@
         <v>200</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR39" t="n">
         <v>4.3</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT39" t="n">
         <v>10</v>
@@ -10381,10 +10381,10 @@
         <v>12.5</v>
       </c>
       <c r="AV39" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX39" t="n">
         <v>8.6</v>
@@ -10393,10 +10393,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ39" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB39" t="n">
         <v>9.800000000000001</v>
@@ -10408,13 +10408,13 @@
         <v>4</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF39" t="n">
         <v>3.35</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -869,13 +869,13 @@
         <v>3.65</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
         <v>1.8</v>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>2.26</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1144,13 +1144,13 @@
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1643,7 +1643,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.18</v>
@@ -1652,7 +1652,7 @@
         <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
@@ -1661,10 +1661,10 @@
         <v>1.18</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1784,65 +1784,65 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5" t="n">
         <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
         <v>1.12</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q6" t="n">
         <v>1.12</v>
@@ -1912,13 +1912,13 @@
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.01</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -2127,31 +2127,31 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
         <v>1.1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.26</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
@@ -2163,10 +2163,10 @@
         <v>1.34</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2292,65 +2292,65 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
         <v>1.94</v>
@@ -2552,13 +2552,13 @@
         <v>970</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>5.7</v>
@@ -2570,41 +2570,41 @@
         <v>23</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>46</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
         <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>60</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>46</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
         <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
         <v>1.21</v>
@@ -2994,7 +2994,7 @@
         <v>14</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP10" t="n">
         <v>12</v>
@@ -3003,10 +3003,10 @@
         <v>13.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT10" t="n">
         <v>7.2</v>
@@ -3039,10 +3039,10 @@
         <v>17</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
         <v>10.5</v>
@@ -3060,59 +3060,59 @@
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BL10" t="n">
         <v>170</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="BP10" t="n">
         <v>14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="BR10" t="n">
         <v>34</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BT10" t="n">
         <v>10</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV10" t="n">
         <v>55</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BX10" t="n">
         <v>65</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>27</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -3314,13 +3314,13 @@
         <v>11</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BL11" t="n">
         <v>120</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BN11" t="n">
         <v>5.5</v>
@@ -3332,41 +3332,41 @@
         <v>15</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BR11" t="n">
         <v>29</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BT11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU11" t="n">
         <v>6</v>
       </c>
       <c r="BV11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BX11" t="n">
         <v>46</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BZ11" t="n">
         <v>23</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>590</v>
       </c>
       <c r="H12" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="I12" t="n">
         <v>2.62</v>
@@ -3427,7 +3427,7 @@
         <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q12" t="n">
         <v>1.84</v>
@@ -3448,7 +3448,7 @@
         <v>1.61</v>
       </c>
       <c r="W12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
         <v>17</v>
@@ -3475,10 +3475,10 @@
         <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH12" t="n">
         <v>44</v>
@@ -3487,31 +3487,31 @@
         <v>130</v>
       </c>
       <c r="AJ12" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AK12" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AL12" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AM12" t="n">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="AN12" t="n">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="AO12" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS12" t="n">
         <v>19.5</v>
@@ -3532,7 +3532,7 @@
         <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>13</v>
@@ -3544,7 +3544,7 @@
         <v>38</v>
       </c>
       <c r="BC12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD12" t="n">
         <v>32</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -3816,65 +3816,65 @@
         <v>1000</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN13" t="n">
         <v>1000</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13" t="n">
         <v>1000</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -4165,13 +4165,13 @@
         <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="I15" t="n">
         <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
         <v>1000</v>
@@ -4183,22 +4183,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.3</v>
+        <v>2.06</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>2.06</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -4210,7 +4210,7 @@
         <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
         <v>3.45</v>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M16" t="n">
         <v>1.13</v>
@@ -4452,7 +4452,7 @@
         <v>1.17</v>
       </c>
       <c r="S16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T16" t="n">
         <v>2.08</v>
@@ -4584,13 +4584,13 @@
         <v>970</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>5</v>
@@ -4602,41 +4602,41 @@
         <v>20</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>50</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>65</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>90</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
         <v>55</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O17" t="n">
         <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q17" t="n">
         <v>1.18</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
         <v>13.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AF18" t="n">
         <v>26</v>
@@ -5011,10 +5011,10 @@
         <v>48</v>
       </c>
       <c r="AJ18" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AK18" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
         <v>65</v>
@@ -5023,7 +5023,7 @@
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AO18" t="n">
         <v>24</v>
@@ -5089,7 +5089,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ18" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18" t="n">
         <v>1.01</v>
@@ -5101,10 +5101,10 @@
         <v>1.01</v>
       </c>
       <c r="BN18" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
@@ -5119,10 +5119,10 @@
         <v>1.01</v>
       </c>
       <c r="BT18" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -5340,65 +5340,65 @@
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
         <v>1000</v>
@@ -5453,7 +5453,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O20" t="n">
         <v>1.12</v>
@@ -5594,65 +5594,65 @@
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
         <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="K21" t="n">
         <v>1000</v>
@@ -5707,13 +5707,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O21" t="n">
         <v>1.15</v>
       </c>
       <c r="P21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q21" t="n">
         <v>1.15</v>
@@ -5848,65 +5848,65 @@
         <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,13 +5961,13 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O22" t="n">
         <v>1.18</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q22" t="n">
         <v>1.18</v>
@@ -6102,65 +6102,65 @@
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -6191,19 +6191,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I23" t="n">
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
@@ -6224,7 +6224,7 @@
         <v>1.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="R23" t="n">
         <v>1.24</v>
@@ -6356,65 +6356,65 @@
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
         <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
         <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
         <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
         <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
         <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
         <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
         <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
         <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G24" t="n">
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6484,7 +6484,7 @@
         <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6493,7 +6493,7 @@
         <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
         <v>1.02</v>
@@ -6610,65 +6610,65 @@
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
         <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
         <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -6864,65 +6864,65 @@
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -6953,19 +6953,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="G26" t="n">
         <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I26" t="n">
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
         <v>1000</v>
@@ -6977,7 +6977,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="O26" t="n">
         <v>1.18</v>
@@ -7118,65 +7118,65 @@
         <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G28" t="n">
         <v>4.1</v>
@@ -7536,7 +7536,7 @@
         <v>11</v>
       </c>
       <c r="AE28" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AF28" t="n">
         <v>36</v>
@@ -7662,7 +7662,7 @@
         <v>5.7</v>
       </c>
       <c r="BU28" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV28" t="n">
         <v>15.5</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
         <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R29" t="n">
         <v>1.36</v>
@@ -7883,7 +7883,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ29" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
         <v>1.01</v>
@@ -7895,50 +7895,50 @@
         <v>1.01</v>
       </c>
       <c r="BN29" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP29" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
         <v>1.01</v>
       </c>
       <c r="BR29" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
         <v>1.01</v>
       </c>
       <c r="BT29" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV29" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
         <v>1.01</v>
       </c>
       <c r="BX29" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ29" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
         <v>1.01</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -8134,65 +8134,65 @@
         <v>1000</v>
       </c>
       <c r="BI30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ30" t="n">
         <v>1000</v>
       </c>
       <c r="BK30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL30" t="n">
         <v>1000</v>
       </c>
       <c r="BM30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN30" t="n">
         <v>1000</v>
       </c>
       <c r="BO30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP30" t="n">
         <v>1000</v>
       </c>
       <c r="BQ30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR30" t="n">
         <v>1000</v>
       </c>
       <c r="BS30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT30" t="n">
         <v>1000</v>
       </c>
       <c r="BU30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV30" t="n">
         <v>1000</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX30" t="n">
         <v>1000</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ30" t="n">
         <v>1000</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -8388,65 +8388,65 @@
         <v>1000</v>
       </c>
       <c r="BI31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ31" t="n">
         <v>1000</v>
       </c>
       <c r="BK31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN31" t="n">
         <v>1000</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT31" t="n">
         <v>1000</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV31" t="n">
         <v>1000</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
         <v>3.9</v>
       </c>
       <c r="L32" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
@@ -8543,10 +8543,10 @@
         <v>150</v>
       </c>
       <c r="AB32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD32" t="n">
         <v>23</v>
@@ -8582,7 +8582,7 @@
         <v>18</v>
       </c>
       <c r="AO32" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP32" t="n">
         <v>9.800000000000001</v>
@@ -8591,10 +8591,10 @@
         <v>12</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT32" t="n">
         <v>6.8</v>
@@ -8606,7 +8606,7 @@
         <v>15</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX32" t="n">
         <v>9.6</v>
@@ -8615,10 +8615,10 @@
         <v>9</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB32" t="n">
         <v>16</v>
@@ -8627,16 +8627,16 @@
         <v>16.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BE32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BF32" t="n">
         <v>11.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BH32" t="n">
         <v>3.55</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O33" t="n">
         <v>1.01</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9009,7 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
         <v>1.01</v>
@@ -9024,7 +9024,7 @@
         <v>1.12</v>
       </c>
       <c r="S34" t="n">
-        <v>1.49</v>
+        <v>1.05</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
         <v>2.74</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J37" t="n">
         <v>3.25</v>
@@ -9765,7 +9765,7 @@
         <v>3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="M37" t="n">
         <v>1.08</v>
@@ -9792,7 +9792,7 @@
         <v>1.81</v>
       </c>
       <c r="U37" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V37" t="n">
         <v>1.51</v>
@@ -9867,7 +9867,7 @@
         <v>3.95</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU37" t="n">
         <v>6.8</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
         <v>2.36</v>
       </c>
       <c r="R38" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S38" t="n">
         <v>2.6</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="K39" t="n">
         <v>1000</v>
@@ -10420,55 +10420,55 @@
         <v>1000</v>
       </c>
       <c r="BI39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ39" t="n">
         <v>1000</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN39" t="n">
         <v>1000</v>
       </c>
       <c r="BO39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP39" t="n">
         <v>1000</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR39" t="n">
         <v>1000</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT39" t="n">
         <v>1000</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV39" t="n">
         <v>1000</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX39" t="n">
         <v>1000</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
         <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K41" t="n">
         <v>1000</v>
@@ -10787,7 +10787,7 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O41" t="n">
         <v>1.01</v>
@@ -10796,19 +10796,19 @@
         <v>1.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R41" t="n">
         <v>1.12</v>
       </c>
       <c r="S41" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T41" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U41" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K42" t="n">
         <v>1000</v>
@@ -11041,7 +11041,7 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O42" t="n">
         <v>1.01</v>
@@ -11050,19 +11050,19 @@
         <v>1.24</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R42" t="n">
         <v>1.12</v>
       </c>
       <c r="S42" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K43" t="n">
         <v>1000</v>
@@ -11295,7 +11295,7 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O43" t="n">
         <v>1.01</v>
@@ -11304,19 +11304,19 @@
         <v>1.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R43" t="n">
         <v>1.12</v>
       </c>
       <c r="S43" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T43" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U43" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V43" t="n">
         <v>1.01</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K44" t="n">
         <v>1000</v>
@@ -11549,7 +11549,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O44" t="n">
         <v>1.01</v>
@@ -11567,10 +11567,10 @@
         <v>1.02</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V44" t="n">
         <v>1.01</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
         <v>1000</v>
       </c>
       <c r="J45" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K45" t="n">
         <v>1000</v>
@@ -11803,7 +11803,7 @@
         <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O45" t="n">
         <v>1.01</v>
@@ -11818,13 +11818,13 @@
         <v>1.12</v>
       </c>
       <c r="S45" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U45" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
         <v>1000</v>
       </c>
       <c r="J46" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K46" t="n">
         <v>1000</v>
@@ -12066,19 +12066,19 @@
         <v>1.24</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R46" t="n">
         <v>1.12</v>
       </c>
       <c r="S46" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
         <v>1000</v>
       </c>
       <c r="J47" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K47" t="n">
         <v>1000</v>
@@ -12311,7 +12311,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O47" t="n">
         <v>1.01</v>
@@ -12320,23 +12320,23 @@
         <v>1.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R47" t="n">
         <v>1.12</v>
       </c>
       <c r="S47" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V47" t="n">
         <v>1.02</v>
       </c>
-      <c r="T47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W47" t="n">
         <v>1.01</v>
       </c>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
         <v>1000</v>
       </c>
       <c r="J48" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K48" t="n">
         <v>1000</v>
@@ -12580,13 +12580,13 @@
         <v>1.12</v>
       </c>
       <c r="S48" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T48" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U48" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V48" t="n">
         <v>1.01</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -12807,7 +12807,7 @@
         <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K49" t="n">
         <v>1000</v>
@@ -12819,28 +12819,28 @@
         <v>1.01</v>
       </c>
       <c r="N49" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="O49" t="n">
         <v>1.01</v>
       </c>
       <c r="P49" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R49" t="n">
         <v>1.12</v>
       </c>
       <c r="S49" t="n">
-        <v>1.02</v>
+        <v>1.52</v>
       </c>
       <c r="T49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U49" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V49" t="n">
         <v>1.01</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -13061,7 +13061,7 @@
         <v>1000</v>
       </c>
       <c r="J50" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K50" t="n">
         <v>1000</v>
@@ -13082,19 +13082,19 @@
         <v>1.24</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R50" t="n">
         <v>1.12</v>
       </c>
       <c r="S50" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U50" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V50" t="n">
         <v>1.01</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -13315,7 +13315,7 @@
         <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K51" t="n">
         <v>1000</v>
@@ -13327,7 +13327,7 @@
         <v>1.01</v>
       </c>
       <c r="N51" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O51" t="n">
         <v>1.01</v>
@@ -13342,13 +13342,13 @@
         <v>1.12</v>
       </c>
       <c r="S51" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -13575,16 +13575,16 @@
         <v>6.8</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P52" t="n">
         <v>2.74</v>
@@ -13593,10 +13593,10 @@
         <v>1.48</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T52" t="n">
         <v>1.89</v>
@@ -13605,10 +13605,10 @@
         <v>1.98</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X52" t="n">
         <v>36</v>
@@ -13623,10 +13623,10 @@
         <v>430</v>
       </c>
       <c r="AB52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC52" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD52" t="n">
         <v>48</v>
@@ -13635,10 +13635,10 @@
         <v>180</v>
       </c>
       <c r="AF52" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG52" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH52" t="n">
         <v>32</v>
@@ -13647,7 +13647,7 @@
         <v>140</v>
       </c>
       <c r="AJ52" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK52" t="n">
         <v>16.5</v>
@@ -13659,22 +13659,22 @@
         <v>150</v>
       </c>
       <c r="AN52" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AO52" t="n">
         <v>200</v>
       </c>
       <c r="AP52" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ52" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AR52" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT52" t="n">
         <v>10</v>
@@ -13683,10 +13683,10 @@
         <v>12.5</v>
       </c>
       <c r="AV52" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AW52" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AX52" t="n">
         <v>8.6</v>
@@ -13695,10 +13695,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ52" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BA52" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB52" t="n">
         <v>9.800000000000001</v>
@@ -13707,80 +13707,80 @@
         <v>11.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BE52" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF52" t="n">
         <v>3.35</v>
       </c>
       <c r="BG52" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH52" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BI52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BJ52" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BK52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL52" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="BM52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN52" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BO52" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BP52" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ52" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BR52" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BS52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT52" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BU52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV52" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BW52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX52" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BY52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ52" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="CA52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB57"/>
+  <dimension ref="A1:CB60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,7 +884,7 @@
         <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
         <v>1.58</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -1371,13 +1371,13 @@
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1395,10 +1395,10 @@
         <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.17</v>
@@ -1924,7 +1924,7 @@
         <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
         <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
         <v>1.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -2916,19 +2916,19 @@
         <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2937,10 +2937,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v>2.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R12" t="n">
         <v>1.58</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kazakhstan Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FC Zhetysu</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.94</v>
+        <v>1.92</v>
       </c>
       <c r="G13" t="n">
-        <v>590</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>1.37</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.32</v>
+        <v>1.78</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP13" t="n">
         <v>14</v>
       </c>
-      <c r="Z13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AQ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT13" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>220</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>170</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>250</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>520</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>370</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AU13" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>16.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
         <v>13</v>
       </c>
       <c r="BA13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>120</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BR13" t="n">
         <v>29</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BS13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV13" t="n">
         <v>38</v>
       </c>
-      <c r="BC13" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,239 +3896,239 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>FC Zhetysu</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.92</v>
+        <v>2.94</v>
       </c>
       <c r="G14" t="n">
-        <v>1.99</v>
+        <v>590</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>2.26</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>2.62</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S14" t="n">
         <v>1.05</v>
       </c>
-      <c r="N14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.92</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD14" t="n">
         <v>18</v>
       </c>
-      <c r="Z14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>20</v>
-      </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="AK14" t="n">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="AM14" t="n">
-        <v>95</v>
+        <v>450</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>270</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AP14" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.6</v>
+        <v>19.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>5.3</v>
+        <v>29</v>
       </c>
       <c r="BB14" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="BC14" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.1</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
         <v>1.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>1.76</v>
       </c>
       <c r="G16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H16" t="n">
         <v>5.2</v>
@@ -4452,7 +4452,7 @@
         <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
         <v>1.91</v>
@@ -4479,7 +4479,7 @@
         <v>170</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC16" t="n">
         <v>10</v>
@@ -4527,10 +4527,10 @@
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
         <v>7.4</v>
@@ -4542,19 +4542,19 @@
         <v>17.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
         <v>9.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB16" t="n">
         <v>15.5</v>
@@ -4563,16 +4563,16 @@
         <v>17</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF16" t="n">
         <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="n">
         <v>3.75</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -4673,13 +4673,13 @@
         <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.59</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -4691,13 +4691,13 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="O17" t="n">
         <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="Q17" t="n">
         <v>2.06</v>
@@ -4718,7 +4718,7 @@
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="G18" t="n">
         <v>1000</v>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -5420,22 +5420,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IF Karlstad</t>
+          <t>FC Jarfalla</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gefle</t>
+          <t>FC Arlanda</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
         <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
@@ -5453,22 +5453,22 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O20" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="P20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T20" t="n">
         <v>1.11</v>
@@ -5477,10 +5477,10 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,127 +5674,127 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kristianstads</t>
+          <t>SER Caxias do Sul</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N21" t="n">
-        <v>1.26</v>
+        <v>2.52</v>
       </c>
       <c r="O21" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.18</v>
+        <v>2.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>1.18</v>
+        <v>5.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.89</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR21" t="n">
         <v>1.01</v>
@@ -5803,10 +5803,10 @@
         <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV21" t="n">
         <v>1.01</v>
@@ -5815,10 +5815,10 @@
         <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
         <v>1.01</v>
@@ -5845,75 +5845,75 @@
         <v>1.01</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR21" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX21" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BZ21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,28 +5928,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eskilsminne</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="K22" t="n">
         <v>1000</v>
@@ -5961,22 +5961,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P22" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T22" t="n">
         <v>1.11</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,175 +6182,175 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IFK Stocksund</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sollentuna FF</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.11</v>
+        <v>3.45</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H23" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.12</v>
+        <v>2.02</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>1.13</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6436,175 +6436,175 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Leiknir R</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IF Vestri</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>1.82</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.15</v>
+        <v>1.79</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>1.15</v>
+        <v>2.96</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FC Jarfalla</t>
+          <t>Volsungur</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Arlanda</t>
+          <t>Njardvik</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -6726,19 +6726,19 @@
         <v>1.33</v>
       </c>
       <c r="O25" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="R25" t="n">
         <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6944,175 +6944,175 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Leiknir R</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>IF Vestri</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>1.83</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>1.34</v>
       </c>
       <c r="O26" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.79</v>
+        <v>1.15</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>2.96</v>
+        <v>1.15</v>
       </c>
       <c r="T26" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7198,175 +7198,175 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>IFK Stocksund</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Sollentuna FF</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.45</v>
+        <v>1.11</v>
       </c>
       <c r="G27" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="I27" t="n">
-        <v>2.38</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>1.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="P27" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.02</v>
+        <v>1.12</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>1.13</v>
       </c>
       <c r="T27" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7452,28 +7452,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>Eskilsminne</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="G28" t="n">
         <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -7485,22 +7485,22 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P28" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="T28" t="n">
         <v>1.11</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7706,127 +7706,127 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>IF Karlstad</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SER Caxias do Sul</t>
+          <t>Gefle</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="G29" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6</v>
+        <v>1.11</v>
       </c>
       <c r="I29" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="K29" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>1.35</v>
       </c>
       <c r="O29" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="P29" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.66</v>
+        <v>1.18</v>
       </c>
       <c r="R29" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="S29" t="n">
-        <v>5.5</v>
+        <v>1.19</v>
       </c>
       <c r="T29" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.68</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.23</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.87</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
         <v>1.01</v>
@@ -7835,10 +7835,10 @@
         <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
         <v>1.01</v>
@@ -7847,10 +7847,10 @@
         <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
         <v>1.01</v>
@@ -7877,75 +7877,75 @@
         <v>1.01</v>
       </c>
       <c r="BH29" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="BI29" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BJ29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BN29" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP29" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR29" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT29" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV29" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX29" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ29" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,22 +7960,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Volsungur</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Njardvik</t>
+          <t>Kristianstads</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
@@ -7993,22 +7993,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O30" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="R30" t="n">
         <v>1.24</v>
       </c>
       <c r="S30" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="T30" t="n">
         <v>1.11</v>
@@ -8017,10 +8017,10 @@
         <v>1.11</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,239 +8468,239 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Uruguay Montevideo FC</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="G32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X32" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>100</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO32" t="n">
         <v>3.35</v>
       </c>
-      <c r="H32" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO32" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP32" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR32" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BT32" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BV32" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BX32" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -8722,175 +8722,175 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.95</v>
+        <v>2.36</v>
       </c>
       <c r="G33" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="H33" t="n">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>2.14</v>
+        <v>3.35</v>
       </c>
       <c r="J33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O33" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P33" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="U33" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="W33" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="X33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF33" t="n">
         <v>17</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AG33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ33" t="n">
         <v>11</v>
       </c>
-      <c r="Z33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC33" t="n">
+      <c r="AR33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY33" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AZ33" t="n">
         <v>13</v>
       </c>
-      <c r="AE33" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>16</v>
-      </c>
       <c r="BA33" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BD33" t="n">
         <v>4.7</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>11.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH33" t="n">
         <v>1000</v>
@@ -8954,14 +8954,14 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8976,246 +8976,246 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="G34" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="H34" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="I34" t="n">
         <v>2.14</v>
       </c>
       <c r="J34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N34" t="n">
         <v>3.6</v>
       </c>
-      <c r="K34" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O34" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="P34" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="R34" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="U34" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="V34" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W34" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X34" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Y34" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Z34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG34" t="n">
         <v>17</v>
       </c>
-      <c r="AA34" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AH34" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="AI34" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AJ34" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AK34" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL34" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM34" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AN34" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AO34" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH34" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI34" t="n">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="BJ34" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK34" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL34" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM34" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN34" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BO34" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BP34" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ34" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR34" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS34" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT34" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BU34" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV34" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW34" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BX34" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ34" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA34" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9230,175 +9230,175 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Uruguay Montevideo FC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="G35" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="J35" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="K35" t="n">
-        <v>3.75</v>
+        <v>5.9</v>
       </c>
       <c r="L35" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="M35" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>3.85</v>
+        <v>2.14</v>
       </c>
       <c r="O35" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P35" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.9</v>
+        <v>2.28</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="S35" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="T35" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="U35" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="V35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.42</v>
       </c>
-      <c r="W35" t="n">
-        <v>1.67</v>
-      </c>
       <c r="X35" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -9738,12 +9738,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Central Cordoba</t>
+          <t>CA Deportivo Paraguayo</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportivo Espanol</t>
+          <t>Justo Jose de Urquiza</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -9771,13 +9771,13 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O37" t="n">
         <v>1.01</v>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Q37" t="n">
         <v>1.01</v>
@@ -9786,7 +9786,7 @@
         <v>1.12</v>
       </c>
       <c r="S37" t="n">
-        <v>1.05</v>
+        <v>1.56</v>
       </c>
       <c r="T37" t="n">
         <v>1.11</v>
@@ -9963,21 +9963,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9992,55 +9992,55 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Leandro N Alem</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Victoriano Arenas</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="G38" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H38" t="n">
-        <v>1.02</v>
+        <v>2.8</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="K38" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M38" t="n">
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
+        <v>3</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R38" t="n">
         <v>1.25</v>
       </c>
-      <c r="O38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S38" t="n">
-        <v>1.05</v>
+        <v>2.88</v>
       </c>
       <c r="T38" t="n">
         <v>1.11</v>
@@ -10049,10 +10049,10 @@
         <v>1.11</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -10246,12 +10246,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CA Deportivo Paraguayo</t>
+          <t>Central Cordoba</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Justo Jose de Urquiza</t>
+          <t>Deportivo Espanol</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -10279,13 +10279,13 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P39" t="n">
         <v>1.24</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.23</v>
       </c>
       <c r="Q39" t="n">
         <v>1.01</v>
@@ -10294,7 +10294,7 @@
         <v>1.12</v>
       </c>
       <c r="S39" t="n">
-        <v>1.56</v>
+        <v>1.05</v>
       </c>
       <c r="T39" t="n">
         <v>1.11</v>
@@ -10471,21 +10471,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ39" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10500,55 +10500,55 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Leandro N Alem</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Victoriano Arenas</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.44</v>
+        <v>1.02</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>2.8</v>
+        <v>1.02</v>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="J40" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="K40" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M40" t="n">
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="O40" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P40" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="S40" t="n">
-        <v>2.88</v>
+        <v>1.05</v>
       </c>
       <c r="T40" t="n">
         <v>1.11</v>
@@ -10557,10 +10557,10 @@
         <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -10732,14 +10732,14 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10754,55 +10754,55 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Club Indep Petrolero</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Centro Atletico Fenix</t>
+          <t>Real Potosi</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="G41" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="H41" t="n">
-        <v>2.54</v>
+        <v>1.09</v>
       </c>
       <c r="I41" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="J41" t="n">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
       <c r="K41" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M41" t="n">
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.16</v>
+        <v>1.26</v>
       </c>
       <c r="O41" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="P41" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.36</v>
+        <v>1.17</v>
       </c>
       <c r="R41" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>2.6</v>
+        <v>1.18</v>
       </c>
       <c r="T41" t="n">
         <v>1.11</v>
@@ -10811,10 +10811,10 @@
         <v>1.11</v>
       </c>
       <c r="V41" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -10979,21 +10979,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ41" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11008,175 +11008,175 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Everton De Vina</t>
+          <t>Amazonas FC</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Anapolis GO</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.76</v>
+        <v>1.54</v>
       </c>
       <c r="G42" t="n">
-        <v>2.94</v>
+        <v>1.97</v>
       </c>
       <c r="H42" t="n">
-        <v>2.74</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="J42" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="L42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R42" t="n">
         <v>1.17</v>
       </c>
-      <c r="M42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.31</v>
-      </c>
       <c r="S42" t="n">
-        <v>3.8</v>
+        <v>2.58</v>
       </c>
       <c r="T42" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U42" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="X42" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y42" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z42" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA42" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD42" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE42" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL42" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM42" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO42" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR42" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT42" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU42" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV42" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW42" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AX42" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY42" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BA42" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BB42" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BC42" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF42" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG42" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH42" t="n">
         <v>1000</v>
@@ -11240,14 +11240,14 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11262,175 +11262,175 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Club Indep Petrolero</t>
+          <t>Everton De Vina</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Potosi</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="G43" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="H43" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="J43" t="n">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M43" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>1.26</v>
+        <v>3.35</v>
       </c>
       <c r="O43" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="P43" t="n">
-        <v>1.26</v>
+        <v>1.81</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.17</v>
+        <v>2.06</v>
       </c>
       <c r="R43" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S43" t="n">
-        <v>1.18</v>
+        <v>3.8</v>
       </c>
       <c r="T43" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U43" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W43" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB43" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF43" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG43" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11487,21 +11487,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ43" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -11516,31 +11516,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Amazonas FC</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Anapolis GO</t>
+          <t>Centro Atletico Fenix</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.54</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>1.95</v>
+        <v>3.55</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>2.54</v>
       </c>
       <c r="I44" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="K44" t="n">
-        <v>6.8</v>
+        <v>3.35</v>
       </c>
       <c r="L44" t="n">
         <v>1.44</v>
@@ -11549,22 +11549,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O44" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="P44" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="R44" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S44" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T44" t="n">
         <v>1.11</v>
@@ -11573,10 +11573,10 @@
         <v>1.11</v>
       </c>
       <c r="V44" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="W44" t="n">
-        <v>2.04</v>
+        <v>1.39</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -11770,22 +11770,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Argentino de Quilmes</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Argentino de Merlo</t>
+          <t>Deportivo Armenio</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G45" t="n">
         <v>1000</v>
       </c>
       <c r="H45" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I45" t="n">
         <v>1000</v>
@@ -11812,7 +11812,7 @@
         <v>1.24</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R45" t="n">
         <v>1.12</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -12024,22 +12024,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sportivo Italiano</t>
+          <t>Flandria</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Excursionistas</t>
+          <t>CA Ituzaingo</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G46" t="n">
         <v>1000</v>
       </c>
       <c r="H46" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I46" t="n">
         <v>1000</v>
@@ -12066,13 +12066,13 @@
         <v>1.24</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R46" t="n">
         <v>1.12</v>
       </c>
       <c r="S46" t="n">
-        <v>1.59</v>
+        <v>1.05</v>
       </c>
       <c r="T46" t="n">
         <v>1.11</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -12278,12 +12278,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CS Dock Sud</t>
+          <t>CSD Liniers de Ciudad Evita</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Talleres (RE)</t>
+          <t>Real Pilar FC</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -12532,22 +12532,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>San Martin de Burzaco</t>
+          <t>Comunicaciones B Aires</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Villa Dalmine</t>
+          <t>Deportivo Laferrere</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G48" t="n">
         <v>1000</v>
       </c>
       <c r="H48" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
@@ -12565,13 +12565,13 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="O48" t="n">
         <v>1.01</v>
       </c>
       <c r="P48" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q48" t="n">
         <v>1.02</v>
@@ -12580,7 +12580,7 @@
         <v>1.12</v>
       </c>
       <c r="S48" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="T48" t="n">
         <v>1.11</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -12786,12 +12786,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Villa San Carlos</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brown de Adrogue</t>
+          <t>UAI Urquiza</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -12807,7 +12807,7 @@
         <v>1000</v>
       </c>
       <c r="J49" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K49" t="n">
         <v>1000</v>
@@ -12828,13 +12828,13 @@
         <v>1.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R49" t="n">
         <v>1.12</v>
       </c>
       <c r="S49" t="n">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="T49" t="n">
         <v>1.11</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -13040,22 +13040,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Camioneros</t>
+          <t>Sportivo Italiano</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandi</t>
+          <t>Excursionistas</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G50" t="n">
         <v>1000</v>
       </c>
       <c r="H50" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I50" t="n">
         <v>1000</v>
@@ -13073,7 +13073,7 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O50" t="n">
         <v>1.01</v>
@@ -13088,7 +13088,7 @@
         <v>1.12</v>
       </c>
       <c r="S50" t="n">
-        <v>1.05</v>
+        <v>1.59</v>
       </c>
       <c r="T50" t="n">
         <v>1.11</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Villa San Carlos</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>UAI Urquiza</t>
+          <t>Brown de Adrogue</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -13315,7 +13315,7 @@
         <v>1000</v>
       </c>
       <c r="J51" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K51" t="n">
         <v>1000</v>
@@ -13336,13 +13336,13 @@
         <v>1.24</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R51" t="n">
         <v>1.12</v>
       </c>
       <c r="S51" t="n">
-        <v>1.58</v>
+        <v>1.05</v>
       </c>
       <c r="T51" t="n">
         <v>1.11</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Argentino de Quilmes</t>
+          <t>San Martin de Burzaco</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Armenio</t>
+          <t>Villa Dalmine</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -13563,7 +13563,7 @@
         <v>1000</v>
       </c>
       <c r="H52" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I52" t="n">
         <v>1000</v>
@@ -13590,13 +13590,13 @@
         <v>1.24</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R52" t="n">
         <v>1.12</v>
       </c>
       <c r="S52" t="n">
-        <v>1.05</v>
+        <v>1.64</v>
       </c>
       <c r="T52" t="n">
         <v>1.11</v>
@@ -13608,7 +13608,7 @@
         <v>1.02</v>
       </c>
       <c r="W52" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -13802,22 +13802,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Comunicaciones B Aires</t>
+          <t>CS Dock Sud</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Laferrere</t>
+          <t>Talleres (RE)</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G53" t="n">
         <v>1000</v>
       </c>
       <c r="H53" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I53" t="n">
         <v>1000</v>
@@ -13835,22 +13835,22 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O53" t="n">
         <v>1.01</v>
       </c>
       <c r="P53" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R53" t="n">
         <v>1.12</v>
       </c>
       <c r="S53" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="T53" t="n">
         <v>1.11</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -14056,16 +14056,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CSD Liniers de Ciudad Evita</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Pilar FC</t>
+          <t>Argentino de Merlo</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G54" t="n">
         <v>1000</v>
@@ -14077,7 +14077,7 @@
         <v>1000</v>
       </c>
       <c r="J54" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K54" t="n">
         <v>1000</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -14310,16 +14310,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Flandria</t>
+          <t>Camioneros</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CA Ituzaingo</t>
+          <t>Arsenal de Sarandi</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G55" t="n">
         <v>1000</v>
@@ -14343,7 +14343,7 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O55" t="n">
         <v>1.01</v>
@@ -14352,7 +14352,7 @@
         <v>1.24</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R55" t="n">
         <v>1.12</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -14678,7 +14678,7 @@
         <v>4.8</v>
       </c>
       <c r="AO56" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP56" t="n">
         <v>4.7</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,769 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Nublense</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S58" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV58" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW58" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX58" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY58" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB58" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB58" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:53:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Phoenix Rising FC</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N59" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ59" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB59" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:53:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Orange County Blues</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X60" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF60" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ60" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB60" t="inlineStr">
+        <is>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O2" t="n">
         <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
         <v>1.91</v>
       </c>
       <c r="U2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -923,10 +923,10 @@
         <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
@@ -938,7 +938,7 @@
         <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>24</v>
@@ -953,7 +953,7 @@
         <v>28</v>
       </c>
       <c r="AL2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
@@ -965,64 +965,64 @@
         <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1037,10 +1037,10 @@
         <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -1219,58 +1219,58 @@
         <v>400</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -1476,22 +1476,22 @@
         <v>3.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AS4" t="n">
         <v>4.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW4" t="n">
         <v>4.5</v>
@@ -1503,7 +1503,7 @@
         <v>4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA4" t="n">
         <v>4.7</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -1619,73 +1619,73 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="G5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.38</v>
       </c>
-      <c r="H5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.86</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="X5" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC5" t="n">
         <v>11</v>
@@ -1694,7 +1694,7 @@
         <v>17.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
         <v>19.5</v>
@@ -1703,55 +1703,55 @@
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AJ5" t="n">
         <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AN5" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
         <v>18</v>
       </c>
       <c r="AS5" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY5" t="n">
         <v>9.800000000000001</v>
@@ -1760,7 +1760,7 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
         <v>21</v>
@@ -1769,80 +1769,80 @@
         <v>16</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.88</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.64</v>
+        <v>5.5</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.88</v>
+        <v>12</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.74</v>
+        <v>7.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.79</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
         <v>9.6</v>
       </c>
-      <c r="BU5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>46</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BZ5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.77</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.52</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G7" t="n">
         <v>4.2</v>
@@ -2139,7 +2139,7 @@
         <v>2.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="K7" t="n">
         <v>3.15</v>
@@ -2151,7 +2151,7 @@
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="O7" t="n">
         <v>1.59</v>
@@ -2160,25 +2160,25 @@
         <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
         <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
         <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X7" t="n">
         <v>8.800000000000001</v>
@@ -2250,7 +2250,7 @@
         <v>3.55</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AV7" t="n">
         <v>3.9</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -2381,25 +2381,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G8" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
@@ -2429,10 +2429,10 @@
         <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X8" t="n">
         <v>12.5</v>
@@ -2495,7 +2495,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS8" t="n">
         <v>5.3</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -2659,28 +2659,28 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
         <v>1.08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
         <v>7.6</v>
@@ -2689,7 +2689,7 @@
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Y9" t="n">
         <v>19</v>
@@ -2707,19 +2707,19 @@
         <v>32</v>
       </c>
       <c r="AD9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>15.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AG9" t="n">
         <v>120</v>
       </c>
       <c r="AH9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI9" t="n">
         <v>46</v>
@@ -2740,22 +2740,22 @@
         <v>500</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS9" t="n">
         <v>5.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
         <v>9.199999999999999</v>
@@ -2764,40 +2764,40 @@
         <v>6.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY9" t="n">
         <v>10</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BA9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD9" t="n">
         <v>10.5</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BE9" t="n">
         <v>10.5</v>
       </c>
-      <c r="BD9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>10</v>
-      </c>
       <c r="BF9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG9" t="n">
         <v>2.04</v>
       </c>
       <c r="BH9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BI9" t="n">
         <v>4.6</v>
@@ -2806,7 +2806,7 @@
         <v>15</v>
       </c>
       <c r="BK9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2815,10 +2815,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BO9" t="n">
-        <v>9</v>
+        <v>2.92</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
@@ -2833,7 +2833,7 @@
         <v>3.15</v>
       </c>
       <c r="BT9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BU9" t="n">
         <v>3.25</v>
@@ -2842,23 +2842,23 @@
         <v>5.6</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BX9" t="n">
         <v>19.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="G10" t="n">
         <v>1.67</v>
@@ -2925,13 +2925,13 @@
         <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
         <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
         <v>1.81</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>1.72</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
         <v>6.8</v>
@@ -3158,7 +3158,7 @@
         <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -3233,7 +3233,7 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AK11" t="n">
         <v>970</v>
@@ -3245,64 +3245,64 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="BC11" t="n">
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -3403,16 +3403,16 @@
         <v>5.8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="I12" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.4</v>
@@ -3430,22 +3430,22 @@
         <v>1.86</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.94</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.96</v>
-      </c>
       <c r="V12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="W12" t="n">
         <v>1.21</v>
@@ -3454,7 +3454,7 @@
         <v>16</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z12" t="n">
         <v>13</v>
@@ -3463,13 +3463,13 @@
         <v>24</v>
       </c>
       <c r="AB12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE12" t="n">
         <v>24</v>
@@ -3478,13 +3478,13 @@
         <v>46</v>
       </c>
       <c r="AG12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
         <v>150</v>
@@ -3502,61 +3502,61 @@
         <v>100</v>
       </c>
       <c r="AO12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AT12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW12" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="AY12" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH12" t="n">
         <v>3.45</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -3693,10 +3693,10 @@
         <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
@@ -3765,10 +3765,10 @@
         <v>7.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
@@ -3777,40 +3777,40 @@
         <v>5.7</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH13" t="n">
         <v>2.9</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G14" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="I14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
         <v>4.4</v>
@@ -3929,34 +3929,34 @@
         <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P14" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="Q14" t="n">
         <v>1.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="U14" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V14" t="n">
         <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
         <v>32</v>
@@ -3971,10 +3971,10 @@
         <v>60</v>
       </c>
       <c r="AB14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD14" t="n">
         <v>17</v>
@@ -3989,16 +3989,16 @@
         <v>14.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ14" t="n">
         <v>38</v>
       </c>
       <c r="AK14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL14" t="n">
         <v>34</v>
@@ -4007,13 +4007,13 @@
         <v>65</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO14" t="n">
         <v>21</v>
       </c>
       <c r="AP14" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>13</v>
@@ -4022,16 +4022,16 @@
         <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AT14" t="n">
         <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="AW14" t="n">
         <v>20</v>
@@ -4046,19 +4046,19 @@
         <v>10.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>15.5</v>
+        <v>3.9</v>
       </c>
       <c r="BD14" t="n">
         <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BF14" t="n">
         <v>8.6</v>
@@ -4067,10 +4067,10 @@
         <v>12.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ14" t="n">
         <v>8.800000000000001</v>
@@ -4082,10 +4082,10 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO14" t="n">
         <v>4.4</v>
@@ -4100,7 +4100,7 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT14" t="n">
         <v>7</v>
@@ -4112,13 +4112,13 @@
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -4159,166 +4159,166 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J15" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
         <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
-        <v>1.06</v>
+        <v>1.43</v>
       </c>
       <c r="P15" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -4416,13 +4416,13 @@
         <v>2.26</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H16" t="n">
         <v>3.3</v>
       </c>
       <c r="I16" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="n">
         <v>2.86</v>
@@ -4437,7 +4437,7 @@
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="O16" t="n">
         <v>1.49</v>
@@ -4452,7 +4452,7 @@
         <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
@@ -4527,16 +4527,16 @@
         <v>3.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AS16" t="n">
         <v>4.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AV16" t="n">
         <v>3.55</v>
@@ -4551,7 +4551,7 @@
         <v>3.35</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BA16" t="n">
         <v>4.1</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
         <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.76</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.11</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -4921,230 +4921,230 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="G18" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="H18" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="I18" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O18" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="P18" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV18" t="n">
         <v>1000</v>
       </c>
       <c r="BW18" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -5175,40 +5175,40 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="G19" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J19" t="n">
         <v>3.05</v>
       </c>
-      <c r="I19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.78</v>
-      </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
@@ -5223,10 +5223,10 @@
         <v>1.11</v>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -5432,19 +5432,19 @@
         <v>4.7</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="H20" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="I20" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="J20" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.41</v>
@@ -5477,10 +5477,10 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -5683,175 +5683,175 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="G21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H21" t="n">
         <v>2.04</v>
       </c>
       <c r="I21" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J21" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
         <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V21" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH21" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK21" t="n">
         <v>1.01</v>
@@ -5863,7 +5863,7 @@
         <v>1.01</v>
       </c>
       <c r="BN21" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO21" t="n">
         <v>1.01</v>
@@ -5881,13 +5881,13 @@
         <v>1.01</v>
       </c>
       <c r="BT21" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU21" t="n">
         <v>1.01</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW21" t="n">
         <v>1.01</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>1.8</v>
       </c>
       <c r="H22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I22" t="n">
         <v>5.7</v>
@@ -5961,16 +5961,16 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
         <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R22" t="n">
         <v>1.34</v>
@@ -5988,7 +5988,7 @@
         <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X22" t="n">
         <v>16</v>
@@ -6024,10 +6024,10 @@
         <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK22" t="n">
         <v>23</v>
@@ -6051,7 +6051,7 @@
         <v>15.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS22" t="n">
         <v>8.4</v>
@@ -6090,7 +6090,7 @@
         <v>7.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF22" t="n">
         <v>10.5</v>
@@ -6108,7 +6108,7 @@
         <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6126,7 +6126,7 @@
         <v>12</v>
       </c>
       <c r="BQ22" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
@@ -6138,7 +6138,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU22" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
@@ -6147,7 +6147,7 @@
         <v>12.5</v>
       </c>
       <c r="BX22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
         <v>13</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G23" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
         <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.34</v>
@@ -6215,22 +6215,22 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P23" t="n">
         <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R23" t="n">
         <v>1.45</v>
       </c>
       <c r="S23" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
         <v>1.76</v>
@@ -6239,10 +6239,10 @@
         <v>2.22</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X23" t="n">
         <v>21</v>
@@ -6281,7 +6281,7 @@
         <v>60</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
@@ -6305,10 +6305,10 @@
         <v>14.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT23" t="n">
         <v>9.199999999999999</v>
@@ -6320,7 +6320,7 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
@@ -6332,7 +6332,7 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
@@ -6341,19 +6341,19 @@
         <v>15</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF23" t="n">
         <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI23" t="n">
         <v>3.1</v>
@@ -6362,7 +6362,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
@@ -6371,7 +6371,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO23" t="n">
         <v>3.8</v>
@@ -6380,7 +6380,7 @@
         <v>13.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="BR23" t="n">
         <v>26</v>
@@ -6404,7 +6404,7 @@
         <v>42</v>
       </c>
       <c r="BY23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ23" t="n">
         <v>21</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
         <v>1.46</v>
       </c>
       <c r="X24" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y24" t="n">
         <v>970</v>
@@ -6553,10 +6553,10 @@
         <v>30</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR24" t="n">
         <v>14</v>
@@ -6565,10 +6565,10 @@
         <v>32</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV24" t="n">
         <v>9.4</v>
@@ -6577,19 +6577,19 @@
         <v>25</v>
       </c>
       <c r="AX24" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY24" t="n">
         <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
         <v>36</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC24" t="n">
         <v>32</v>
@@ -6598,10 +6598,10 @@
         <v>42</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG24" t="n">
         <v>19.5</v>
@@ -6622,7 +6622,7 @@
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.82</v>
+        <v>4.4</v>
       </c>
       <c r="BN24" t="n">
         <v>6.4</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
         <v>5.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M25" t="n">
         <v>1.02</v>
@@ -6741,10 +6741,10 @@
         <v>1.88</v>
       </c>
       <c r="T25" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U25" t="n">
-        <v>1.11</v>
+        <v>2.78</v>
       </c>
       <c r="V25" t="n">
         <v>2.28</v>
@@ -6861,68 +6861,68 @@
         <v>4.2</v>
       </c>
       <c r="BH25" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BJ25" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN25" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR25" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX25" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="G26" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6983,7 +6983,7 @@
         <v>1.16</v>
       </c>
       <c r="P26" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q26" t="n">
         <v>1.51</v>
@@ -7001,10 +7001,10 @@
         <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W26" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -7461,163 +7461,163 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G28" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="H28" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="I28" t="n">
-        <v>990</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W28" t="n">
         <v>2.56</v>
       </c>
-      <c r="K28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.46</v>
-      </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
         <v>1.03</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
         <v>1.03</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -7727,13 +7727,13 @@
         <v>16.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
         <v>7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
@@ -7766,7 +7766,7 @@
         <v>1.07</v>
       </c>
       <c r="W29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X29" t="n">
         <v>970</v>
@@ -7781,7 +7781,7 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AC29" t="n">
         <v>970</v>
@@ -7823,7 +7823,7 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AQ29" t="n">
         <v>4.2</v>
@@ -7838,7 +7838,7 @@
         <v>5.1</v>
       </c>
       <c r="AU29" t="n">
-        <v>9.4</v>
+        <v>3.6</v>
       </c>
       <c r="AV29" t="n">
         <v>4.4</v>
@@ -7850,7 +7850,7 @@
         <v>5.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="AZ29" t="n">
         <v>4.4</v>
@@ -7859,7 +7859,7 @@
         <v>4.7</v>
       </c>
       <c r="BB29" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BC29" t="n">
         <v>3.9</v>
@@ -7877,16 +7877,16 @@
         <v>4.8</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ29" t="n">
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
@@ -7895,16 +7895,16 @@
         <v>1.04</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BP29" t="n">
         <v>1000</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR29" t="n">
         <v>1000</v>
@@ -7916,7 +7916,7 @@
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
@@ -7934,11 +7934,11 @@
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
         <v>4.1</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AQ30" t="n">
         <v>8.4</v>
@@ -8089,7 +8089,7 @@
         <v>7.2</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU30" t="n">
         <v>13.5</v>
@@ -8107,7 +8107,7 @@
         <v>5.2</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BA30" t="n">
         <v>5</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="G31" t="n">
         <v>3.8</v>
@@ -8235,34 +8235,34 @@
         <v>2.46</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P31" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
         <v>1.68</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S31" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T31" t="n">
         <v>1.11</v>
@@ -8274,7 +8274,7 @@
         <v>1.68</v>
       </c>
       <c r="W31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -8477,43 +8477,43 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H32" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J32" t="n">
         <v>4</v>
       </c>
       <c r="K32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N32" t="n">
         <v>4.8</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N32" t="n">
-        <v>4.7</v>
       </c>
       <c r="O32" t="n">
         <v>1.21</v>
       </c>
       <c r="P32" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R32" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S32" t="n">
         <v>2.52</v>
@@ -8525,10 +8525,10 @@
         <v>2.34</v>
       </c>
       <c r="V32" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X32" t="n">
         <v>26</v>
@@ -8537,10 +8537,10 @@
         <v>22</v>
       </c>
       <c r="Z32" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AA32" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB32" t="n">
         <v>13.5</v>
@@ -8552,7 +8552,7 @@
         <v>18.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF32" t="n">
         <v>16</v>
@@ -8567,7 +8567,7 @@
         <v>48</v>
       </c>
       <c r="AJ32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK32" t="n">
         <v>21</v>
@@ -8579,10 +8579,10 @@
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AP32" t="n">
         <v>16.5</v>
@@ -8600,7 +8600,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV32" t="n">
         <v>12</v>
@@ -8633,74 +8633,74 @@
         <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BG32" t="n">
         <v>1.01</v>
       </c>
       <c r="BH32" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ32" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK32" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BN32" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO32" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP32" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR32" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS32" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT32" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU32" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV32" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ32" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -8740,31 +8740,31 @@
         <v>3.7</v>
       </c>
       <c r="I33" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K33" t="n">
         <v>4.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N33" t="n">
         <v>4.7</v>
       </c>
       <c r="O33" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="R33" t="n">
         <v>1.51</v>
@@ -8779,7 +8779,7 @@
         <v>2.3</v>
       </c>
       <c r="V33" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W33" t="n">
         <v>1.94</v>
@@ -8788,7 +8788,7 @@
         <v>25</v>
       </c>
       <c r="Y33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z33" t="n">
         <v>38</v>
@@ -8842,119 +8842,119 @@
         <v>16.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT33" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV33" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX33" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY33" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ33" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC33" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BD33" t="n">
         <v>21</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY33" t="n">
         <v>7.8</v>
       </c>
-      <c r="BG33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BZ33" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -8985,22 +8985,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H34" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I34" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="J34" t="n">
         <v>4.1</v>
       </c>
       <c r="K34" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L34" t="n">
         <v>1.32</v>
@@ -9015,16 +9015,16 @@
         <v>1.23</v>
       </c>
       <c r="P34" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R34" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T34" t="n">
         <v>1.65</v>
@@ -9033,7 +9033,7 @@
         <v>2.26</v>
       </c>
       <c r="V34" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="W34" t="n">
         <v>1.3</v>
@@ -9063,7 +9063,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG34" t="n">
         <v>970</v>
@@ -9090,7 +9090,7 @@
         <v>42</v>
       </c>
       <c r="AO34" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AP34" t="n">
         <v>14.5</v>
@@ -9198,7 +9198,7 @@
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H35" t="n">
         <v>6.2</v>
@@ -9275,10 +9275,10 @@
         <v>1.67</v>
       </c>
       <c r="R35" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S35" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T35" t="n">
         <v>1.77</v>
@@ -9290,7 +9290,7 @@
         <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X35" t="n">
         <v>26</v>
@@ -9353,10 +9353,10 @@
         <v>18</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT35" t="n">
         <v>7.2</v>
@@ -9368,7 +9368,7 @@
         <v>18</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX35" t="n">
         <v>7.6</v>
@@ -9380,7 +9380,7 @@
         <v>15</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB35" t="n">
         <v>10.5</v>
@@ -9389,16 +9389,16 @@
         <v>11.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH35" t="n">
         <v>1000</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
         <v>1.43</v>
       </c>
       <c r="R37" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S37" t="n">
         <v>2.14</v>
@@ -9873,7 +9873,7 @@
         <v>8</v>
       </c>
       <c r="AV37" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AW37" t="n">
         <v>14.5</v>
@@ -9885,7 +9885,7 @@
         <v>10</v>
       </c>
       <c r="AZ37" t="n">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA37" t="n">
         <v>17.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -10007,7 +10007,7 @@
         <v>5.3</v>
       </c>
       <c r="H38" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I38" t="n">
         <v>1.83</v>
@@ -10016,10 +10016,10 @@
         <v>3.95</v>
       </c>
       <c r="K38" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L38" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
@@ -10028,25 +10028,25 @@
         <v>4.2</v>
       </c>
       <c r="O38" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R38" t="n">
         <v>1.45</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T38" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U38" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V38" t="n">
         <v>2.2</v>
@@ -10055,43 +10055,43 @@
         <v>1.23</v>
       </c>
       <c r="X38" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z38" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AA38" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AC38" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AF38" t="n">
         <v>55</v>
       </c>
       <c r="AG38" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AH38" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AI38" t="n">
         <v>46</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK38" t="n">
         <v>90</v>
@@ -10100,68 +10100,68 @@
         <v>85</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB38" t="n">
         <v>12.5</v>
       </c>
-      <c r="AP38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV38" t="n">
+      <c r="BC38" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG38" t="n">
         <v>8.6</v>
       </c>
-      <c r="AW38" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH38" t="n">
         <v>1000</v>
       </c>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -10255,22 +10255,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="G39" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H39" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I39" t="n">
         <v>2.24</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2.36</v>
       </c>
       <c r="J39" t="n">
         <v>3.4</v>
       </c>
       <c r="K39" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L39" t="n">
         <v>1.39</v>
@@ -10294,31 +10294,31 @@
         <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T39" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U39" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V39" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W39" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X39" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y39" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z39" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA39" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AB39" t="n">
         <v>13</v>
@@ -10327,67 +10327,67 @@
         <v>7.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE39" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF39" t="n">
         <v>26</v>
       </c>
-      <c r="AF39" t="n">
-        <v>25</v>
-      </c>
       <c r="AG39" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH39" t="n">
         <v>18</v>
       </c>
       <c r="AI39" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AJ39" t="n">
         <v>100</v>
       </c>
       <c r="AK39" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AL39" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM39" t="n">
         <v>140</v>
       </c>
       <c r="AN39" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP39" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR39" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT39" t="n">
         <v>11</v>
       </c>
       <c r="AU39" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV39" t="n">
         <v>10</v>
       </c>
       <c r="AW39" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AX39" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY39" t="n">
         <v>13.5</v>
@@ -10399,19 +10399,19 @@
         <v>32</v>
       </c>
       <c r="BB39" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD39" t="n">
         <v>32</v>
       </c>
-      <c r="BC39" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>30</v>
-      </c>
       <c r="BE39" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF39" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BG39" t="n">
         <v>18.5</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -10509,22 +10509,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G40" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="H40" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I40" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J40" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K40" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -10533,206 +10533,206 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>4.5</v>
+        <v>1.11</v>
       </c>
       <c r="O40" t="n">
         <v>1.2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R40" t="n">
         <v>1.53</v>
       </c>
       <c r="S40" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T40" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="U40" t="n">
-        <v>2.42</v>
+        <v>2.14</v>
       </c>
       <c r="V40" t="n">
         <v>1.35</v>
       </c>
       <c r="W40" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y40" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB40" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE40" t="n">
         <v>40</v>
       </c>
       <c r="AF40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK40" t="n">
         <v>21</v>
       </c>
-      <c r="AG40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL40" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH40" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI40" t="n">
-        <v>1.95</v>
+        <v>2.96</v>
       </c>
       <c r="BJ40" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK40" t="n">
-        <v>1.69</v>
+        <v>4.5</v>
       </c>
       <c r="BL40" t="n">
         <v>1000</v>
       </c>
       <c r="BM40" t="n">
-        <v>1.95</v>
+        <v>8</v>
       </c>
       <c r="BN40" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO40" t="n">
-        <v>1.55</v>
+        <v>3.55</v>
       </c>
       <c r="BP40" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BQ40" t="n">
-        <v>1.79</v>
+        <v>5.7</v>
       </c>
       <c r="BR40" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BS40" t="n">
-        <v>1.85</v>
+        <v>6.6</v>
       </c>
       <c r="BT40" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BU40" t="n">
-        <v>1.62</v>
+        <v>4.4</v>
       </c>
       <c r="BV40" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BW40" t="n">
-        <v>1.85</v>
+        <v>6.6</v>
       </c>
       <c r="BX40" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY40" t="n">
-        <v>1.87</v>
+        <v>7</v>
       </c>
       <c r="BZ40" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.81</v>
+        <v>6</v>
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -10763,13 +10763,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G41" t="n">
         <v>1.97</v>
       </c>
       <c r="H41" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I41" t="n">
         <v>5.6</v>
@@ -10778,7 +10778,7 @@
         <v>3.25</v>
       </c>
       <c r="K41" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L41" t="n">
         <v>1.53</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -11035,13 +11035,13 @@
         <v>5.6</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M42" t="n">
         <v>1.02</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="O42" t="n">
         <v>1.17</v>
@@ -11125,13 +11125,13 @@
         <v>6.4</v>
       </c>
       <c r="AP42" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AQ42" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR42" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS42" t="n">
         <v>10.5</v>
@@ -11146,7 +11146,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW42" t="n">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="AX42" t="n">
         <v>5.5</v>
@@ -11155,16 +11155,16 @@
         <v>16.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="BB42" t="n">
         <v>5</v>
       </c>
       <c r="BC42" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD42" t="n">
         <v>5.5</v>
@@ -11179,68 +11179,68 @@
         <v>4.1</v>
       </c>
       <c r="BH42" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI42" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
       </c>
       <c r="BK42" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL42" t="n">
         <v>1000</v>
       </c>
       <c r="BM42" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BN42" t="n">
         <v>1000</v>
       </c>
       <c r="BO42" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BP42" t="n">
         <v>1000</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BR42" t="n">
         <v>1000</v>
       </c>
       <c r="BS42" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BT42" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU42" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BV42" t="n">
         <v>1000</v>
       </c>
       <c r="BW42" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BX42" t="n">
         <v>1000</v>
       </c>
       <c r="BY42" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ42" t="n">
         <v>1000</v>
       </c>
       <c r="CA42" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
         <v>1000</v>
       </c>
       <c r="H43" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="I43" t="n">
         <v>1000</v>
@@ -11295,13 +11295,13 @@
         <v>1.07</v>
       </c>
       <c r="N43" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O43" t="n">
         <v>1.36</v>
       </c>
       <c r="P43" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q43" t="n">
         <v>1.94</v>
@@ -11313,10 +11313,10 @@
         <v>3.25</v>
       </c>
       <c r="T43" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U43" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V43" t="n">
         <v>1.11</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
         <v>1.48</v>
       </c>
       <c r="G44" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="H44" t="n">
         <v>6.8</v>
@@ -11540,7 +11540,7 @@
         <v>4.3</v>
       </c>
       <c r="K44" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L44" t="n">
         <v>1.27</v>
@@ -11549,19 +11549,19 @@
         <v>1.05</v>
       </c>
       <c r="N44" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O44" t="n">
         <v>1.24</v>
       </c>
       <c r="P44" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R44" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S44" t="n">
         <v>2.74</v>
@@ -11570,16 +11570,16 @@
         <v>1.85</v>
       </c>
       <c r="U44" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V44" t="n">
         <v>1.13</v>
       </c>
       <c r="W44" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="X44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y44" t="n">
         <v>32</v>
@@ -11615,94 +11615,94 @@
         <v>110</v>
       </c>
       <c r="AJ44" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK44" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL44" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM44" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN44" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AO44" t="n">
         <v>150</v>
       </c>
       <c r="AP44" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ44" t="n">
         <v>21</v>
       </c>
       <c r="AR44" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT44" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU44" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV44" t="n">
         <v>18</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX44" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY44" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
         <v>19</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BB44" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC44" t="n">
         <v>11.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF44" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG44" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH44" t="n">
         <v>4.1</v>
       </c>
       <c r="BI44" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ44" t="n">
         <v>11</v>
       </c>
       <c r="BK44" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL44" t="n">
         <v>1000</v>
       </c>
       <c r="BM44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN44" t="n">
         <v>4.2</v>
@@ -11711,10 +11711,10 @@
         <v>3.2</v>
       </c>
       <c r="BP44" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BQ44" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR44" t="n">
         <v>24</v>
@@ -11723,7 +11723,7 @@
         <v>7.6</v>
       </c>
       <c r="BT44" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU44" t="n">
         <v>5.6</v>
@@ -11732,13 +11732,13 @@
         <v>65</v>
       </c>
       <c r="BW44" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX44" t="n">
         <v>65</v>
       </c>
       <c r="BY44" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ44" t="n">
         <v>15.5</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -11779,10 +11779,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G45" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H45" t="n">
         <v>2.04</v>
@@ -11809,7 +11809,7 @@
         <v>1.34</v>
       </c>
       <c r="P45" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q45" t="n">
         <v>2.02</v>
@@ -11821,10 +11821,10 @@
         <v>3.6</v>
       </c>
       <c r="T45" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U45" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V45" t="n">
         <v>1.9</v>
@@ -11869,7 +11869,7 @@
         <v>100</v>
       </c>
       <c r="AJ45" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="n">
         <v>190</v>
@@ -11884,7 +11884,7 @@
         <v>60</v>
       </c>
       <c r="AO45" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP45" t="n">
         <v>12.5</v>
@@ -11923,7 +11923,7 @@
         <v>24</v>
       </c>
       <c r="BB45" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC45" t="n">
         <v>27</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -12039,16 +12039,16 @@
         <v>4.1</v>
       </c>
       <c r="H46" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I46" t="n">
         <v>2.1</v>
       </c>
       <c r="J46" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K46" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L46" t="n">
         <v>1.28</v>
@@ -12057,28 +12057,28 @@
         <v>1.04</v>
       </c>
       <c r="N46" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O46" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P46" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R46" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S46" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="T46" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U46" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V46" t="n">
         <v>1.9</v>
@@ -12087,10 +12087,10 @@
         <v>1.33</v>
       </c>
       <c r="X46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y46" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z46" t="n">
         <v>15</v>
@@ -12102,7 +12102,7 @@
         <v>21</v>
       </c>
       <c r="AC46" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD46" t="n">
         <v>12.5</v>
@@ -12117,7 +12117,7 @@
         <v>18.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI46" t="n">
         <v>34</v>
@@ -12126,7 +12126,7 @@
         <v>80</v>
       </c>
       <c r="AK46" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL46" t="n">
         <v>50</v>
@@ -12144,7 +12144,7 @@
         <v>16</v>
       </c>
       <c r="AQ46" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR46" t="n">
         <v>11</v>
@@ -12153,110 +12153,110 @@
         <v>20</v>
       </c>
       <c r="AT46" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU46" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AW46" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX46" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AY46" t="n">
         <v>12</v>
       </c>
       <c r="AZ46" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA46" t="n">
         <v>4.9</v>
       </c>
       <c r="BB46" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC46" t="n">
         <v>32</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE46" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF46" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG46" t="n">
         <v>9.4</v>
       </c>
       <c r="BH46" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI46" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BJ46" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK46" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL46" t="n">
         <v>1000</v>
       </c>
       <c r="BM46" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN46" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO46" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BP46" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ46" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BR46" t="n">
         <v>1000</v>
       </c>
       <c r="BS46" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT46" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU46" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV46" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW46" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX46" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY46" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ46" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA46" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -12287,34 +12287,34 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G47" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H47" t="n">
         <v>3.25</v>
       </c>
       <c r="I47" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>3.55</v>
       </c>
       <c r="K47" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L47" t="n">
         <v>1.13</v>
       </c>
       <c r="M47" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N47" t="n">
         <v>4</v>
       </c>
       <c r="O47" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P47" t="n">
         <v>2.02</v>
@@ -12326,19 +12326,19 @@
         <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T47" t="n">
         <v>1.71</v>
       </c>
       <c r="U47" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V47" t="n">
         <v>1.42</v>
       </c>
       <c r="W47" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X47" t="n">
         <v>17.5</v>
@@ -12356,7 +12356,7 @@
         <v>12.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD47" t="n">
         <v>16</v>
@@ -12365,13 +12365,13 @@
         <v>42</v>
       </c>
       <c r="AF47" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG47" t="n">
         <v>13</v>
       </c>
       <c r="AH47" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI47" t="n">
         <v>55</v>
@@ -12383,16 +12383,16 @@
         <v>28</v>
       </c>
       <c r="AL47" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM47" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN47" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO47" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP47" t="n">
         <v>12.5</v>
@@ -12401,22 +12401,22 @@
         <v>10</v>
       </c>
       <c r="AR47" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT47" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU47" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV47" t="n">
         <v>10.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX47" t="n">
         <v>12</v>
@@ -12428,25 +12428,25 @@
         <v>14</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB47" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BC47" t="n">
         <v>19.5</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE47" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF47" t="n">
         <v>14.5</v>
       </c>
       <c r="BG47" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH47" t="n">
         <v>1000</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
         <v>1.52</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="R48" t="n">
         <v>1.22</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
         <v>3.6</v>
       </c>
       <c r="K49" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L49" t="n">
         <v>1.45</v>
@@ -12819,7 +12819,7 @@
         <v>1.07</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
         <v>1.35</v>
@@ -12828,7 +12828,7 @@
         <v>1.88</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R49" t="n">
         <v>1.31</v>
@@ -12840,7 +12840,7 @@
         <v>1.89</v>
       </c>
       <c r="U49" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V49" t="n">
         <v>1.25</v>
@@ -12861,10 +12861,10 @@
         <v>130</v>
       </c>
       <c r="AB49" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC49" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD49" t="n">
         <v>21</v>
@@ -12897,7 +12897,7 @@
         <v>150</v>
       </c>
       <c r="AN49" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO49" t="n">
         <v>100</v>
@@ -12909,10 +12909,10 @@
         <v>11.5</v>
       </c>
       <c r="AR49" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT49" t="n">
         <v>7.2</v>
@@ -12924,7 +12924,7 @@
         <v>16</v>
       </c>
       <c r="AW49" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX49" t="n">
         <v>8.800000000000001</v>
@@ -12936,7 +12936,7 @@
         <v>17.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB49" t="n">
         <v>16.5</v>
@@ -12945,16 +12945,16 @@
         <v>18.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF49" t="n">
         <v>12</v>
       </c>
       <c r="BG49" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH49" t="n">
         <v>3.2</v>
@@ -12999,7 +12999,7 @@
         <v>5.4</v>
       </c>
       <c r="BV49" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW49" t="n">
         <v>12</v>
@@ -13008,7 +13008,7 @@
         <v>1000</v>
       </c>
       <c r="BY49" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ49" t="n">
         <v>1000</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -13055,13 +13055,13 @@
         <v>1000</v>
       </c>
       <c r="H50" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I50" t="n">
         <v>1000</v>
       </c>
       <c r="J50" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="K50" t="n">
         <v>1000</v>
@@ -13073,13 +13073,13 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O50" t="n">
         <v>1.19</v>
       </c>
       <c r="P50" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q50" t="n">
         <v>1.18</v>
@@ -13088,7 +13088,7 @@
         <v>1.24</v>
       </c>
       <c r="S50" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T50" t="n">
         <v>1.11</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -13339,10 +13339,10 @@
         <v>1.27</v>
       </c>
       <c r="R51" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S51" t="n">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="T51" t="n">
         <v>1.11</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -13814,7 +13814,7 @@
         <v>2.42</v>
       </c>
       <c r="G53" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="H53" t="n">
         <v>2.74</v>
@@ -13823,7 +13823,7 @@
         <v>3.3</v>
       </c>
       <c r="J53" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="K53" t="n">
         <v>4.5</v>
@@ -13832,10 +13832,10 @@
         <v>1.33</v>
       </c>
       <c r="M53" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N53" t="n">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="O53" t="n">
         <v>1.33</v>
@@ -13853,16 +13853,16 @@
         <v>2.88</v>
       </c>
       <c r="T53" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="U53" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V53" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W53" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -14065,22 +14065,22 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="G54" t="n">
         <v>1000</v>
       </c>
       <c r="H54" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="I54" t="n">
         <v>1000</v>
       </c>
       <c r="J54" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="K54" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -14331,7 +14331,7 @@
         <v>1000</v>
       </c>
       <c r="J55" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -14585,28 +14585,28 @@
         <v>2.6</v>
       </c>
       <c r="J56" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K56" t="n">
         <v>3.4</v>
       </c>
       <c r="L56" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M56" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N56" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="O56" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P56" t="n">
         <v>1.53</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R56" t="n">
         <v>1.19</v>
@@ -14618,7 +14618,7 @@
         <v>2.02</v>
       </c>
       <c r="U56" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V56" t="n">
         <v>1.63</v>
@@ -14630,7 +14630,7 @@
         <v>11</v>
       </c>
       <c r="Y56" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z56" t="n">
         <v>17</v>
@@ -14648,7 +14648,7 @@
         <v>14.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF56" t="n">
         <v>32</v>
@@ -14657,7 +14657,7 @@
         <v>20</v>
       </c>
       <c r="AH56" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI56" t="n">
         <v>75</v>
@@ -14672,10 +14672,10 @@
         <v>100</v>
       </c>
       <c r="AM56" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN56" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO56" t="n">
         <v>42</v>
@@ -14684,7 +14684,7 @@
         <v>3.1</v>
       </c>
       <c r="AQ56" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AR56" t="n">
         <v>3.45</v>
@@ -14699,7 +14699,7 @@
         <v>2.88</v>
       </c>
       <c r="AV56" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AW56" t="n">
         <v>3.9</v>
@@ -14732,16 +14732,16 @@
         <v>4.1</v>
       </c>
       <c r="BG56" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BH56" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BI56" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ56" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK56" t="n">
         <v>5.6</v>
@@ -14750,7 +14750,7 @@
         <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BN56" t="n">
         <v>7</v>
@@ -14762,41 +14762,41 @@
         <v>1000</v>
       </c>
       <c r="BQ56" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BR56" t="n">
         <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BT56" t="n">
         <v>5.2</v>
       </c>
       <c r="BU56" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BV56" t="n">
         <v>22</v>
       </c>
       <c r="BW56" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BX56" t="n">
         <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BZ56" t="n">
         <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -14830,16 +14830,16 @@
         <v>2.76</v>
       </c>
       <c r="G57" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H57" t="n">
         <v>2.84</v>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J57" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K57" t="n">
         <v>3.45</v>
@@ -14851,7 +14851,7 @@
         <v>1.08</v>
       </c>
       <c r="N57" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O57" t="n">
         <v>1.37</v>
@@ -14866,22 +14866,22 @@
         <v>1.31</v>
       </c>
       <c r="S57" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T57" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U57" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V57" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W57" t="n">
         <v>1.54</v>
       </c>
       <c r="X57" t="n">
-        <v>970</v>
+        <v>180</v>
       </c>
       <c r="Y57" t="n">
         <v>11</v>
@@ -14896,7 +14896,7 @@
         <v>10.5</v>
       </c>
       <c r="AC57" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD57" t="n">
         <v>16</v>
@@ -14908,7 +14908,7 @@
         <v>970</v>
       </c>
       <c r="AG57" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH57" t="n">
         <v>970</v>
@@ -14917,7 +14917,7 @@
         <v>60</v>
       </c>
       <c r="AJ57" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="n">
         <v>55</v>
@@ -14932,7 +14932,7 @@
         <v>50</v>
       </c>
       <c r="AO57" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP57" t="n">
         <v>11.5</v>
@@ -14947,13 +14947,13 @@
         <v>25</v>
       </c>
       <c r="AT57" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU57" t="n">
         <v>6.6</v>
       </c>
       <c r="AV57" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW57" t="n">
         <v>21</v>
@@ -14968,7 +14968,7 @@
         <v>15.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB57" t="n">
         <v>24</v>
@@ -14977,16 +14977,16 @@
         <v>20</v>
       </c>
       <c r="BD57" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE57" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF57" t="n">
         <v>19.5</v>
       </c>
       <c r="BG57" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH57" t="n">
         <v>3.2</v>
@@ -15004,10 +15004,10 @@
         <v>1000</v>
       </c>
       <c r="BM57" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN57" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO57" t="n">
         <v>4.4</v>
@@ -15043,14 +15043,14 @@
         <v>11</v>
       </c>
       <c r="BZ57" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA57" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
         <v>1.12</v>
       </c>
       <c r="N59" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O59" t="n">
         <v>1.52</v>
@@ -15368,13 +15368,13 @@
         <v>1.51</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R59" t="n">
         <v>1.18</v>
       </c>
       <c r="S59" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T59" t="n">
         <v>2.4</v>
@@ -15410,7 +15410,7 @@
         <v>40</v>
       </c>
       <c r="AE59" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AF59" t="n">
         <v>9.800000000000001</v>
@@ -15422,7 +15422,7 @@
         <v>42</v>
       </c>
       <c r="AI59" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AJ59" t="n">
         <v>21</v>
@@ -15440,7 +15440,7 @@
         <v>22</v>
       </c>
       <c r="AO59" t="n">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="AP59" t="n">
         <v>6.6</v>
@@ -15500,40 +15500,40 @@
         <v>2.82</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ59" t="n">
         <v>14</v>
       </c>
       <c r="BK59" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL59" t="n">
         <v>1000</v>
       </c>
       <c r="BM59" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN59" t="n">
         <v>4</v>
       </c>
       <c r="BO59" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP59" t="n">
         <v>13</v>
       </c>
       <c r="BQ59" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR59" t="n">
         <v>42</v>
       </c>
       <c r="BS59" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT59" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU59" t="n">
         <v>5.7</v>
@@ -15542,23 +15542,23 @@
         <v>1000</v>
       </c>
       <c r="BW59" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX59" t="n">
         <v>1000</v>
       </c>
       <c r="BY59" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ59" t="n">
         <v>38</v>
       </c>
       <c r="CA59" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -15843,22 +15843,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.09</v>
+        <v>2.62</v>
       </c>
       <c r="G61" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="H61" t="n">
-        <v>1.09</v>
+        <v>2.42</v>
       </c>
       <c r="I61" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J61" t="n">
-        <v>1.1</v>
+        <v>2.36</v>
       </c>
       <c r="K61" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -15867,22 +15867,22 @@
         <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="O61" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="P61" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="R61" t="n">
         <v>1.13</v>
       </c>
       <c r="S61" t="n">
-        <v>1.59</v>
+        <v>2.68</v>
       </c>
       <c r="T61" t="n">
         <v>1.11</v>
@@ -15891,10 +15891,10 @@
         <v>1.11</v>
       </c>
       <c r="V61" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="W61" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -16097,22 +16097,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.09</v>
+        <v>2.78</v>
       </c>
       <c r="G62" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="H62" t="n">
-        <v>1.09</v>
+        <v>2.26</v>
       </c>
       <c r="I62" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J62" t="n">
-        <v>1.1</v>
+        <v>2.32</v>
       </c>
       <c r="K62" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L62" t="n">
         <v>1.01</v>
@@ -16121,22 +16121,22 @@
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="O62" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="P62" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="R62" t="n">
         <v>1.12</v>
       </c>
       <c r="S62" t="n">
-        <v>1.05</v>
+        <v>2.78</v>
       </c>
       <c r="T62" t="n">
         <v>1.11</v>
@@ -16145,10 +16145,10 @@
         <v>1.11</v>
       </c>
       <c r="V62" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="W62" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -16351,100 +16351,100 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.09</v>
+        <v>2.34</v>
       </c>
       <c r="G63" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="H63" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="I63" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J63" t="n">
-        <v>1.1</v>
+        <v>2.44</v>
       </c>
       <c r="K63" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L63" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M63" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N63" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="O63" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="P63" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="R63" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S63" t="n">
-        <v>1.05</v>
+        <v>1.67</v>
       </c>
       <c r="T63" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="U63" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V63" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="W63" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="X63" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y63" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z63" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA63" t="n">
         <v>1000</v>
       </c>
       <c r="AB63" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC63" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD63" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE63" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF63" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG63" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH63" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI63" t="n">
         <v>1000</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK63" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL63" t="n">
         <v>1000</v>
@@ -16453,7 +16453,7 @@
         <v>1000</v>
       </c>
       <c r="AN63" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO63" t="n">
         <v>1000</v>
@@ -16513,10 +16513,10 @@
         <v>1.01</v>
       </c>
       <c r="BH63" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="BI63" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ63" t="n">
         <v>1000</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -16605,112 +16605,112 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="G64" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="H64" t="n">
-        <v>1.09</v>
+        <v>2.44</v>
       </c>
       <c r="I64" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="J64" t="n">
-        <v>1.1</v>
+        <v>2.44</v>
       </c>
       <c r="K64" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L64" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M64" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N64" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="O64" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="P64" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="R64" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S64" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T64" t="n">
-        <v>1.11</v>
+        <v>2.22</v>
       </c>
       <c r="U64" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="V64" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="W64" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="X64" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Y64" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z64" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA64" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB64" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC64" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD64" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE64" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF64" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG64" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH64" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI64" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ64" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL64" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM64" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN64" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO64" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP64" t="n">
         <v>1.03</v>
@@ -16767,13 +16767,13 @@
         <v>1.01</v>
       </c>
       <c r="BH64" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="BI64" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ64" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK64" t="n">
         <v>1.04</v>
@@ -16785,7 +16785,7 @@
         <v>1.04</v>
       </c>
       <c r="BN64" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO64" t="n">
         <v>1.04</v>
@@ -16803,13 +16803,13 @@
         <v>1.04</v>
       </c>
       <c r="BT64" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU64" t="n">
         <v>1.04</v>
       </c>
       <c r="BV64" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW64" t="n">
         <v>1.04</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -16859,230 +16859,230 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="G65" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H65" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="I65" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J65" t="n">
-        <v>1.09</v>
+        <v>2.82</v>
       </c>
       <c r="K65" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L65" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M65" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N65" t="n">
-        <v>1.27</v>
+        <v>2.28</v>
       </c>
       <c r="O65" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="P65" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="R65" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S65" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W65" t="n">
         <v>1.58</v>
       </c>
-      <c r="T65" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.02</v>
-      </c>
       <c r="X65" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y65" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z65" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA65" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB65" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC65" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD65" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE65" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF65" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG65" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH65" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI65" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ65" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK65" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL65" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM65" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN65" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO65" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AU65" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV65" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX65" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY65" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AZ65" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA65" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB65" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC65" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD65" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE65" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF65" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG65" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH65" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI65" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ65" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK65" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL65" t="n">
         <v>1000</v>
       </c>
       <c r="BM65" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BN65" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO65" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP65" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ65" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="BR65" t="n">
         <v>1000</v>
       </c>
       <c r="BS65" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BT65" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU65" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV65" t="n">
         <v>1000</v>
       </c>
       <c r="BW65" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BX65" t="n">
         <v>1000</v>
       </c>
       <c r="BY65" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BZ65" t="n">
         <v>1000</v>
       </c>
       <c r="CA65" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -17367,154 +17367,154 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.09</v>
+        <v>1.98</v>
       </c>
       <c r="G67" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H67" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="I67" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="J67" t="n">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="K67" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L67" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M67" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N67" t="n">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="O67" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="P67" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.1</v>
+        <v>2.48</v>
       </c>
       <c r="R67" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="S67" t="n">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="T67" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U67" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="V67" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W67" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="X67" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y67" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z67" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA67" t="n">
         <v>1000</v>
       </c>
       <c r="AB67" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC67" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD67" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE67" t="n">
         <v>1000</v>
       </c>
       <c r="AF67" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG67" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI67" t="n">
         <v>1000</v>
       </c>
       <c r="AJ67" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK67" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL67" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM67" t="n">
         <v>1000</v>
       </c>
       <c r="AN67" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO67" t="n">
         <v>1000</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS67" t="n">
         <v>1.03</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW67" t="n">
         <v>1.03</v>
       </c>
       <c r="AX67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA67" t="n">
         <v>1.03</v>
       </c>
       <c r="BB67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD67" t="n">
         <v>1.03</v>
@@ -17532,7 +17532,7 @@
         <v>1000</v>
       </c>
       <c r="BI67" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ67" t="n">
         <v>1000</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -17645,22 +17645,22 @@
         <v>1.09</v>
       </c>
       <c r="N68" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O68" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="P68" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="R68" t="n">
         <v>1.12</v>
       </c>
       <c r="S68" t="n">
-        <v>1.67</v>
+        <v>1.05</v>
       </c>
       <c r="T68" t="n">
         <v>1.11</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -17875,112 +17875,112 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.09</v>
+        <v>1.69</v>
       </c>
       <c r="G69" t="n">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="H69" t="n">
-        <v>1.09</v>
+        <v>4.8</v>
       </c>
       <c r="I69" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="K69" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L69" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M69" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N69" t="n">
-        <v>1.34</v>
+        <v>2.44</v>
       </c>
       <c r="O69" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P69" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="R69" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="S69" t="n">
         <v>1.52</v>
       </c>
       <c r="T69" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="U69" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="V69" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W69" t="n">
-        <v>1.02</v>
+        <v>2.08</v>
       </c>
       <c r="X69" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y69" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z69" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA69" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AB69" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AC69" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD69" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE69" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF69" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG69" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH69" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI69" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ69" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK69" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL69" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM69" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AN69" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO69" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AP69" t="n">
         <v>1.03</v>
@@ -18031,19 +18031,19 @@
         <v>1.03</v>
       </c>
       <c r="BF69" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG69" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH69" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="BI69" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BJ69" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK69" t="n">
         <v>1.04</v>
@@ -18055,25 +18055,25 @@
         <v>1.04</v>
       </c>
       <c r="BN69" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO69" t="n">
         <v>1.04</v>
       </c>
       <c r="BP69" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ69" t="n">
         <v>1.04</v>
       </c>
       <c r="BR69" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS69" t="n">
         <v>1.04</v>
       </c>
       <c r="BT69" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU69" t="n">
         <v>1.04</v>
@@ -18091,14 +18091,14 @@
         <v>1.04</v>
       </c>
       <c r="BZ69" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA69" t="n">
         <v>1.04</v>
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18138,7 @@
         <v>10</v>
       </c>
       <c r="I70" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J70" t="n">
         <v>5.9</v>
@@ -18156,7 +18156,7 @@
         <v>6</v>
       </c>
       <c r="O70" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P70" t="n">
         <v>2.72</v>
@@ -18177,7 +18177,7 @@
         <v>1.97</v>
       </c>
       <c r="V70" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W70" t="n">
         <v>3.85</v>
@@ -18201,13 +18201,13 @@
         <v>18</v>
       </c>
       <c r="AD70" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AE70" t="n">
         <v>180</v>
       </c>
       <c r="AF70" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG70" t="n">
         <v>11.5</v>
@@ -18219,19 +18219,19 @@
         <v>1000</v>
       </c>
       <c r="AJ70" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK70" t="n">
         <v>14</v>
       </c>
       <c r="AL70" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AM70" t="n">
         <v>150</v>
       </c>
       <c r="AN70" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO70" t="n">
         <v>200</v>
@@ -18243,10 +18243,10 @@
         <v>23</v>
       </c>
       <c r="AR70" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS70" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT70" t="n">
         <v>10</v>
@@ -18258,7 +18258,7 @@
         <v>22</v>
       </c>
       <c r="AW70" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AX70" t="n">
         <v>8.4</v>
@@ -18270,7 +18270,7 @@
         <v>23</v>
       </c>
       <c r="BA70" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BB70" t="n">
         <v>9.800000000000001</v>
@@ -18279,16 +18279,16 @@
         <v>12</v>
       </c>
       <c r="BD70" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE70" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BF70" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BG70" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BH70" t="n">
         <v>4.8</v>
@@ -18300,16 +18300,16 @@
         <v>11.5</v>
       </c>
       <c r="BK70" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL70" t="n">
         <v>1000</v>
       </c>
       <c r="BM70" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN70" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BO70" t="n">
         <v>3.15</v>
@@ -18324,35 +18324,35 @@
         <v>21</v>
       </c>
       <c r="BS70" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT70" t="n">
         <v>14</v>
       </c>
       <c r="BU70" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BV70" t="n">
         <v>1000</v>
       </c>
       <c r="BW70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX70" t="n">
         <v>1000</v>
       </c>
       <c r="BY70" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ70" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="CA70" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -18491,52 +18491,52 @@
         <v>1000</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF71" t="n">
         <v>1.01</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -18637,10 +18637,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G72" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H72" t="n">
         <v>4.2</v>
@@ -18649,10 +18649,10 @@
         <v>4.6</v>
       </c>
       <c r="J72" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K72" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L72" t="n">
         <v>1.01</v>
@@ -18679,22 +18679,22 @@
         <v>4</v>
       </c>
       <c r="T72" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U72" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V72" t="n">
         <v>1.28</v>
       </c>
       <c r="W72" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="X72" t="n">
         <v>12.5</v>
       </c>
       <c r="Y72" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z72" t="n">
         <v>32</v>
@@ -18703,10 +18703,10 @@
         <v>120</v>
       </c>
       <c r="AB72" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC72" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD72" t="n">
         <v>18</v>
@@ -18715,13 +18715,13 @@
         <v>85</v>
       </c>
       <c r="AF72" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG72" t="n">
         <v>13</v>
       </c>
       <c r="AH72" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI72" t="n">
         <v>100</v>
@@ -18736,10 +18736,10 @@
         <v>42</v>
       </c>
       <c r="AM72" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN72" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO72" t="n">
         <v>100</v>
@@ -18751,10 +18751,10 @@
         <v>12.5</v>
       </c>
       <c r="AR72" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AS72" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AT72" t="n">
         <v>7.2</v>
@@ -18766,7 +18766,7 @@
         <v>15.5</v>
       </c>
       <c r="AW72" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX72" t="n">
         <v>10.5</v>
@@ -18778,89 +18778,89 @@
         <v>17.5</v>
       </c>
       <c r="BA72" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB72" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BC72" t="n">
         <v>20</v>
       </c>
       <c r="BD72" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE72" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BF72" t="n">
         <v>13</v>
       </c>
       <c r="BG72" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH72" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI72" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ72" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK72" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL72" t="n">
         <v>1000</v>
       </c>
       <c r="BM72" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN72" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO72" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP72" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ72" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR72" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS72" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT72" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU72" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BV72" t="n">
         <v>1000</v>
       </c>
       <c r="BW72" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX72" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY72" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ72" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA72" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -19005,10 +19005,10 @@
         <v>14</v>
       </c>
       <c r="AR73" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AS73" t="n">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="AT73" t="n">
         <v>9.6</v>
@@ -19020,7 +19020,7 @@
         <v>12</v>
       </c>
       <c r="AW73" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="AX73" t="n">
         <v>10.5</v>
@@ -19032,7 +19032,7 @@
         <v>11.5</v>
       </c>
       <c r="BA73" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BB73" t="n">
         <v>16.5</v>
@@ -19044,7 +19044,7 @@
         <v>20</v>
       </c>
       <c r="BE73" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BF73" t="n">
         <v>7</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>
@@ -19148,7 +19148,7 @@
         <v>1.95</v>
       </c>
       <c r="G74" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H74" t="n">
         <v>3.85</v>
@@ -19190,7 +19190,7 @@
         <v>1.73</v>
       </c>
       <c r="U74" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V74" t="n">
         <v>1.29</v>
@@ -19259,10 +19259,10 @@
         <v>13</v>
       </c>
       <c r="AR74" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AS74" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="AT74" t="n">
         <v>8</v>
@@ -19274,7 +19274,7 @@
         <v>13.5</v>
       </c>
       <c r="AW74" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AX74" t="n">
         <v>10</v>
@@ -19286,7 +19286,7 @@
         <v>13.5</v>
       </c>
       <c r="BA74" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB74" t="n">
         <v>16.5</v>
@@ -19295,10 +19295,10 @@
         <v>14.5</v>
       </c>
       <c r="BD74" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BE74" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="BF74" t="n">
         <v>9.800000000000001</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-06-12 14:36:19</t>
+          <t>2026-06-12 16:55:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -866,13 +866,13 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
         <v>1.46</v>
@@ -881,10 +881,10 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P2" t="n">
         <v>1.75</v>
@@ -941,7 +941,7 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI2" t="n">
         <v>370</v>
@@ -965,7 +965,7 @@
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
         <v>6.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AV2" t="n">
         <v>8.4</v>
@@ -1013,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BG2" t="n">
         <v>8.6</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.5</v>
@@ -1135,7 +1135,7 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="O3" t="n">
         <v>1.47</v>
@@ -1144,7 +1144,7 @@
         <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -1222,7 +1222,7 @@
         <v>4.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR3" t="n">
         <v>7.6</v>
@@ -1243,7 +1243,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY3" t="n">
         <v>4.9</v>
@@ -1282,13 +1282,13 @@
         <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BN3" t="n">
         <v>4</v>
@@ -1300,31 +1300,31 @@
         <v>12.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BT3" t="n">
         <v>11</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
         <v>1.45</v>
@@ -1497,10 +1497,10 @@
         <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AZ4" t="n">
         <v>6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G5" t="n">
         <v>2.28</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
         <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
@@ -1646,31 +1646,31 @@
         <v>5.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
         <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
         <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U5" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V5" t="n">
         <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X5" t="n">
         <v>32</v>
@@ -1730,13 +1730,13 @@
         <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
         <v>12.5</v>
@@ -1745,10 +1745,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX5" t="n">
         <v>15.5</v>
@@ -1757,28 +1757,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
         <v>23</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
         <v>9.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="n">
         <v>4.1</v>
@@ -1790,16 +1790,16 @@
         <v>9</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO5" t="n">
         <v>4.2</v>
@@ -1808,41 +1808,41 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT5" t="n">
         <v>7</v>
       </c>
       <c r="BU5" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1897,22 +1897,22 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1924,115 +1924,115 @@
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
         <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J7" t="n">
         <v>2.76</v>
@@ -2151,16 +2151,16 @@
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.59</v>
       </c>
       <c r="P7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
@@ -2172,19 +2172,19 @@
         <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
         <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="Z7" t="n">
         <v>970</v>
@@ -2214,7 +2214,7 @@
         <v>48</v>
       </c>
       <c r="AI7" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
@@ -2229,64 +2229,64 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS7" t="n">
         <v>5.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AW7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX7" t="n">
         <v>5.1</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD7" t="n">
         <v>4.7</v>
       </c>
-      <c r="AY7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ7" t="n">
+      <c r="BE7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH7" t="n">
         <v>2.62</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="n">
         <v>4.3</v>
@@ -2393,13 +2393,13 @@
         <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
@@ -2432,7 +2432,7 @@
         <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X8" t="n">
         <v>11.5</v>
@@ -2441,7 +2441,7 @@
         <v>14</v>
       </c>
       <c r="Z8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -2486,7 +2486,7 @@
         <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
         <v>9.199999999999999</v>
@@ -2495,52 +2495,52 @@
         <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB8" t="n">
         <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BE8" t="n">
         <v>7.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BH8" t="n">
         <v>3.05</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H9" t="n">
         <v>1.11</v>
@@ -2665,7 +2665,7 @@
         <v>1.09</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q9" t="n">
         <v>1.28</v>
@@ -2680,7 +2680,7 @@
         <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V9" t="n">
         <v>7.8</v>
@@ -2713,7 +2713,7 @@
         <v>15.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AG9" t="n">
         <v>120</v>
@@ -2749,7 +2749,7 @@
         <v>7.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
         <v>5.6</v>
@@ -2788,7 +2788,7 @@
         <v>12.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF9" t="n">
         <v>13</v>
@@ -2824,13 +2824,13 @@
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>3.05</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>3.05</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT9" t="n">
         <v>4.1</v>
@@ -2842,7 +2842,7 @@
         <v>5.6</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BX9" t="n">
         <v>21</v>
@@ -2854,11 +2854,11 @@
         <v>5.4</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -2889,230 +2889,230 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.46</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>80</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.41</v>
-      </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
         <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W10" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB10" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>95</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ10" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
         <v>95</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.64</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.71</v>
+        <v>18</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.71</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.71</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.61</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX10" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AY10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA10" t="n">
         <v>7</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BB10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>11</v>
       </c>
-      <c r="BD10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -3146,227 +3146,227 @@
         <v>1.55</v>
       </c>
       <c r="G11" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
         <v>5.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y11" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AK11" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.46</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.46</v>
+        <v>7.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.46</v>
+        <v>4.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.46</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.46</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.46</v>
+        <v>6</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.46</v>
+        <v>7.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.46</v>
+        <v>7.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.37</v>
+        <v>5.7</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.46</v>
+        <v>7.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.37</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.46</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.46</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.46</v>
+        <v>5</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G12" t="n">
         <v>5.6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I12" t="n">
         <v>1.95</v>
@@ -3433,7 +3433,7 @@
         <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
         <v>3.4</v>
@@ -3457,7 +3457,7 @@
         <v>9</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
         <v>24</v>
@@ -3478,16 +3478,16 @@
         <v>46</v>
       </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
         <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AK12" t="n">
         <v>700</v>
@@ -3496,31 +3496,31 @@
         <v>700</v>
       </c>
       <c r="AM12" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
         <v>13.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
         <v>7.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
         <v>8.6</v>
@@ -3529,31 +3529,31 @@
         <v>16.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
         <v>11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>2.42</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="H13" t="n">
         <v>3.25</v>
@@ -3663,10 +3663,10 @@
         <v>3.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.52</v>
@@ -3681,7 +3681,7 @@
         <v>1.49</v>
       </c>
       <c r="P13" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q13" t="n">
         <v>2.44</v>
@@ -3693,19 +3693,19 @@
         <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>90</v>
       </c>
       <c r="Y13" t="n">
         <v>970</v>
@@ -3735,7 +3735,7 @@
         <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AI13" t="n">
         <v>190</v>
@@ -3753,70 +3753,70 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>42</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AY13" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
         <v>4</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="n">
         <v>2.9</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G14" t="n">
         <v>2.46</v>
@@ -3914,7 +3914,7 @@
         <v>2.88</v>
       </c>
       <c r="I14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -3923,7 +3923,7 @@
         <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
@@ -3938,7 +3938,7 @@
         <v>2.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R14" t="n">
         <v>1.69</v>
@@ -3947,28 +3947,28 @@
         <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="U14" t="n">
         <v>2.72</v>
       </c>
       <c r="V14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
         <v>1.69</v>
       </c>
       <c r="X14" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="Y14" t="n">
         <v>22</v>
       </c>
       <c r="Z14" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AA14" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AB14" t="n">
         <v>19</v>
@@ -3980,76 +3980,76 @@
         <v>17</v>
       </c>
       <c r="AE14" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AF14" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>60</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AK14" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>13</v>
       </c>
       <c r="AO14" t="n">
-        <v>19.5</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.75</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX14" t="n">
         <v>14</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC14" t="n">
         <v>15.5</v>
@@ -4058,10 +4058,10 @@
         <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG14" t="n">
         <v>12.5</v>
@@ -4106,7 +4106,7 @@
         <v>7</v>
       </c>
       <c r="BU14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -4165,64 +4165,64 @@
         <v>1.86</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
         <v>3.95</v>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T15" t="n">
         <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
         <v>2.16</v>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z15" t="n">
         <v>500</v>
       </c>
       <c r="AA15" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
         <v>8</v>
@@ -4243,104 +4243,104 @@
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AI15" t="n">
         <v>700</v>
       </c>
       <c r="AJ15" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AK15" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AL15" t="n">
         <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AO15" t="n">
         <v>700</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT15" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT15" t="n">
-        <v>2.92</v>
-      </c>
       <c r="AU15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH15" t="n">
         <v>3.1</v>
       </c>
-      <c r="AV15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW15" t="n">
+      <c r="BI15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN15" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO15" t="n">
         <v>1.01</v>
       </c>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>2.66</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I16" t="n">
         <v>4.1</v>
@@ -4431,7 +4431,7 @@
         <v>3.45</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M16" t="n">
         <v>1.11</v>
@@ -4446,7 +4446,7 @@
         <v>1.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="R16" t="n">
         <v>1.19</v>
@@ -4470,31 +4470,31 @@
         <v>9.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA16" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC16" t="n">
         <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF16" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
         <v>27</v>
@@ -4503,13 +4503,13 @@
         <v>100</v>
       </c>
       <c r="AJ16" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK16" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AM16" t="n">
         <v>500</v>
@@ -4521,67 +4521,67 @@
         <v>100</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AS16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY16" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK16" t="n">
         <v>1.01</v>
@@ -4593,37 +4593,37 @@
         <v>1.01</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO16" t="n">
         <v>1.01</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ16" t="n">
         <v>1.01</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS16" t="n">
         <v>1.01</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU16" t="n">
         <v>1.01</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW16" t="n">
         <v>1.01</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
         <v>1.01</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -4667,172 +4667,172 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="G17" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1</v>
+        <v>2.46</v>
       </c>
       <c r="O17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P17" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V17" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.05</v>
+        <v>3.85</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH17" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BJ17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -4924,16 +4924,16 @@
         <v>2.18</v>
       </c>
       <c r="G18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H18" t="n">
         <v>3.85</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K18" t="n">
         <v>3.3</v>
@@ -4948,7 +4948,7 @@
         <v>2.44</v>
       </c>
       <c r="O18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P18" t="n">
         <v>1.48</v>
@@ -4957,7 +4957,7 @@
         <v>2.68</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
         <v>5.5</v>
@@ -4969,16 +4969,16 @@
         <v>1.7</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X18" t="n">
         <v>8.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z18" t="n">
         <v>500</v>
@@ -4987,34 +4987,34 @@
         <v>500</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AC18" t="n">
         <v>7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AE18" t="n">
         <v>500</v>
       </c>
       <c r="AF18" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AI18" t="n">
         <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AL18" t="n">
         <v>500</v>
@@ -5026,10 +5026,10 @@
         <v>500</v>
       </c>
       <c r="AO18" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ18" t="n">
         <v>9</v>
@@ -5038,7 +5038,7 @@
         <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
         <v>5.9</v>
@@ -5047,40 +5047,40 @@
         <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BG18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BH18" t="n">
         <v>2.7</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -5175,10 +5175,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
         <v>3.35</v>
@@ -5187,163 +5187,163 @@
         <v>3.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
         <v>3.55</v>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1</v>
+        <v>2.92</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH19" t="n">
         <v>3.1</v>
       </c>
-      <c r="T19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X19" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>1000</v>
-      </c>
       <c r="BI19" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK19" t="n">
         <v>1.01</v>
@@ -5355,50 +5355,50 @@
         <v>1.01</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ19" t="n">
         <v>1.01</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS19" t="n">
         <v>1.01</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW19" t="n">
         <v>1.01</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY19" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA19" t="n">
         <v>1.01</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -5429,172 +5429,172 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="G20" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I20" t="n">
         <v>1.83</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P20" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>2.48</v>
+        <v>1.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
         <v>2.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
         <v>90</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC20" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO20" t="n">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BH20" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BJ20" t="n">
         <v>1000</v>
@@ -5627,7 +5627,7 @@
         <v>1.01</v>
       </c>
       <c r="BT20" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BU20" t="n">
         <v>1.01</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>4.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I21" t="n">
         <v>2.26</v>
@@ -5701,7 +5701,7 @@
         <v>3.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -5713,25 +5713,25 @@
         <v>1.36</v>
       </c>
       <c r="P21" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R21" t="n">
         <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U21" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V21" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W21" t="n">
         <v>1.28</v>
@@ -5740,7 +5740,7 @@
         <v>13</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z21" t="n">
         <v>15.5</v>
@@ -5776,19 +5776,19 @@
         <v>500</v>
       </c>
       <c r="AK21" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AL21" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM21" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>80</v>
+        <v>600</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AP21" t="n">
         <v>10.5</v>
@@ -5797,16 +5797,16 @@
         <v>6.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AS21" t="n">
         <v>20</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
         <v>8</v>
@@ -5824,22 +5824,22 @@
         <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BG21" t="n">
         <v>16</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>1.8</v>
       </c>
       <c r="H22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I22" t="n">
         <v>5.7</v>
@@ -5955,7 +5955,7 @@
         <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
@@ -5964,7 +5964,7 @@
         <v>3.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P22" t="n">
         <v>1.92</v>
@@ -5976,13 +5976,13 @@
         <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.96</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.94</v>
       </c>
       <c r="V22" t="n">
         <v>1.21</v>
@@ -6024,7 +6024,7 @@
         <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>700</v>
+        <v>330</v>
       </c>
       <c r="AJ22" t="n">
         <v>18.5</v>
@@ -6036,7 +6036,7 @@
         <v>46</v>
       </c>
       <c r="AM22" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
         <v>12.5</v>
@@ -6051,10 +6051,10 @@
         <v>15.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT22" t="n">
         <v>7.2</v>
@@ -6066,7 +6066,7 @@
         <v>17.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX22" t="n">
         <v>9</v>
@@ -6075,10 +6075,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB22" t="n">
         <v>15</v>
@@ -6087,16 +6087,16 @@
         <v>17</v>
       </c>
       <c r="BD22" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF22" t="n">
         <v>10.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH22" t="n">
         <v>3.4</v>
@@ -6147,7 +6147,7 @@
         <v>12.5</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY22" t="n">
         <v>13</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>1.89</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H23" t="n">
         <v>4.2</v>
@@ -6221,13 +6221,13 @@
         <v>1.27</v>
       </c>
       <c r="P23" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
         <v>1.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
         <v>2.98</v>
@@ -6242,7 +6242,7 @@
         <v>1.29</v>
       </c>
       <c r="W23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X23" t="n">
         <v>19</v>
@@ -6278,7 +6278,7 @@
         <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
@@ -6290,7 +6290,7 @@
         <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
         <v>11.5</v>
@@ -6302,7 +6302,7 @@
         <v>15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AR23" t="n">
         <v>14.5</v>
@@ -6353,10 +6353,10 @@
         <v>9</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.800000000000001</v>
@@ -6368,7 +6368,7 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN23" t="n">
         <v>4.9</v>
@@ -6380,13 +6380,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ23" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR23" t="n">
         <v>26</v>
       </c>
       <c r="BS23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT23" t="n">
         <v>8.199999999999999</v>
@@ -6398,23 +6398,23 @@
         <v>36</v>
       </c>
       <c r="BW23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX23" t="n">
         <v>42</v>
       </c>
       <c r="BY23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ23" t="n">
         <v>21</v>
       </c>
       <c r="CA23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -6448,10 +6448,10 @@
         <v>3.15</v>
       </c>
       <c r="G24" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H24" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I24" t="n">
         <v>2.5</v>
@@ -6463,22 +6463,22 @@
         <v>3.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O24" t="n">
         <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R24" t="n">
         <v>1.29</v>
@@ -6487,7 +6487,7 @@
         <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U24" t="n">
         <v>1.98</v>
@@ -6496,13 +6496,13 @@
         <v>1.66</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z24" t="n">
         <v>16.5</v>
@@ -6511,7 +6511,7 @@
         <v>40</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
         <v>7.8</v>
@@ -6529,10 +6529,10 @@
         <v>14.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AI24" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AJ24" t="n">
         <v>60</v>
@@ -6541,19 +6541,19 @@
         <v>110</v>
       </c>
       <c r="AL24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM24" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="AO24" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ24" t="n">
         <v>7.6</v>
@@ -6562,7 +6562,7 @@
         <v>8.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -6571,13 +6571,13 @@
         <v>6.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW24" t="n">
         <v>24</v>
       </c>
       <c r="AX24" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AY24" t="n">
         <v>12</v>
@@ -6586,10 +6586,10 @@
         <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB24" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC24" t="n">
         <v>32</v>
@@ -6598,16 +6598,16 @@
         <v>42</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF24" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BG24" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BH24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI24" t="n">
         <v>2.54</v>
@@ -6616,16 +6616,16 @@
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BN24" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
         <v>4.5</v>
@@ -6634,41 +6634,41 @@
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>6.2</v>
+        <v>3.65</v>
       </c>
       <c r="BT24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV24" t="n">
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
         <v>3.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R25" t="n">
         <v>1.92</v>
@@ -6762,13 +6762,13 @@
         <v>19</v>
       </c>
       <c r="AA25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB25" t="n">
         <v>34</v>
       </c>
       <c r="AC25" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="n">
         <v>13.5</v>
@@ -6783,7 +6783,7 @@
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI25" t="n">
         <v>26</v>
@@ -6807,16 +6807,16 @@
         <v>6</v>
       </c>
       <c r="AP25" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR25" t="n">
         <v>12.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>16</v>
@@ -6831,7 +6831,7 @@
         <v>12</v>
       </c>
       <c r="AX25" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AY25" t="n">
         <v>15.5</v>
@@ -6843,16 +6843,16 @@
         <v>16.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD25" t="n">
         <v>16</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF25" t="n">
         <v>19</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -6971,157 +6971,157 @@
         <v>4.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P26" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S26" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W26" t="n">
         <v>1.4</v>
       </c>
       <c r="X26" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="Y26" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>500</v>
+        <v>18.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AB26" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AC26" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AF26" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AG26" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AJ26" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AK26" t="n">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AL26" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="AM26" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AO26" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK26" t="n">
         <v>1.01</v>
@@ -7133,13 +7133,13 @@
         <v>1.01</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BP26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ26" t="n">
         <v>1.01</v>
@@ -7151,32 +7151,32 @@
         <v>1.01</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV26" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW26" t="n">
         <v>1.01</v>
       </c>
       <c r="BX26" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY26" t="n">
         <v>1.01</v>
       </c>
       <c r="BZ26" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA26" t="n">
         <v>1.01</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -7264,46 +7264,46 @@
         <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AH27" t="n">
         <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
@@ -7363,10 +7363,10 @@
         <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC28" t="n">
         <v>20</v>
@@ -7539,7 +7539,7 @@
         <v>200</v>
       </c>
       <c r="AF28" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AG28" t="n">
         <v>36</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="F29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G29" t="n">
         <v>1.31</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.36</v>
       </c>
       <c r="H29" t="n">
         <v>10.5</v>
@@ -7727,10 +7727,10 @@
         <v>16.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="K29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L29" t="n">
         <v>1.33</v>
@@ -7742,10 +7742,10 @@
         <v>3.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P29" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q29" t="n">
         <v>1.9</v>
@@ -7766,7 +7766,7 @@
         <v>1.07</v>
       </c>
       <c r="W29" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="X29" t="n">
         <v>970</v>
@@ -7781,7 +7781,7 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC29" t="n">
         <v>42</v>
@@ -7793,7 +7793,7 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AG29" t="n">
         <v>970</v>
@@ -7826,7 +7826,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR29" t="n">
         <v>4.2</v>
@@ -7841,7 +7841,7 @@
         <v>6.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AW29" t="n">
         <v>4.2</v>
@@ -7850,31 +7850,31 @@
         <v>5.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BA29" t="n">
         <v>4.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC29" t="n">
         <v>10</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="BF29" t="n">
         <v>5.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BH29" t="n">
         <v>8.199999999999999</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
         <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="O30" t="n">
         <v>1.15</v>
@@ -8011,7 +8011,7 @@
         <v>2.14</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
         <v>1.72</v>
@@ -8029,10 +8029,10 @@
         <v>11.5</v>
       </c>
       <c r="Z30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA30" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>10.5</v>
       </c>
       <c r="AB30" t="n">
         <v>950</v>
@@ -8050,7 +8050,7 @@
         <v>200</v>
       </c>
       <c r="AG30" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="AH30" t="n">
         <v>44</v>
@@ -8089,7 +8089,7 @@
         <v>7.2</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU30" t="n">
         <v>13.5</v>
@@ -8101,10 +8101,10 @@
         <v>10.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AZ30" t="n">
         <v>18</v>
@@ -8113,16 +8113,16 @@
         <v>19.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD30" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF30" t="n">
         <v>15</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -8259,13 +8259,13 @@
         <v>1.68</v>
       </c>
       <c r="R31" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S31" t="n">
         <v>2.62</v>
       </c>
       <c r="T31" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="U31" t="n">
         <v>1.11</v>
@@ -8274,22 +8274,22 @@
         <v>1.69</v>
       </c>
       <c r="W31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X31" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="Z31" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AA31" t="n">
         <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="AC31" t="n">
         <v>42</v>
@@ -8298,91 +8298,91 @@
         <v>970</v>
       </c>
       <c r="AE31" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AF31" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AG31" t="n">
-        <v>38</v>
+        <v>170</v>
       </c>
       <c r="AH31" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI31" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AJ31" t="n">
-        <v>440</v>
+        <v>900</v>
       </c>
       <c r="AK31" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AL31" t="n">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="AM31" t="n">
-        <v>320</v>
+        <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AU31" t="n">
         <v>5.1</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.1</v>
+        <v>1.55</v>
       </c>
       <c r="BG31" t="n">
-        <v>2.86</v>
+        <v>1.55</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G32" t="n">
         <v>1.96</v>
@@ -8516,7 +8516,7 @@
         <v>1.53</v>
       </c>
       <c r="S32" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
         <v>1.6</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8746,7 @@
         <v>3.8</v>
       </c>
       <c r="K33" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L33" t="n">
         <v>1.27</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G34" t="n">
         <v>4.5</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -9242,16 +9242,16 @@
         <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H35" t="n">
         <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K35" t="n">
         <v>5.2</v>
@@ -9266,7 +9266,7 @@
         <v>4.5</v>
       </c>
       <c r="O35" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P35" t="n">
         <v>2.22</v>
@@ -9290,10 +9290,10 @@
         <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X35" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y35" t="n">
         <v>32</v>
@@ -9353,7 +9353,7 @@
         <v>18</v>
       </c>
       <c r="AR35" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS35" t="n">
         <v>5</v>
@@ -9368,7 +9368,7 @@
         <v>18</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX35" t="n">
         <v>7.6</v>
@@ -9392,7 +9392,7 @@
         <v>16</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF35" t="n">
         <v>6</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>2.6</v>
       </c>
       <c r="H36" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I36" t="n">
         <v>2.98</v>
@@ -9523,7 +9523,7 @@
         <v>1.19</v>
       </c>
       <c r="P36" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q36" t="n">
         <v>1.58</v>
@@ -9547,13 +9547,13 @@
         <v>1.62</v>
       </c>
       <c r="X36" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y36" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z36" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA36" t="n">
         <v>48</v>
@@ -9562,43 +9562,43 @@
         <v>16.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE36" t="n">
         <v>32</v>
       </c>
       <c r="AF36" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG36" t="n">
         <v>13</v>
       </c>
       <c r="AH36" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI36" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ36" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK36" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN36" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO36" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP36" t="n">
         <v>18.5</v>
@@ -9610,7 +9610,7 @@
         <v>19</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.9</v>
+        <v>34</v>
       </c>
       <c r="AT36" t="n">
         <v>13</v>
@@ -9622,7 +9622,7 @@
         <v>11</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AX36" t="n">
         <v>15</v>
@@ -9634,19 +9634,19 @@
         <v>12.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="BB36" t="n">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="BC36" t="n">
         <v>19.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BF36" t="n">
         <v>11.5</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G37" t="n">
         <v>3.3</v>
@@ -9771,22 +9771,22 @@
         <v>1.02</v>
       </c>
       <c r="N37" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P37" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R37" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S37" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T37" t="n">
         <v>1.47</v>
@@ -9804,7 +9804,7 @@
         <v>90</v>
       </c>
       <c r="Y37" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="Z37" t="n">
         <v>50</v>
@@ -9825,7 +9825,7 @@
         <v>500</v>
       </c>
       <c r="AF37" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AG37" t="n">
         <v>18.5</v>
@@ -9858,7 +9858,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AR37" t="n">
         <v>14</v>
@@ -9867,7 +9867,7 @@
         <v>20</v>
       </c>
       <c r="AT37" t="n">
-        <v>15</v>
+        <v>4.9</v>
       </c>
       <c r="AU37" t="n">
         <v>8</v>
@@ -9879,7 +9879,7 @@
         <v>14.5</v>
       </c>
       <c r="AX37" t="n">
-        <v>18.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY37" t="n">
         <v>10</v>
@@ -9891,7 +9891,7 @@
         <v>17.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC37" t="n">
         <v>4.9</v>
@@ -9900,7 +9900,7 @@
         <v>14.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF37" t="n">
         <v>12</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
         <v>4.9</v>
       </c>
       <c r="G38" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H38" t="n">
         <v>1.76</v>
@@ -10025,28 +10025,28 @@
         <v>1.05</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P38" t="n">
         <v>2.22</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R38" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S38" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="T38" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U38" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V38" t="n">
         <v>2.18</v>
@@ -10055,7 +10055,7 @@
         <v>1.23</v>
       </c>
       <c r="X38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y38" t="n">
         <v>10.5</v>
@@ -10085,7 +10085,7 @@
         <v>19</v>
       </c>
       <c r="AH38" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI38" t="n">
         <v>46</v>
@@ -10100,13 +10100,13 @@
         <v>130</v>
       </c>
       <c r="AM38" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN38" t="n">
         <v>120</v>
       </c>
       <c r="AO38" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP38" t="n">
         <v>15</v>
@@ -10139,13 +10139,13 @@
         <v>17</v>
       </c>
       <c r="AZ38" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA38" t="n">
         <v>23</v>
       </c>
       <c r="BB38" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC38" t="n">
         <v>42</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="G39" t="n">
         <v>3.8</v>
@@ -10264,7 +10264,7 @@
         <v>2.22</v>
       </c>
       <c r="I39" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J39" t="n">
         <v>3.45</v>
@@ -10282,16 +10282,16 @@
         <v>3.45</v>
       </c>
       <c r="O39" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P39" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q39" t="n">
         <v>2.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
         <v>3.9</v>
@@ -10303,10 +10303,10 @@
         <v>2.06</v>
       </c>
       <c r="V39" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="W39" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X39" t="n">
         <v>13</v>
@@ -10318,16 +10318,16 @@
         <v>14</v>
       </c>
       <c r="AA39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB39" t="n">
         <v>13</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE39" t="n">
         <v>25</v>
@@ -10354,7 +10354,7 @@
         <v>65</v>
       </c>
       <c r="AM39" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN39" t="n">
         <v>65</v>
@@ -10363,7 +10363,7 @@
         <v>21</v>
       </c>
       <c r="AP39" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ39" t="n">
         <v>8.199999999999999</v>
@@ -10378,7 +10378,7 @@
         <v>11</v>
       </c>
       <c r="AU39" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV39" t="n">
         <v>10</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -10509,16 +10509,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="G40" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H40" t="n">
         <v>3.45</v>
       </c>
       <c r="I40" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J40" t="n">
         <v>4.2</v>
@@ -10539,7 +10539,7 @@
         <v>1.2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q40" t="n">
         <v>1.58</v>
@@ -10557,10 +10557,10 @@
         <v>2.14</v>
       </c>
       <c r="V40" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W40" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X40" t="n">
         <v>29</v>
@@ -10569,7 +10569,7 @@
         <v>19.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA40" t="n">
         <v>75</v>
@@ -10584,7 +10584,7 @@
         <v>16</v>
       </c>
       <c r="AE40" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF40" t="n">
         <v>16.5</v>
@@ -10596,7 +10596,7 @@
         <v>16.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ40" t="n">
         <v>28</v>
@@ -10617,37 +10617,37 @@
         <v>27</v>
       </c>
       <c r="AP40" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR40" t="n">
         <v>24</v>
       </c>
       <c r="AS40" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT40" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU40" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AV40" t="n">
         <v>6.2</v>
       </c>
       <c r="AW40" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX40" t="n">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="AY40" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA40" t="n">
         <v>8.199999999999999</v>
@@ -10656,7 +10656,7 @@
         <v>22</v>
       </c>
       <c r="BC40" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BD40" t="n">
         <v>23</v>
@@ -10668,7 +10668,7 @@
         <v>5.4</v>
       </c>
       <c r="BG40" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH40" t="n">
         <v>4.4</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G41" t="n">
         <v>1.93</v>
@@ -10775,7 +10775,7 @@
         <v>5.6</v>
       </c>
       <c r="J41" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K41" t="n">
         <v>3.5</v>
@@ -10787,13 +10787,13 @@
         <v>1.12</v>
       </c>
       <c r="N41" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O41" t="n">
         <v>1.57</v>
       </c>
       <c r="P41" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q41" t="n">
         <v>2.62</v>
@@ -10808,7 +10808,7 @@
         <v>2.28</v>
       </c>
       <c r="U41" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V41" t="n">
         <v>1.22</v>
@@ -10817,10 +10817,10 @@
         <v>2.06</v>
       </c>
       <c r="X41" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z41" t="n">
         <v>500</v>
@@ -10877,22 +10877,22 @@
         <v>9.6</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.74</v>
+        <v>1.98</v>
       </c>
       <c r="AT41" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU41" t="n">
         <v>6.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="AX41" t="n">
         <v>7.8</v>
@@ -10901,31 +10901,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ41" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.3</v>
+        <v>1.97</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC41" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD41" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE41" t="n">
-        <v>6.6</v>
+        <v>3</v>
       </c>
       <c r="BF41" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG41" t="n">
-        <v>2.74</v>
+        <v>1.98</v>
       </c>
       <c r="BH41" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BI41" t="n">
         <v>2.22</v>
@@ -10934,7 +10934,7 @@
         <v>1000</v>
       </c>
       <c r="BK41" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL41" t="n">
         <v>1000</v>
@@ -10946,25 +10946,25 @@
         <v>4.4</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP41" t="n">
         <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BT41" t="n">
         <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -11041,7 +11041,7 @@
         <v>1.02</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O42" t="n">
         <v>1.17</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -11271,22 +11271,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G43" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="H43" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I43" t="n">
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
@@ -11304,7 +11304,7 @@
         <v>1.32</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
@@ -11322,7 +11322,7 @@
         <v>1.11</v>
       </c>
       <c r="W43" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -11340,7 +11340,7 @@
         <v>970</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD43" t="n">
         <v>1000</v>
@@ -11373,7 +11373,7 @@
         <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO43" t="n">
         <v>1000</v>
@@ -11394,7 +11394,7 @@
         <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV43" t="n">
         <v>1.01</v>
@@ -11403,7 +11403,7 @@
         <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY43" t="n">
         <v>1.01</v>
@@ -11415,7 +11415,7 @@
         <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC43" t="n">
         <v>1.01</v>
@@ -11427,10 +11427,10 @@
         <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.05</v>
+        <v>3.15</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
         <v>8.6</v>
       </c>
       <c r="J44" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K44" t="n">
         <v>5.3</v>
@@ -11624,13 +11624,13 @@
         <v>34</v>
       </c>
       <c r="AM44" t="n">
-        <v>140</v>
+        <v>390</v>
       </c>
       <c r="AN44" t="n">
         <v>7</v>
       </c>
       <c r="AO44" t="n">
-        <v>150</v>
+        <v>530</v>
       </c>
       <c r="AP44" t="n">
         <v>14.5</v>
@@ -11642,7 +11642,7 @@
         <v>21</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT44" t="n">
         <v>8</v>
@@ -11675,10 +11675,10 @@
         <v>11.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF44" t="n">
         <v>6</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -11779,22 +11779,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="G45" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="H45" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="I45" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="J45" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K45" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L45" t="n">
         <v>1.28</v>
@@ -11803,206 +11803,206 @@
         <v>1.04</v>
       </c>
       <c r="N45" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O45" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P45" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R45" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S45" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T45" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U45" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V45" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="W45" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="X45" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Y45" t="n">
         <v>14.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AA45" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AB45" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AE45" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG45" t="n">
         <v>22</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>18.5</v>
       </c>
       <c r="AH45" t="n">
         <v>18.5</v>
       </c>
       <c r="AI45" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ45" t="n">
-        <v>80</v>
+        <v>900</v>
       </c>
       <c r="AK45" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL45" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM45" t="n">
         <v>75</v>
       </c>
       <c r="AN45" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AO45" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AP45" t="n">
         <v>16</v>
       </c>
       <c r="AQ45" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AR45" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS45" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AT45" t="n">
         <v>14</v>
       </c>
       <c r="AU45" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV45" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AW45" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX45" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AY45" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ45" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.1</v>
+        <v>19</v>
       </c>
       <c r="BB45" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC45" t="n">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF45" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BH45" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BI45" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BJ45" t="n">
         <v>9</v>
       </c>
       <c r="BK45" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BL45" t="n">
         <v>1000</v>
       </c>
       <c r="BM45" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN45" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BO45" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BP45" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BQ45" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW45" t="n">
         <v>9.4</v>
       </c>
-      <c r="BR45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS45" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT45" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BU45" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV45" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BW45" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BX45" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY45" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA45" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -12042,13 +12042,13 @@
         <v>3.25</v>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J46" t="n">
         <v>3.55</v>
       </c>
       <c r="K46" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L46" t="n">
         <v>1.34</v>
@@ -12066,7 +12066,7 @@
         <v>2.06</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R46" t="n">
         <v>1.41</v>
@@ -12075,7 +12075,7 @@
         <v>3.2</v>
       </c>
       <c r="T46" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U46" t="n">
         <v>2.26</v>
@@ -12090,13 +12090,13 @@
         <v>17.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z46" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA46" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB46" t="n">
         <v>12</v>
@@ -12111,7 +12111,7 @@
         <v>42</v>
       </c>
       <c r="AF46" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG46" t="n">
         <v>12</v>
@@ -12120,7 +12120,7 @@
         <v>17.5</v>
       </c>
       <c r="AI46" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ46" t="n">
         <v>32</v>
@@ -12132,10 +12132,10 @@
         <v>38</v>
       </c>
       <c r="AM46" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN46" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO46" t="n">
         <v>34</v>
@@ -12150,7 +12150,7 @@
         <v>20</v>
       </c>
       <c r="AS46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT46" t="n">
         <v>10</v>
@@ -12162,7 +12162,7 @@
         <v>12</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.6</v>
+        <v>16</v>
       </c>
       <c r="AX46" t="n">
         <v>13</v>
@@ -12174,25 +12174,25 @@
         <v>14</v>
       </c>
       <c r="BA46" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB46" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC46" t="n">
         <v>19.5</v>
       </c>
       <c r="BD46" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BE46" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF46" t="n">
         <v>14.5</v>
       </c>
       <c r="BG46" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH46" t="n">
         <v>1000</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -12287,7 +12287,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
         <v>4.2</v>
@@ -12296,7 +12296,7 @@
         <v>2.06</v>
       </c>
       <c r="I47" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J47" t="n">
         <v>3.55</v>
@@ -12329,7 +12329,7 @@
         <v>3.65</v>
       </c>
       <c r="T47" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U47" t="n">
         <v>2.1</v>
@@ -12374,19 +12374,19 @@
         <v>18.5</v>
       </c>
       <c r="AI47" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AJ47" t="n">
         <v>900</v>
       </c>
       <c r="AK47" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="AL47" t="n">
         <v>500</v>
       </c>
       <c r="AM47" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN47" t="n">
         <v>500</v>
@@ -12431,7 +12431,7 @@
         <v>24</v>
       </c>
       <c r="BB47" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BC47" t="n">
         <v>27</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="G48" t="n">
         <v>3</v>
@@ -12586,7 +12586,7 @@
         <v>2.02</v>
       </c>
       <c r="U48" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V48" t="n">
         <v>1.4</v>
@@ -12595,49 +12595,49 @@
         <v>1.5</v>
       </c>
       <c r="X48" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y48" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z48" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AA48" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB48" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD48" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE48" t="n">
         <v>60</v>
       </c>
       <c r="AF48" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG48" t="n">
         <v>14</v>
       </c>
       <c r="AH48" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI48" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AJ48" t="n">
         <v>60</v>
       </c>
       <c r="AK48" t="n">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="AL48" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AM48" t="n">
         <v>500</v>
@@ -12646,61 +12646,61 @@
         <v>60</v>
       </c>
       <c r="AO48" t="n">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="AP48" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="AR48" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="AS48" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT48" t="n">
         <v>4.4</v>
       </c>
-      <c r="AT48" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AU48" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AV48" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AW48" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AX48" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AY48" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ48" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BB48" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BC48" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF48" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BG48" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH48" t="n">
         <v>2.8</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="G49" t="n">
         <v>1.94</v>
@@ -12810,10 +12810,10 @@
         <v>3.6</v>
       </c>
       <c r="K49" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L49" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M49" t="n">
         <v>1.07</v>
@@ -12843,7 +12843,7 @@
         <v>2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W49" t="n">
         <v>2.06</v>
@@ -12861,7 +12861,7 @@
         <v>900</v>
       </c>
       <c r="AB49" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AC49" t="n">
         <v>8.800000000000001</v>
@@ -12885,7 +12885,7 @@
         <v>500</v>
       </c>
       <c r="AJ49" t="n">
-        <v>22</v>
+        <v>900</v>
       </c>
       <c r="AK49" t="n">
         <v>25</v>
@@ -12909,10 +12909,10 @@
         <v>11.5</v>
       </c>
       <c r="AR49" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AS49" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT49" t="n">
         <v>7.2</v>
@@ -12924,7 +12924,7 @@
         <v>16</v>
       </c>
       <c r="AW49" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AX49" t="n">
         <v>8.800000000000001</v>
@@ -12936,7 +12936,7 @@
         <v>17.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BB49" t="n">
         <v>16.5</v>
@@ -12945,16 +12945,16 @@
         <v>18.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE49" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF49" t="n">
         <v>12</v>
       </c>
       <c r="BG49" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BH49" t="n">
         <v>3.25</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v>1.41</v>
       </c>
       <c r="G50" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H50" t="n">
         <v>2.44</v>
@@ -13061,7 +13061,7 @@
         <v>1000</v>
       </c>
       <c r="J50" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K50" t="n">
         <v>1000</v>
@@ -13073,7 +13073,7 @@
         <v>1.03</v>
       </c>
       <c r="N50" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="O50" t="n">
         <v>1.19</v>
@@ -13100,7 +13100,7 @@
         <v>1.17</v>
       </c>
       <c r="W50" t="n">
-        <v>1.06</v>
+        <v>1.71</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -13115,7 +13115,7 @@
         <v>1000</v>
       </c>
       <c r="AB50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC50" t="n">
         <v>1000</v>
@@ -13127,10 +13127,10 @@
         <v>1000</v>
       </c>
       <c r="AF50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG50" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AH50" t="n">
         <v>1000</v>
@@ -13142,16 +13142,16 @@
         <v>900</v>
       </c>
       <c r="AK50" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM50" t="n">
         <v>1000</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -13303,16 +13303,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.27</v>
+        <v>2.2</v>
       </c>
       <c r="G51" t="n">
         <v>1000</v>
       </c>
       <c r="H51" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="I51" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="J51" t="n">
         <v>2.2</v>
@@ -13342,7 +13342,7 @@
         <v>1.18</v>
       </c>
       <c r="S51" t="n">
-        <v>1.89</v>
+        <v>1.27</v>
       </c>
       <c r="T51" t="n">
         <v>1.11</v>
@@ -13351,64 +13351,64 @@
         <v>1.11</v>
       </c>
       <c r="V51" t="n">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="W51" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA51" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO51" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP51" t="n">
         <v>1.03</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -13569,7 +13569,7 @@
         <v>3.3</v>
       </c>
       <c r="J52" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="K52" t="n">
         <v>4.5</v>
@@ -13587,10 +13587,10 @@
         <v>1.33</v>
       </c>
       <c r="P52" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
         <v>1.26</v>
@@ -13608,115 +13608,115 @@
         <v>1.44</v>
       </c>
       <c r="W52" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA52" t="n">
         <v>900</v>
       </c>
       <c r="AB52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC52" t="n">
         <v>9.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF52" t="n">
         <v>21</v>
       </c>
       <c r="AG52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH52" t="n">
         <v>22</v>
       </c>
       <c r="AI52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ52" t="n">
         <v>900</v>
       </c>
       <c r="AK52" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AL52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN52" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO52" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.33</v>
+        <v>8.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.33</v>
+        <v>7.8</v>
       </c>
       <c r="AU52" t="n">
         <v>5.7</v>
       </c>
       <c r="AV52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BC52" t="n">
         <v>1.33</v>
       </c>
-      <c r="AW52" t="n">
+      <c r="BD52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG52" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>1.29</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
         <v>1000</v>
       </c>
       <c r="J53" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="K53" t="n">
         <v>1000</v>
@@ -13832,25 +13832,25 @@
         <v>1.01</v>
       </c>
       <c r="M53" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N53" t="n">
         <v>1.25</v>
       </c>
       <c r="O53" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="P53" t="n">
         <v>1.24</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="R53" t="n">
         <v>1.12</v>
       </c>
       <c r="S53" t="n">
-        <v>1.39</v>
+        <v>1.05</v>
       </c>
       <c r="T53" t="n">
         <v>1.11</v>
@@ -13862,61 +13862,61 @@
         <v>1.3</v>
       </c>
       <c r="W53" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="X53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA53" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO53" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP53" t="n">
         <v>1.03</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -14319,22 +14319,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G55" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H55" t="n">
         <v>4.5</v>
       </c>
       <c r="I55" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J55" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K55" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L55" t="n">
         <v>1.51</v>
@@ -14343,10 +14343,10 @@
         <v>1.11</v>
       </c>
       <c r="N55" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="O55" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P55" t="n">
         <v>1.49</v>
@@ -14358,7 +14358,7 @@
         <v>1.17</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="T55" t="n">
         <v>2.2</v>
@@ -14370,25 +14370,25 @@
         <v>1.22</v>
       </c>
       <c r="W55" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X55" t="n">
         <v>9.6</v>
       </c>
       <c r="Y55" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z55" t="n">
         <v>500</v>
       </c>
       <c r="AA55" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB55" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AC55" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD55" t="n">
         <v>500</v>
@@ -14397,10 +14397,10 @@
         <v>500</v>
       </c>
       <c r="AF55" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG55" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH55" t="n">
         <v>500</v>
@@ -14409,7 +14409,7 @@
         <v>500</v>
       </c>
       <c r="AJ55" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK55" t="n">
         <v>500</v>
@@ -14430,13 +14430,13 @@
         <v>6.4</v>
       </c>
       <c r="AQ55" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AR55" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AT55" t="n">
         <v>5.1</v>
@@ -14445,10 +14445,10 @@
         <v>5.8</v>
       </c>
       <c r="AV55" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW55" t="n">
         <v>4.2</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>4.9</v>
       </c>
       <c r="AX55" t="n">
         <v>8.6</v>
@@ -14457,34 +14457,34 @@
         <v>9</v>
       </c>
       <c r="AZ55" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BA55" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB55" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BC55" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE55" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BF55" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BG55" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BH55" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="BJ55" t="n">
         <v>1000</v>
@@ -14514,7 +14514,7 @@
         <v>1000</v>
       </c>
       <c r="BS55" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BT55" t="n">
         <v>1000</v>
@@ -14538,11 +14538,11 @@
         <v>1000</v>
       </c>
       <c r="CA55" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="G56" t="n">
         <v>1000</v>
       </c>
       <c r="H56" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="I56" t="n">
         <v>1000</v>
@@ -14624,61 +14624,61 @@
         <v>1.23</v>
       </c>
       <c r="W56" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO56" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP56" t="n">
         <v>1.03</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -15081,7 +15081,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G58" t="n">
         <v>1.75</v>
@@ -15090,7 +15090,7 @@
         <v>7</v>
       </c>
       <c r="I58" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J58" t="n">
         <v>3.4</v>
@@ -15111,7 +15111,7 @@
         <v>1.52</v>
       </c>
       <c r="P58" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q58" t="n">
         <v>2.58</v>
@@ -15165,7 +15165,7 @@
         <v>13.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI58" t="n">
         <v>700</v>
@@ -15177,7 +15177,7 @@
         <v>26</v>
       </c>
       <c r="AL58" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM58" t="n">
         <v>700</v>
@@ -15243,22 +15243,22 @@
         <v>4.4</v>
       </c>
       <c r="BH58" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BI58" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ58" t="n">
         <v>14</v>
       </c>
       <c r="BK58" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL58" t="n">
         <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN58" t="n">
         <v>4</v>
@@ -15267,44 +15267,44 @@
         <v>3.05</v>
       </c>
       <c r="BP58" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ58" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR58" t="n">
         <v>42</v>
       </c>
       <c r="BS58" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT58" t="n">
         <v>11</v>
       </c>
       <c r="BU58" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV58" t="n">
         <v>1000</v>
       </c>
       <c r="BW58" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX58" t="n">
         <v>1000</v>
       </c>
       <c r="BY58" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ58" t="n">
         <v>38</v>
       </c>
       <c r="CA58" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
         <v>12.5</v>
       </c>
       <c r="BF59" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG59" t="n">
         <v>19.5</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G60" t="n">
         <v>4.2</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
         <v>2.78</v>
       </c>
       <c r="G61" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H61" t="n">
         <v>2.26</v>
@@ -15873,7 +15873,7 @@
         <v>1.66</v>
       </c>
       <c r="P61" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Q61" t="n">
         <v>2.78</v>
@@ -15894,61 +15894,61 @@
         <v>1.44</v>
       </c>
       <c r="W61" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO61" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP61" t="n">
         <v>1.03</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
         <v>4.8</v>
       </c>
       <c r="L63" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M63" t="n">
         <v>1.01</v>
@@ -16405,58 +16405,58 @@
         <v>1.31</v>
       </c>
       <c r="X63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA63" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO63" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP63" t="n">
         <v>1.03</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -16620,7 +16620,7 @@
         <v>2.68</v>
       </c>
       <c r="K64" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L64" t="n">
         <v>1.57</v>
@@ -16662,13 +16662,13 @@
         <v>90</v>
       </c>
       <c r="Y64" t="n">
-        <v>500</v>
+        <v>9.6</v>
       </c>
       <c r="Z64" t="n">
         <v>500</v>
       </c>
       <c r="AA64" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB64" t="n">
         <v>500</v>
@@ -16695,7 +16695,7 @@
         <v>500</v>
       </c>
       <c r="AJ64" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK64" t="n">
         <v>500</v>
@@ -16770,7 +16770,7 @@
         <v>2.54</v>
       </c>
       <c r="BI64" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ64" t="n">
         <v>1000</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -16973,7 +16973,7 @@
         <v>5.6</v>
       </c>
       <c r="AR65" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AS65" t="n">
         <v>4.5</v>
@@ -16994,7 +16994,7 @@
         <v>4.1</v>
       </c>
       <c r="AY65" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AZ65" t="n">
         <v>19.5</v>
@@ -17018,7 +17018,7 @@
         <v>4.7</v>
       </c>
       <c r="BG65" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH65" t="n">
         <v>2.58</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -17134,7 +17134,7 @@
         <v>1.54</v>
       </c>
       <c r="M66" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N66" t="n">
         <v>2.38</v>
@@ -17143,7 +17143,7 @@
         <v>1.59</v>
       </c>
       <c r="P66" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q66" t="n">
         <v>2.8</v>
@@ -17161,7 +17161,7 @@
         <v>1.68</v>
       </c>
       <c r="V66" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W66" t="n">
         <v>1.64</v>
@@ -17176,7 +17176,7 @@
         <v>32</v>
       </c>
       <c r="AA66" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB66" t="n">
         <v>8</v>
@@ -17278,7 +17278,7 @@
         <v>2.64</v>
       </c>
       <c r="BI66" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="BJ66" t="n">
         <v>12.5</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -17875,16 +17875,16 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G69" t="n">
         <v>1.91</v>
       </c>
       <c r="H69" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I69" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J69" t="n">
         <v>3.05</v>
@@ -17899,10 +17899,10 @@
         <v>1.13</v>
       </c>
       <c r="N69" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="O69" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P69" t="n">
         <v>1.43</v>
@@ -17923,7 +17923,7 @@
         <v>1.54</v>
       </c>
       <c r="V69" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W69" t="n">
         <v>2.08</v>
@@ -17932,13 +17932,13 @@
         <v>9.4</v>
       </c>
       <c r="Y69" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z69" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA69" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB69" t="n">
         <v>5.8</v>
@@ -17947,7 +17947,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD69" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE69" t="n">
         <v>700</v>
@@ -17959,7 +17959,7 @@
         <v>12.5</v>
       </c>
       <c r="AH69" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI69" t="n">
         <v>700</v>
@@ -17989,10 +17989,10 @@
         <v>10.5</v>
       </c>
       <c r="AR69" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS69" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT69" t="n">
         <v>4.2</v>
@@ -18004,10 +18004,10 @@
         <v>21</v>
       </c>
       <c r="AW69" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX69" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY69" t="n">
         <v>8.6</v>
@@ -18016,7 +18016,7 @@
         <v>20</v>
       </c>
       <c r="BA69" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB69" t="n">
         <v>14.5</v>
@@ -18025,16 +18025,16 @@
         <v>20</v>
       </c>
       <c r="BD69" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE69" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF69" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG69" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH69" t="n">
         <v>2.7</v>
@@ -18058,7 +18058,7 @@
         <v>4.3</v>
       </c>
       <c r="BO69" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="BP69" t="n">
         <v>15.5</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -18141,7 +18141,7 @@
         <v>12.5</v>
       </c>
       <c r="J70" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="K70" t="n">
         <v>6.8</v>
@@ -18153,28 +18153,28 @@
         <v>1.03</v>
       </c>
       <c r="N70" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O70" t="n">
         <v>1.17</v>
       </c>
       <c r="P70" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="Q70" t="n">
         <v>1.51</v>
       </c>
       <c r="R70" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="S70" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="T70" t="n">
         <v>1.91</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V70" t="n">
         <v>1.09</v>
@@ -18207,7 +18207,7 @@
         <v>180</v>
       </c>
       <c r="AF70" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG70" t="n">
         <v>11</v>
@@ -18225,28 +18225,28 @@
         <v>13.5</v>
       </c>
       <c r="AL70" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM70" t="n">
         <v>150</v>
       </c>
       <c r="AN70" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AO70" t="n">
         <v>200</v>
       </c>
       <c r="AP70" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AQ70" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AR70" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS70" t="n">
         <v>13</v>
-      </c>
-      <c r="AS70" t="n">
-        <v>14</v>
       </c>
       <c r="AT70" t="n">
         <v>10</v>
@@ -18258,19 +18258,19 @@
         <v>23</v>
       </c>
       <c r="AW70" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX70" t="n">
         <v>8.4</v>
       </c>
       <c r="AY70" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ70" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB70" t="n">
         <v>9.6</v>
@@ -18282,13 +18282,13 @@
         <v>28</v>
       </c>
       <c r="BE70" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BF70" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG70" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH70" t="n">
         <v>4.8</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -18392,7 +18392,7 @@
         <v>2.52</v>
       </c>
       <c r="I71" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J71" t="n">
         <v>2.78</v>
@@ -18410,7 +18410,7 @@
         <v>2.28</v>
       </c>
       <c r="O71" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P71" t="n">
         <v>1.41</v>
@@ -18548,65 +18548,65 @@
         <v>1000</v>
       </c>
       <c r="BI71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ71" t="n">
         <v>1000</v>
       </c>
       <c r="BK71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL71" t="n">
         <v>1000</v>
       </c>
       <c r="BM71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN71" t="n">
         <v>1000</v>
       </c>
       <c r="BO71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP71" t="n">
         <v>1000</v>
       </c>
       <c r="BQ71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR71" t="n">
         <v>1000</v>
       </c>
       <c r="BS71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT71" t="n">
         <v>1000</v>
       </c>
       <c r="BU71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV71" t="n">
         <v>1000</v>
       </c>
       <c r="BW71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX71" t="n">
         <v>1000</v>
       </c>
       <c r="BY71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ71" t="n">
         <v>1000</v>
       </c>
       <c r="CA71" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G72" t="n">
         <v>2.12</v>
@@ -18646,7 +18646,7 @@
         <v>4.2</v>
       </c>
       <c r="I72" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>3.3</v>
@@ -18685,7 +18685,7 @@
         <v>1.99</v>
       </c>
       <c r="V72" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W72" t="n">
         <v>1.89</v>
@@ -18715,10 +18715,10 @@
         <v>85</v>
       </c>
       <c r="AF72" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG72" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH72" t="n">
         <v>20</v>
@@ -18751,10 +18751,10 @@
         <v>12.5</v>
       </c>
       <c r="AR72" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS72" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT72" t="n">
         <v>7.2</v>
@@ -18766,7 +18766,7 @@
         <v>15.5</v>
       </c>
       <c r="AW72" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX72" t="n">
         <v>10.5</v>
@@ -18778,37 +18778,37 @@
         <v>17.5</v>
       </c>
       <c r="BA72" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB72" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC72" t="n">
         <v>20</v>
       </c>
       <c r="BD72" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BE72" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF72" t="n">
         <v>13</v>
       </c>
       <c r="BG72" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH72" t="n">
         <v>3.2</v>
       </c>
       <c r="BI72" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ72" t="n">
         <v>10.5</v>
       </c>
       <c r="BK72" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL72" t="n">
         <v>1000</v>
@@ -18841,7 +18841,7 @@
         <v>5.7</v>
       </c>
       <c r="BV72" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW72" t="n">
         <v>10.5</v>
@@ -18856,11 +18856,11 @@
         <v>30</v>
       </c>
       <c r="CA72" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
         <v>1.56</v>
       </c>
       <c r="S73" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T73" t="n">
         <v>1.59</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>
@@ -19160,7 +19160,7 @@
         <v>3.7</v>
       </c>
       <c r="K74" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L74" t="n">
         <v>1.32</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-06-12 19:13:36</t>
+          <t>2026-06-12 21:32:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G2" t="n">
         <v>2.14</v>
@@ -866,10 +866,10 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>3.65</v>
@@ -881,31 +881,31 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.38</v>
       </c>
       <c r="P2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T2" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
         <v>1.87</v>
@@ -917,7 +917,7 @@
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA2" t="n">
         <v>500</v>
@@ -941,7 +941,7 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI2" t="n">
         <v>370</v>
@@ -965,7 +965,7 @@
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>10</v>
@@ -974,40 +974,40 @@
         <v>10.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY2" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE2" t="n">
         <v>9</v>
@@ -1019,68 +1019,68 @@
         <v>8.6</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
         <v>1.1</v>
@@ -1144,7 +1144,7 @@
         <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
         <v>1.21</v>
@@ -1162,7 +1162,7 @@
         <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X3" t="n">
         <v>10.5</v>
@@ -1276,7 +1276,7 @@
         <v>2.96</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
         <v>13.5</v>
@@ -1294,7 +1294,7 @@
         <v>4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BP3" t="n">
         <v>12.5</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G4" t="n">
         <v>5.2</v>
@@ -1374,16 +1374,16 @@
         <v>1.93</v>
       </c>
       <c r="I4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
@@ -1398,7 +1398,7 @@
         <v>1.57</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
         <v>1.21</v>
@@ -1413,7 +1413,7 @@
         <v>1.76</v>
       </c>
       <c r="V4" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W4" t="n">
         <v>1.24</v>
@@ -1497,13 +1497,13 @@
         <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY4" t="n">
         <v>6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BA4" t="n">
         <v>6.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J5" t="n">
         <v>4.1</v>
@@ -1637,34 +1637,34 @@
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
         <v>5.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P5" t="n">
         <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
         <v>2.44</v>
       </c>
       <c r="T5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V5" t="n">
         <v>1.41</v>
@@ -1676,7 +1676,7 @@
         <v>32</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Z5" t="n">
         <v>34</v>
@@ -1694,19 +1694,19 @@
         <v>18</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
         <v>22</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
         <v>17.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
         <v>36</v>
@@ -1739,7 +1739,7 @@
         <v>23</v>
       </c>
       <c r="AT5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
         <v>9.199999999999999</v>
@@ -1754,7 +1754,7 @@
         <v>15.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
         <v>12.5</v>
@@ -1763,86 +1763,86 @@
         <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
         <v>14.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="BJ5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
         <v>9</v>
       </c>
-      <c r="BK5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BT5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -1906,13 +1906,13 @@
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.54</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1942,7 +1942,7 @@
         <v>150</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
         <v>95</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O7" t="n">
         <v>1.59</v>
@@ -2160,10 +2160,10 @@
         <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
         <v>1.05</v>
@@ -2184,7 +2184,7 @@
         <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="Z7" t="n">
         <v>970</v>
@@ -2235,7 +2235,7 @@
         <v>600</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>3.6</v>
@@ -2244,13 +2244,13 @@
         <v>4.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>4.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AV7" t="n">
         <v>4.5</v>
@@ -2259,13 +2259,13 @@
         <v>4.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AY7" t="n">
         <v>4.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BA7" t="n">
         <v>4.6</v>
@@ -2280,13 +2280,13 @@
         <v>4.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF7" t="n">
         <v>4.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH7" t="n">
         <v>2.62</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G8" t="n">
         <v>2.1</v>
@@ -2393,10 +2393,10 @@
         <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.5</v>
@@ -2471,7 +2471,7 @@
         <v>450</v>
       </c>
       <c r="AJ8" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
         <v>29</v>
@@ -2510,7 +2510,7 @@
         <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX8" t="n">
         <v>9.199999999999999</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
         <v>120</v>
       </c>
       <c r="AH9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI9" t="n">
         <v>50</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="H10" t="n">
         <v>6.2</v>
       </c>
       <c r="I10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.27</v>
@@ -2913,19 +2913,19 @@
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
         <v>2.7</v>
@@ -2934,19 +2934,19 @@
         <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
         <v>1.15</v>
       </c>
       <c r="W10" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="Z10" t="n">
         <v>160</v>
@@ -2958,7 +2958,7 @@
         <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
         <v>75</v>
@@ -2967,7 +2967,7 @@
         <v>240</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG10" t="n">
         <v>10.5</v>
@@ -2997,16 +2997,16 @@
         <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
@@ -3018,7 +3018,7 @@
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
         <v>7.4</v>
@@ -3030,7 +3030,7 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
         <v>12</v>
@@ -3042,13 +3042,13 @@
         <v>16</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
         <v>6.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="n">
         <v>4.2</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
         <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>4.4</v>
@@ -3176,7 +3176,7 @@
         <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
         <v>1.65</v>
@@ -3191,7 +3191,7 @@
         <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
         <v>2.42</v>
@@ -3233,7 +3233,7 @@
         <v>150</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
         <v>18.5</v>
@@ -3245,31 +3245,31 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
         <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
         <v>7.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="AT11" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AU11" t="n">
         <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW11" t="n">
         <v>7.2</v>
@@ -3281,7 +3281,7 @@
         <v>7.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BA11" t="n">
         <v>7.2</v>
@@ -3293,7 +3293,7 @@
         <v>11</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
         <v>7.4</v>
@@ -3302,7 +3302,7 @@
         <v>5.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="n">
         <v>4.9</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -3693,10 +3693,10 @@
         <v>4.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
@@ -3759,31 +3759,31 @@
         <v>600</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AT13" t="n">
         <v>6.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AY13" t="n">
         <v>9.4</v>
@@ -3792,25 +3792,25 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="BE13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="BH13" t="n">
         <v>2.9</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -3929,28 +3929,28 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q14" t="n">
         <v>1.46</v>
       </c>
       <c r="R14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S14" t="n">
         <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U14" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V14" t="n">
         <v>1.46</v>
@@ -3959,7 +3959,7 @@
         <v>1.69</v>
       </c>
       <c r="X14" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Y14" t="n">
         <v>22</v>
@@ -3974,7 +3974,7 @@
         <v>19</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
         <v>17</v>
@@ -3989,7 +3989,7 @@
         <v>17.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>500</v>
@@ -4001,7 +4001,7 @@
         <v>55</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
@@ -4019,10 +4019,10 @@
         <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT14" t="n">
         <v>9</v>
@@ -4034,7 +4034,7 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AX14" t="n">
         <v>14</v>
@@ -4049,22 +4049,22 @@
         <v>14.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>15.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD14" t="n">
         <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF14" t="n">
         <v>4.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>12.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH14" t="n">
         <v>4.8</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -4165,10 +4165,10 @@
         <v>1.86</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J15" t="n">
         <v>3.4</v>
@@ -4231,7 +4231,7 @@
         <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AE15" t="n">
         <v>700</v>
@@ -4252,7 +4252,7 @@
         <v>110</v>
       </c>
       <c r="AK15" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
         <v>500</v>
@@ -4270,13 +4270,13 @@
         <v>4.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT15" t="n">
         <v>4.4</v>
@@ -4288,22 +4288,22 @@
         <v>4.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
         <v>5.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC15" t="n">
         <v>4.2</v>
@@ -4330,59 +4330,59 @@
         <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BN15" t="n">
         <v>4.3</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
         <v>4.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR16" t="n">
         <v>5.7</v>
@@ -4548,7 +4548,7 @@
         <v>4.9</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AZ16" t="n">
         <v>5.7</v>
@@ -4584,49 +4584,49 @@
         <v>12</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BN16" t="n">
         <v>5.3</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP16" t="n">
         <v>22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BR16" t="n">
         <v>46</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BT16" t="n">
         <v>7</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BV16" t="n">
         <v>38</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BX16" t="n">
         <v>60</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BZ16" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
         <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
         <v>19.5</v>
@@ -4751,22 +4751,22 @@
         <v>970</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AI17" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
         <v>900</v>
       </c>
       <c r="AK17" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AL17" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN17" t="n">
         <v>600</v>
@@ -4820,7 +4820,7 @@
         <v>5.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="BF17" t="n">
         <v>3.85</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
         <v>2.68</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S18" t="n">
         <v>5.5</v>
@@ -5011,10 +5011,10 @@
         <v>500</v>
       </c>
       <c r="AJ18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK18" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AL18" t="n">
         <v>500</v>
@@ -5023,7 +5023,7 @@
         <v>500</v>
       </c>
       <c r="AN18" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO18" t="n">
         <v>600</v>
@@ -5047,10 +5047,10 @@
         <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
@@ -5065,13 +5065,13 @@
         <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
         <v>8.199999999999999</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H19" t="n">
         <v>3.35</v>
@@ -5190,7 +5190,7 @@
         <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L19" t="n">
         <v>1.48</v>
@@ -5205,7 +5205,7 @@
         <v>1.42</v>
       </c>
       <c r="P19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
         <v>2.24</v>
@@ -5220,7 +5220,7 @@
         <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="V19" t="n">
         <v>1.35</v>
@@ -5247,7 +5247,7 @@
         <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
         <v>55</v>
@@ -5256,7 +5256,7 @@
         <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
@@ -5292,7 +5292,7 @@
         <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
         <v>7.2</v>
@@ -5304,7 +5304,7 @@
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
@@ -5316,25 +5316,25 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD19" t="n">
         <v>40</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="BH19" t="n">
         <v>3.1</v>
@@ -5346,13 +5346,13 @@
         <v>11</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN19" t="n">
         <v>5.3</v>
@@ -5364,13 +5364,13 @@
         <v>19.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR19" t="n">
         <v>38</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT19" t="n">
         <v>7</v>
@@ -5382,23 +5382,23 @@
         <v>34</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BX19" t="n">
         <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BZ19" t="n">
         <v>38</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -5429,22 +5429,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="G20" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>1.64</v>
       </c>
       <c r="I20" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J20" t="n">
         <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.48</v>
@@ -5453,13 +5453,13 @@
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" t="n">
         <v>2.32</v>
@@ -5474,28 +5474,28 @@
         <v>2.18</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V20" t="n">
         <v>2.2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC20" t="n">
         <v>14</v>
@@ -5513,7 +5513,7 @@
         <v>500</v>
       </c>
       <c r="AH20" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
@@ -5534,58 +5534,58 @@
         <v>700</v>
       </c>
       <c r="AO20" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AP20" t="n">
         <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AR20" t="n">
         <v>4.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX20" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AY20" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.36</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.44</v>
+        <v>4.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.46</v>
+        <v>4.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG20" t="n">
         <v>5.3</v>
@@ -5600,59 +5600,59 @@
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BT20" t="n">
         <v>4.2</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>3.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -5716,13 +5716,13 @@
         <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
         <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
         <v>1.86</v>
@@ -5779,7 +5779,7 @@
         <v>160</v>
       </c>
       <c r="AL21" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM21" t="n">
         <v>580</v>
@@ -5794,22 +5794,22 @@
         <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AR21" t="n">
         <v>11</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AT21" t="n">
         <v>11</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW21" t="n">
         <v>17.5</v>
@@ -5824,7 +5824,7 @@
         <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB21" t="n">
         <v>6</v>
@@ -5836,7 +5836,7 @@
         <v>5.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF21" t="n">
         <v>5.9</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
         <v>1.35</v>
@@ -5970,10 +5970,10 @@
         <v>1.92</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
         <v>3.7</v>
@@ -6033,7 +6033,7 @@
         <v>21</v>
       </c>
       <c r="AL22" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
@@ -6048,16 +6048,16 @@
         <v>12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
         <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU22" t="n">
         <v>7.8</v>
@@ -6066,7 +6066,7 @@
         <v>17.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>9</v>
@@ -6078,7 +6078,7 @@
         <v>12</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB22" t="n">
         <v>15</v>
@@ -6090,13 +6090,13 @@
         <v>18</v>
       </c>
       <c r="BE22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF22" t="n">
         <v>10.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="n">
         <v>3.4</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -6215,16 +6215,16 @@
         <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
         <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
         <v>1.46</v>
@@ -6263,10 +6263,10 @@
         <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF23" t="n">
         <v>12.5</v>
@@ -6308,7 +6308,7 @@
         <v>14.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT23" t="n">
         <v>9.199999999999999</v>
@@ -6320,7 +6320,7 @@
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
@@ -6332,7 +6332,7 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB23" t="n">
         <v>17.5</v>
@@ -6344,19 +6344,19 @@
         <v>16</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF23" t="n">
         <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH23" t="n">
         <v>3.9</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BJ23" t="n">
         <v>9.800000000000001</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
         <v>3.35</v>
       </c>
       <c r="H24" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I24" t="n">
         <v>2.5</v>
@@ -6463,31 +6463,31 @@
         <v>3.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U24" t="n">
         <v>1.98</v>
@@ -6496,13 +6496,13 @@
         <v>1.66</v>
       </c>
       <c r="W24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
         <v>13.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z24" t="n">
         <v>16.5</v>
@@ -6511,13 +6511,13 @@
         <v>40</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC24" t="n">
         <v>7.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>500</v>
@@ -6529,7 +6529,7 @@
         <v>14.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AI24" t="n">
         <v>290</v>
@@ -6538,31 +6538,31 @@
         <v>60</v>
       </c>
       <c r="AK24" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AL24" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="AM24" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN24" t="n">
         <v>600</v>
       </c>
       <c r="AO24" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP24" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AT24" t="n">
         <v>10</v>
@@ -6574,25 +6574,25 @@
         <v>9.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AX24" t="n">
         <v>18</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
         <v>38</v>
       </c>
       <c r="BB24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD24" t="n">
         <v>42</v>
@@ -6601,10 +6601,10 @@
         <v>29</v>
       </c>
       <c r="BF24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG24" t="n">
         <v>20</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>7.6</v>
       </c>
       <c r="BH24" t="n">
         <v>3.35</v>
@@ -6616,13 +6616,13 @@
         <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="BN24" t="n">
         <v>1000</v>
@@ -6634,16 +6634,16 @@
         <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="BT24" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
         <v>4.2</v>
@@ -6652,13 +6652,13 @@
         <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="BZ24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
         <v>2.28</v>
       </c>
       <c r="W25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
         <v>44</v>
@@ -6807,13 +6807,13 @@
         <v>6</v>
       </c>
       <c r="AP25" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AQ25" t="n">
         <v>15.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
         <v>17</v>
@@ -6822,40 +6822,40 @@
         <v>16</v>
       </c>
       <c r="AU25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV25" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX25" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BB25" t="n">
         <v>5.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD25" t="n">
         <v>16</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BG25" t="n">
         <v>4.6</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H26" t="n">
         <v>2.12</v>
@@ -6977,13 +6977,13 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
         <v>1.18</v>
       </c>
       <c r="P26" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q26" t="n">
         <v>1.56</v>
@@ -7004,7 +7004,7 @@
         <v>1.74</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X26" t="n">
         <v>48</v>
@@ -7019,7 +7019,7 @@
         <v>65</v>
       </c>
       <c r="AB26" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AC26" t="n">
         <v>10.5</v>
@@ -7070,7 +7070,7 @@
         <v>14.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AT26" t="n">
         <v>15.5</v>
@@ -7085,7 +7085,7 @@
         <v>17.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY26" t="n">
         <v>12</v>
@@ -7094,19 +7094,19 @@
         <v>12.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BB26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD26" t="n">
         <v>7.2</v>
       </c>
-      <c r="BC26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE26" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF26" t="n">
         <v>17</v>
@@ -7124,13 +7124,13 @@
         <v>9</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BN26" t="n">
         <v>7.2</v>
@@ -7142,13 +7142,13 @@
         <v>23</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BT26" t="n">
         <v>5.8</v>
@@ -7160,23 +7160,23 @@
         <v>15.5</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX26" t="n">
         <v>24</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ26" t="n">
         <v>16.5</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -7207,230 +7207,230 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="G27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H27" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K27" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="O27" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="P27" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q27" t="n">
         <v>2.74</v>
       </c>
       <c r="R27" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S27" t="n">
-        <v>3.35</v>
+        <v>5.7</v>
       </c>
       <c r="T27" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U27" t="n">
-        <v>1.11</v>
+        <v>1.69</v>
       </c>
       <c r="V27" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W27" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="Z27" t="n">
-        <v>95</v>
+        <v>970</v>
       </c>
       <c r="AA27" t="n">
         <v>900</v>
       </c>
       <c r="AB27" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AC27" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="AD27" t="n">
         <v>160</v>
       </c>
       <c r="AE27" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AF27" t="n">
-        <v>95</v>
+        <v>970</v>
       </c>
       <c r="AG27" t="n">
         <v>160</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI27" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
         <v>900</v>
       </c>
       <c r="AK27" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AL27" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.55</v>
+        <v>3.7</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.55</v>
+        <v>3.7</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G28" t="n">
         <v>1.64</v>
@@ -7479,7 +7479,7 @@
         <v>5.3</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M28" t="n">
         <v>1.03</v>
@@ -7491,7 +7491,7 @@
         <v>1.18</v>
       </c>
       <c r="P28" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
         <v>1.53</v>
@@ -7500,10 +7500,10 @@
         <v>1.61</v>
       </c>
       <c r="S28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T28" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U28" t="n">
         <v>2.22</v>
@@ -7533,7 +7533,7 @@
         <v>20</v>
       </c>
       <c r="AD28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE28" t="n">
         <v>200</v>
@@ -7560,7 +7560,7 @@
         <v>500</v>
       </c>
       <c r="AM28" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
         <v>6.4</v>
@@ -7569,13 +7569,13 @@
         <v>110</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS28" t="n">
         <v>4.2</v>
@@ -7587,25 +7587,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX28" t="n">
         <v>6.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AZ28" t="n">
         <v>10.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB28" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BC28" t="n">
         <v>8.4</v>
@@ -7614,7 +7614,7 @@
         <v>14.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF28" t="n">
         <v>5.3</v>
@@ -7623,10 +7623,10 @@
         <v>7</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ28" t="n">
         <v>1000</v>
@@ -7641,10 +7641,10 @@
         <v>1.01</v>
       </c>
       <c r="BN28" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
@@ -7659,7 +7659,7 @@
         <v>1.01</v>
       </c>
       <c r="BT28" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU28" t="n">
         <v>1.01</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -7715,22 +7715,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G29" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="H29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="L29" t="n">
         <v>1.33</v>
@@ -7739,7 +7739,7 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O29" t="n">
         <v>1.3</v>
@@ -7748,10 +7748,10 @@
         <v>1.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
         <v>3.05</v>
@@ -7766,7 +7766,7 @@
         <v>1.07</v>
       </c>
       <c r="W29" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="X29" t="n">
         <v>970</v>
@@ -7781,7 +7781,7 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AC29" t="n">
         <v>42</v>
@@ -7793,7 +7793,7 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
         <v>970</v>
@@ -7805,10 +7805,10 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL29" t="n">
         <v>500</v>
@@ -7826,7 +7826,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AR29" t="n">
         <v>4.2</v>
@@ -7841,7 +7841,7 @@
         <v>6.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AW29" t="n">
         <v>4.2</v>
@@ -7850,10 +7850,10 @@
         <v>5.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BA29" t="n">
         <v>4.2</v>
@@ -7862,22 +7862,22 @@
         <v>7.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="BF29" t="n">
         <v>5.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BI29" t="n">
         <v>2.78</v>
@@ -7886,7 +7886,7 @@
         <v>1000</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
@@ -7895,7 +7895,7 @@
         <v>1.04</v>
       </c>
       <c r="BN29" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BO29" t="n">
         <v>2.78</v>
@@ -7910,35 +7910,35 @@
         <v>1000</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BT29" t="n">
         <v>1000</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="BV29" t="n">
         <v>1000</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BX29" t="n">
         <v>1000</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BZ29" t="n">
         <v>1000</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.13</v>
+        <v>6.8</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
         <v>7.2</v>
       </c>
       <c r="K30" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L30" t="n">
         <v>1.23</v>
@@ -7999,16 +7999,16 @@
         <v>1.15</v>
       </c>
       <c r="P30" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R30" t="n">
         <v>1.71</v>
       </c>
       <c r="S30" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T30" t="n">
         <v>2.1</v>
@@ -8023,7 +8023,7 @@
         <v>1.05</v>
       </c>
       <c r="X30" t="n">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="Y30" t="n">
         <v>11.5</v>
@@ -8050,7 +8050,7 @@
         <v>200</v>
       </c>
       <c r="AG30" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="AH30" t="n">
         <v>44</v>
@@ -8074,61 +8074,61 @@
         <v>430</v>
       </c>
       <c r="AO30" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="AP30" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ30" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR30" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AV30" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW30" t="n">
         <v>10.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY30" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB30" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD30" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE30" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BF30" t="n">
         <v>15</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BH30" t="n">
         <v>4.9</v>
@@ -8170,13 +8170,13 @@
         <v>3.9</v>
       </c>
       <c r="BU30" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BV30" t="n">
         <v>6.8</v>
       </c>
       <c r="BW30" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BX30" t="n">
         <v>24</v>
@@ -8188,11 +8188,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CA30" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -8223,28 +8223,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="G31" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H31" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I31" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N31" t="n">
         <v>4.4</v>
@@ -8253,61 +8253,61 @@
         <v>1.23</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S31" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="T31" t="n">
         <v>1.65</v>
       </c>
       <c r="U31" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="V31" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W31" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y31" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="Z31" t="n">
         <v>170</v>
       </c>
       <c r="AA31" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB31" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="AC31" t="n">
-        <v>42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>200</v>
       </c>
       <c r="AF31" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AG31" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AI31" t="n">
         <v>260</v>
@@ -8319,134 +8319,134 @@
         <v>250</v>
       </c>
       <c r="AL31" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AM31" t="n">
         <v>580</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.25</v>
+        <v>10.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.22</v>
+        <v>10.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.23</v>
+        <v>6.4</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.24</v>
+        <v>14.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.23</v>
+        <v>6.2</v>
       </c>
       <c r="AU31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK31" t="n">
         <v>5.1</v>
       </c>
-      <c r="AV31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BL31" t="n">
         <v>1000</v>
       </c>
       <c r="BM31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN31" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO31" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BP31" t="n">
         <v>1000</v>
       </c>
       <c r="BQ31" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BR31" t="n">
         <v>1000</v>
       </c>
       <c r="BS31" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT31" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU31" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV31" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW31" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BX31" t="n">
         <v>1000</v>
       </c>
       <c r="BY31" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ31" t="n">
         <v>1000</v>
       </c>
       <c r="CA31" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -8477,10 +8477,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="G32" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H32" t="n">
         <v>3.9</v>
@@ -8489,13 +8489,13 @@
         <v>4.6</v>
       </c>
       <c r="J32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
         <v>4.5</v>
       </c>
       <c r="L32" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M32" t="n">
         <v>1.04</v>
@@ -8510,7 +8510,7 @@
         <v>2.34</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R32" t="n">
         <v>1.53</v>
@@ -8537,13 +8537,13 @@
         <v>22</v>
       </c>
       <c r="Z32" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AA32" t="n">
         <v>900</v>
       </c>
       <c r="AB32" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC32" t="n">
         <v>11</v>
@@ -8573,7 +8573,7 @@
         <v>18.5</v>
       </c>
       <c r="AL32" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AM32" t="n">
         <v>320</v>
@@ -8594,7 +8594,7 @@
         <v>16</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT32" t="n">
         <v>9.800000000000001</v>
@@ -8606,7 +8606,7 @@
         <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX32" t="n">
         <v>11.5</v>
@@ -8618,10 +8618,10 @@
         <v>12</v>
       </c>
       <c r="BA32" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB32" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC32" t="n">
         <v>15</v>
@@ -8630,19 +8630,19 @@
         <v>21</v>
       </c>
       <c r="BE32" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF32" t="n">
         <v>7</v>
       </c>
       <c r="BG32" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BH32" t="n">
         <v>4.4</v>
       </c>
       <c r="BI32" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ32" t="n">
         <v>9.4</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -8731,16 +8731,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G33" t="n">
         <v>2.06</v>
       </c>
       <c r="H33" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J33" t="n">
         <v>3.8</v>
@@ -8833,7 +8833,7 @@
         <v>500</v>
       </c>
       <c r="AN33" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO33" t="n">
         <v>40</v>
@@ -8848,7 +8848,7 @@
         <v>13</v>
       </c>
       <c r="AS33" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT33" t="n">
         <v>10</v>
@@ -8860,7 +8860,7 @@
         <v>14</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX33" t="n">
         <v>12</v>
@@ -8872,7 +8872,7 @@
         <v>13.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB33" t="n">
         <v>17</v>
@@ -8884,13 +8884,13 @@
         <v>21</v>
       </c>
       <c r="BE33" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF33" t="n">
         <v>8.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH33" t="n">
         <v>4.3</v>
@@ -8932,10 +8932,10 @@
         <v>8</v>
       </c>
       <c r="BU33" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BV33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW33" t="n">
         <v>7.4</v>
@@ -8944,17 +8944,17 @@
         <v>1000</v>
       </c>
       <c r="BY33" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ33" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="CA33" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -8985,49 +8985,49 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="G34" t="n">
         <v>4.5</v>
       </c>
       <c r="H34" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="I34" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J34" t="n">
         <v>4.1</v>
       </c>
       <c r="K34" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M34" t="n">
         <v>1.04</v>
       </c>
       <c r="N34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O34" t="n">
         <v>1.23</v>
       </c>
       <c r="P34" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R34" t="n">
         <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T34" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U34" t="n">
         <v>2.26</v>
@@ -9108,13 +9108,13 @@
         <v>6.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AV34" t="n">
         <v>5.1</v>
       </c>
       <c r="AW34" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX34" t="n">
         <v>7.8</v>
@@ -9132,7 +9132,7 @@
         <v>9</v>
       </c>
       <c r="BC34" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="BD34" t="n">
         <v>8.4</v>
@@ -9144,13 +9144,13 @@
         <v>5</v>
       </c>
       <c r="BG34" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BH34" t="n">
         <v>4.1</v>
       </c>
       <c r="BI34" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ34" t="n">
         <v>9.4</v>
@@ -9198,7 +9198,7 @@
         <v>1000</v>
       </c>
       <c r="BY34" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ34" t="n">
         <v>1000</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H35" t="n">
         <v>6</v>
@@ -9257,7 +9257,7 @@
         <v>5.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M35" t="n">
         <v>1.04</v>
@@ -9338,7 +9338,7 @@
         <v>36</v>
       </c>
       <c r="AM35" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="AN35" t="n">
         <v>8.4</v>
@@ -9401,68 +9401,68 @@
         <v>4.9</v>
       </c>
       <c r="BH35" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI35" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK35" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL35" t="n">
         <v>1000</v>
       </c>
       <c r="BM35" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN35" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BP35" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ35" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR35" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS35" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT35" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU35" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV35" t="n">
         <v>1000</v>
       </c>
       <c r="BW35" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX35" t="n">
         <v>1000</v>
       </c>
       <c r="BY35" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
         <v>4.3</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M36" t="n">
         <v>1.03</v>
@@ -9538,10 +9538,10 @@
         <v>1.53</v>
       </c>
       <c r="U36" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V36" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W36" t="n">
         <v>1.62</v>
@@ -9601,7 +9601,7 @@
         <v>19</v>
       </c>
       <c r="AP36" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AQ36" t="n">
         <v>14</v>
@@ -9655,68 +9655,68 @@
         <v>14</v>
       </c>
       <c r="BH36" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI36" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BJ36" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK36" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL36" t="n">
         <v>1000</v>
       </c>
       <c r="BM36" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN36" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO36" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP36" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ36" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR36" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS36" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT36" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU36" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV36" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW36" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX36" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY36" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ36" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA36" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
         <v>3.3</v>
       </c>
       <c r="H37" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I37" t="n">
         <v>2.36</v>
@@ -9762,7 +9762,7 @@
         <v>3.85</v>
       </c>
       <c r="K37" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L37" t="n">
         <v>1.21</v>
@@ -9780,7 +9780,7 @@
         <v>2.74</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R37" t="n">
         <v>1.7</v>
@@ -9801,7 +9801,7 @@
         <v>1.44</v>
       </c>
       <c r="X37" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y37" t="n">
         <v>970</v>
@@ -9816,7 +9816,7 @@
         <v>500</v>
       </c>
       <c r="AC37" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD37" t="n">
         <v>14.5</v>
@@ -9849,7 +9849,7 @@
         <v>580</v>
       </c>
       <c r="AN37" t="n">
-        <v>48</v>
+        <v>970</v>
       </c>
       <c r="AO37" t="n">
         <v>36</v>
@@ -9867,7 +9867,7 @@
         <v>20</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AU37" t="n">
         <v>8</v>
@@ -9879,7 +9879,7 @@
         <v>14.5</v>
       </c>
       <c r="AX37" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="AY37" t="n">
         <v>10</v>
@@ -9891,16 +9891,16 @@
         <v>17.5</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BD37" t="n">
         <v>14.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF37" t="n">
         <v>12</v>
@@ -9912,7 +9912,7 @@
         <v>5</v>
       </c>
       <c r="BI37" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BJ37" t="n">
         <v>8.800000000000001</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -10001,67 +10001,67 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H38" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="I38" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J38" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
         <v>4.3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M38" t="n">
         <v>1.05</v>
       </c>
       <c r="N38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W38" t="n">
         <v>1.25</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V38" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.23</v>
       </c>
       <c r="X38" t="n">
         <v>19</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z38" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AA38" t="n">
         <v>19.5</v>
@@ -10070,7 +10070,7 @@
         <v>20</v>
       </c>
       <c r="AC38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD38" t="n">
         <v>10.5</v>
@@ -10085,7 +10085,7 @@
         <v>19</v>
       </c>
       <c r="AH38" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI38" t="n">
         <v>46</v>
@@ -10097,7 +10097,7 @@
         <v>320</v>
       </c>
       <c r="AL38" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="AM38" t="n">
         <v>320</v>
@@ -10106,46 +10106,46 @@
         <v>120</v>
       </c>
       <c r="AO38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ38" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AP38" t="n">
+      <c r="AR38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW38" t="n">
         <v>15</v>
       </c>
-      <c r="AQ38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT38" t="n">
+      <c r="AX38" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY38" t="n">
         <v>16.5</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>17</v>
       </c>
       <c r="AZ38" t="n">
         <v>15.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB38" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BC38" t="n">
         <v>42</v>
@@ -10154,77 +10154,77 @@
         <v>42</v>
       </c>
       <c r="BE38" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>29</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>38</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>11</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV38" t="n">
         <v>12</v>
       </c>
-      <c r="BF38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV38" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW38" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX38" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY38" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ38" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA38" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G39" t="n">
         <v>3.8</v>
@@ -10273,7 +10273,7 @@
         <v>3.55</v>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M39" t="n">
         <v>1.08</v>
@@ -10282,7 +10282,7 @@
         <v>3.45</v>
       </c>
       <c r="O39" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P39" t="n">
         <v>1.84</v>
@@ -10294,7 +10294,7 @@
         <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T39" t="n">
         <v>1.87</v>
@@ -10309,7 +10309,7 @@
         <v>1.36</v>
       </c>
       <c r="X39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y39" t="n">
         <v>9.199999999999999</v>
@@ -10342,22 +10342,22 @@
         <v>18</v>
       </c>
       <c r="AI39" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AJ39" t="n">
         <v>500</v>
       </c>
       <c r="AK39" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AL39" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AM39" t="n">
         <v>580</v>
       </c>
       <c r="AN39" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AO39" t="n">
         <v>21</v>
@@ -10372,7 +10372,7 @@
         <v>12</v>
       </c>
       <c r="AS39" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT39" t="n">
         <v>11</v>
@@ -10387,7 +10387,7 @@
         <v>21</v>
       </c>
       <c r="AX39" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY39" t="n">
         <v>13.5</v>
@@ -10396,16 +10396,16 @@
         <v>16</v>
       </c>
       <c r="BA39" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB39" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BC39" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BD39" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="BE39" t="n">
         <v>20</v>
@@ -10414,71 +10414,71 @@
         <v>28</v>
       </c>
       <c r="BG39" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH39" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="BI39" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ39" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK39" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BL39" t="n">
         <v>1000</v>
       </c>
       <c r="BM39" t="n">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BN39" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO39" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP39" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BR39" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS39" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BT39" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU39" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV39" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW39" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX39" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY39" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ39" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -10509,16 +10509,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G40" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H40" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="I40" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>4.2</v>
@@ -10527,19 +10527,19 @@
         <v>4.4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M40" t="n">
         <v>1.03</v>
       </c>
       <c r="N40" t="n">
-        <v>1.11</v>
+        <v>4.7</v>
       </c>
       <c r="O40" t="n">
         <v>1.2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q40" t="n">
         <v>1.58</v>
@@ -10551,16 +10551,16 @@
         <v>2.44</v>
       </c>
       <c r="T40" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="U40" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W40" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="X40" t="n">
         <v>29</v>
@@ -10572,7 +10572,7 @@
         <v>30</v>
       </c>
       <c r="AA40" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB40" t="n">
         <v>14</v>
@@ -10590,7 +10590,7 @@
         <v>16.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH40" t="n">
         <v>16.5</v>
@@ -10617,7 +10617,7 @@
         <v>27</v>
       </c>
       <c r="AP40" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ40" t="n">
         <v>17</v>
@@ -10626,10 +10626,10 @@
         <v>24</v>
       </c>
       <c r="AS40" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT40" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU40" t="n">
         <v>5.1</v>
@@ -10638,16 +10638,16 @@
         <v>6.2</v>
       </c>
       <c r="AW40" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX40" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY40" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA40" t="n">
         <v>8.199999999999999</v>
@@ -10668,13 +10668,13 @@
         <v>5.4</v>
       </c>
       <c r="BG40" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH40" t="n">
         <v>4.4</v>
       </c>
       <c r="BI40" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="BJ40" t="n">
         <v>9.199999999999999</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -10763,43 +10763,43 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G41" t="n">
         <v>1.89</v>
       </c>
-      <c r="G41" t="n">
-        <v>1.93</v>
-      </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I41" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J41" t="n">
         <v>3.3</v>
       </c>
       <c r="K41" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L41" t="n">
         <v>1.53</v>
       </c>
       <c r="M41" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N41" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="P41" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="R41" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S41" t="n">
         <v>5.7</v>
@@ -10808,16 +10808,16 @@
         <v>2.28</v>
       </c>
       <c r="U41" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V41" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W41" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X41" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y41" t="n">
         <v>970</v>
@@ -10862,131 +10862,131 @@
         <v>500</v>
       </c>
       <c r="AM41" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN41" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO41" t="n">
         <v>700</v>
       </c>
       <c r="AP41" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="AR41" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AT41" t="n">
         <v>4.7</v>
       </c>
       <c r="AU41" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="AX41" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AY41" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ41" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB41" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA41" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK41" t="n">
         <v>6.6</v>
       </c>
-      <c r="BD41" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BI41" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK41" t="n">
-        <v>6</v>
-      </c>
       <c r="BL41" t="n">
         <v>1000</v>
       </c>
       <c r="BM41" t="n">
-        <v>1.33</v>
+        <v>2.86</v>
       </c>
       <c r="BN41" t="n">
         <v>4.4</v>
       </c>
       <c r="BO41" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BP41" t="n">
         <v>1000</v>
       </c>
       <c r="BQ41" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR41" t="n">
         <v>1000</v>
       </c>
       <c r="BS41" t="n">
-        <v>1.84</v>
+        <v>2.72</v>
       </c>
       <c r="BT41" t="n">
         <v>1000</v>
       </c>
       <c r="BU41" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV41" t="n">
         <v>1000</v>
       </c>
       <c r="BW41" t="n">
-        <v>1.31</v>
+        <v>2.88</v>
       </c>
       <c r="BX41" t="n">
         <v>1000</v>
       </c>
       <c r="BY41" t="n">
-        <v>1.32</v>
+        <v>2.88</v>
       </c>
       <c r="BZ41" t="n">
         <v>1000</v>
       </c>
       <c r="CA41" t="n">
-        <v>1.85</v>
+        <v>2.72</v>
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
         <v>6.2</v>
       </c>
       <c r="G42" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="H42" t="n">
         <v>1.46</v>
@@ -11029,7 +11029,7 @@
         <v>1.54</v>
       </c>
       <c r="J42" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K42" t="n">
         <v>5.6</v>
@@ -11068,7 +11068,7 @@
         <v>2.84</v>
       </c>
       <c r="W42" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X42" t="n">
         <v>80</v>
@@ -11101,10 +11101,10 @@
         <v>60</v>
       </c>
       <c r="AH42" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AI42" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ42" t="n">
         <v>210</v>
@@ -11125,7 +11125,7 @@
         <v>6.4</v>
       </c>
       <c r="AP42" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ42" t="n">
         <v>9.199999999999999</v>
@@ -11149,7 +11149,7 @@
         <v>7.6</v>
       </c>
       <c r="AX42" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AY42" t="n">
         <v>16.5</v>
@@ -11161,16 +11161,16 @@
         <v>14.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC42" t="n">
         <v>6</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF42" t="n">
         <v>10.5</v>
@@ -11182,7 +11182,7 @@
         <v>4.7</v>
       </c>
       <c r="BI42" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BJ42" t="n">
         <v>1000</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -11271,166 +11271,166 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="G43" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="H43" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="I43" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="J43" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="K43" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N43" t="n">
-        <v>1.33</v>
+        <v>2.88</v>
       </c>
       <c r="O43" t="n">
         <v>1.36</v>
       </c>
       <c r="P43" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="R43" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S43" t="n">
-        <v>1.05</v>
+        <v>3.35</v>
       </c>
       <c r="T43" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V43" t="n">
         <v>1.11</v>
       </c>
       <c r="W43" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AB43" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="AC43" t="n">
-        <v>95</v>
+        <v>10.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AF43" t="n">
-        <v>970</v>
+        <v>8.4</v>
       </c>
       <c r="AG43" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="AH43" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ43" t="n">
-        <v>900</v>
+        <v>14</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN43" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU43" t="n">
         <v>5.8</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX43" t="n">
         <v>4.4</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF43" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH43" t="n">
         <v>1000</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="G44" t="n">
         <v>1.56</v>
@@ -11534,31 +11534,31 @@
         <v>6.8</v>
       </c>
       <c r="I44" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J44" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K44" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L44" t="n">
         <v>1.27</v>
       </c>
       <c r="M44" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N44" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O44" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P44" t="n">
         <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R44" t="n">
         <v>1.47</v>
@@ -11570,13 +11570,13 @@
         <v>1.85</v>
       </c>
       <c r="U44" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V44" t="n">
         <v>1.13</v>
       </c>
       <c r="W44" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X44" t="n">
         <v>25</v>
@@ -11603,7 +11603,7 @@
         <v>130</v>
       </c>
       <c r="AF44" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AG44" t="n">
         <v>12.5</v>
@@ -11633,7 +11633,7 @@
         <v>530</v>
       </c>
       <c r="AP44" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ44" t="n">
         <v>21</v>
@@ -11642,7 +11642,7 @@
         <v>21</v>
       </c>
       <c r="AS44" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT44" t="n">
         <v>8</v>
@@ -11654,7 +11654,7 @@
         <v>18</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX44" t="n">
         <v>8.199999999999999</v>
@@ -11666,7 +11666,7 @@
         <v>19</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB44" t="n">
         <v>11.5</v>
@@ -11678,13 +11678,13 @@
         <v>18</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF44" t="n">
         <v>6</v>
       </c>
       <c r="BG44" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH44" t="n">
         <v>4.1</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
         <v>4.7</v>
       </c>
       <c r="H45" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="I45" t="n">
         <v>1.86</v>
@@ -11803,10 +11803,10 @@
         <v>1.04</v>
       </c>
       <c r="N45" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O45" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P45" t="n">
         <v>2.48</v>
@@ -11824,7 +11824,7 @@
         <v>1.63</v>
       </c>
       <c r="U45" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V45" t="n">
         <v>2.16</v>
@@ -11962,7 +11962,7 @@
         <v>8</v>
       </c>
       <c r="BO45" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BP45" t="n">
         <v>32</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -12051,7 +12051,7 @@
         <v>3.7</v>
       </c>
       <c r="L46" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="M46" t="n">
         <v>1.06</v>
@@ -12078,7 +12078,7 @@
         <v>1.72</v>
       </c>
       <c r="U46" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V46" t="n">
         <v>1.41</v>
@@ -12102,7 +12102,7 @@
         <v>12</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD46" t="n">
         <v>16</v>
@@ -12186,7 +12186,7 @@
         <v>18</v>
       </c>
       <c r="BE46" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF46" t="n">
         <v>14.5</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
         <v>3.55</v>
       </c>
       <c r="K47" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L47" t="n">
         <v>1.15</v>
@@ -12365,7 +12365,7 @@
         <v>23</v>
       </c>
       <c r="AF47" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG47" t="n">
         <v>16.5</v>
@@ -12443,7 +12443,7 @@
         <v>13</v>
       </c>
       <c r="BF47" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BG47" t="n">
         <v>14</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -12541,37 +12541,37 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="H48" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I48" t="n">
         <v>3.45</v>
       </c>
       <c r="J48" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K48" t="n">
         <v>3.3</v>
       </c>
       <c r="L48" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M48" t="n">
         <v>1.12</v>
       </c>
       <c r="N48" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="O48" t="n">
         <v>1.51</v>
       </c>
       <c r="P48" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q48" t="n">
         <v>2.5</v>
@@ -12580,7 +12580,7 @@
         <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="T48" t="n">
         <v>2.02</v>
@@ -12592,7 +12592,7 @@
         <v>1.4</v>
       </c>
       <c r="W48" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X48" t="n">
         <v>9.199999999999999</v>
@@ -12625,7 +12625,7 @@
         <v>14</v>
       </c>
       <c r="AH48" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI48" t="n">
         <v>200</v>
@@ -12637,7 +12637,7 @@
         <v>140</v>
       </c>
       <c r="AL48" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM48" t="n">
         <v>500</v>
@@ -12646,125 +12646,125 @@
         <v>60</v>
       </c>
       <c r="AO48" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AP48" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ48" t="n">
         <v>5.6</v>
       </c>
       <c r="AR48" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AS48" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT48" t="n">
         <v>7</v>
       </c>
-      <c r="AT48" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AU48" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV48" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX48" t="n">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="AY48" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AZ48" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA48" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC48" t="n">
         <v>7</v>
       </c>
-      <c r="BB48" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD48" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE48" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF48" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF48" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG48" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH48" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI48" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ48" t="n">
         <v>11.5</v>
       </c>
       <c r="BK48" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL48" t="n">
         <v>1000</v>
       </c>
       <c r="BM48" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="BN48" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO48" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BP48" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ48" t="n">
-        <v>2.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR48" t="n">
         <v>1000</v>
       </c>
       <c r="BS48" t="n">
-        <v>2.12</v>
+        <v>8.6</v>
       </c>
       <c r="BT48" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU48" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BV48" t="n">
         <v>32</v>
       </c>
       <c r="BW48" t="n">
-        <v>2.08</v>
+        <v>7.8</v>
       </c>
       <c r="BX48" t="n">
         <v>1000</v>
       </c>
       <c r="BY48" t="n">
-        <v>2.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ48" t="n">
         <v>1000</v>
       </c>
       <c r="CA48" t="n">
-        <v>2.14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -12798,19 +12798,19 @@
         <v>1.92</v>
       </c>
       <c r="G49" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="H49" t="n">
         <v>4.5</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K49" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L49" t="n">
         <v>1.43</v>
@@ -12825,7 +12825,7 @@
         <v>1.35</v>
       </c>
       <c r="P49" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q49" t="n">
         <v>1.99</v>
@@ -12843,10 +12843,10 @@
         <v>2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W49" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X49" t="n">
         <v>15.5</v>
@@ -12870,7 +12870,7 @@
         <v>21</v>
       </c>
       <c r="AE49" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AF49" t="n">
         <v>13</v>
@@ -12885,16 +12885,16 @@
         <v>500</v>
       </c>
       <c r="AJ49" t="n">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AK49" t="n">
         <v>25</v>
       </c>
       <c r="AL49" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AM49" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN49" t="n">
         <v>17.5</v>
@@ -12909,13 +12909,13 @@
         <v>11.5</v>
       </c>
       <c r="AR49" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT49" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU49" t="n">
         <v>7.4</v>
@@ -12924,7 +12924,7 @@
         <v>16</v>
       </c>
       <c r="AW49" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX49" t="n">
         <v>8.800000000000001</v>
@@ -12936,7 +12936,7 @@
         <v>17.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB49" t="n">
         <v>16.5</v>
@@ -12945,16 +12945,16 @@
         <v>18.5</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF49" t="n">
         <v>12</v>
       </c>
       <c r="BG49" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH49" t="n">
         <v>3.25</v>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -13061,7 +13061,7 @@
         <v>1000</v>
       </c>
       <c r="J50" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="K50" t="n">
         <v>1000</v>
@@ -13103,40 +13103,40 @@
         <v>1.71</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y50" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA50" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AB50" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC50" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD50" t="n">
         <v>1000</v>
       </c>
       <c r="AE50" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF50" t="n">
         <v>500</v>
       </c>
       <c r="AG50" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH50" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AI50" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ50" t="n">
         <v>900</v>
@@ -13148,25 +13148,25 @@
         <v>500</v>
       </c>
       <c r="AM50" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN50" t="n">
         <v>500</v>
       </c>
       <c r="AO50" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT50" t="n">
         <v>1.03</v>
@@ -13178,7 +13178,7 @@
         <v>1.03</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX50" t="n">
         <v>1.03</v>
@@ -13187,28 +13187,28 @@
         <v>1.03</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF50" t="n">
-        <v>1.05</v>
+        <v>2.26</v>
       </c>
       <c r="BG50" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
         <v>1.5</v>
       </c>
       <c r="I51" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="J51" t="n">
         <v>2.2</v>
@@ -13330,19 +13330,19 @@
         <v>1.31</v>
       </c>
       <c r="O51" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P51" t="n">
         <v>1.31</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="R51" t="n">
         <v>1.18</v>
       </c>
       <c r="S51" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T51" t="n">
         <v>1.11</v>
@@ -13351,7 +13351,7 @@
         <v>1.11</v>
       </c>
       <c r="V51" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W51" t="n">
         <v>1.22</v>
@@ -13360,7 +13360,7 @@
         <v>500</v>
       </c>
       <c r="Y51" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z51" t="n">
         <v>500</v>
@@ -13372,10 +13372,10 @@
         <v>500</v>
       </c>
       <c r="AC51" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AD51" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE51" t="n">
         <v>500</v>
@@ -13423,7 +13423,7 @@
         <v>1.03</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU51" t="n">
         <v>1.03</v>
@@ -13435,10 +13435,10 @@
         <v>1.03</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ51" t="n">
         <v>1.03</v>
@@ -13447,19 +13447,19 @@
         <v>1.03</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BG51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
         <v>1.33</v>
       </c>
       <c r="P52" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q52" t="n">
         <v>2</v>
@@ -13632,7 +13632,7 @@
         <v>500</v>
       </c>
       <c r="AE52" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF52" t="n">
         <v>21</v>
@@ -13650,13 +13650,13 @@
         <v>900</v>
       </c>
       <c r="AK52" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AL52" t="n">
         <v>500</v>
       </c>
       <c r="AM52" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN52" t="n">
         <v>500</v>
@@ -13665,16 +13665,16 @@
         <v>500</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.37</v>
+        <v>2.26</v>
       </c>
       <c r="AQ52" t="n">
         <v>8.4</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.37</v>
+        <v>2.44</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.37</v>
+        <v>2.54</v>
       </c>
       <c r="AT52" t="n">
         <v>7.8</v>
@@ -13683,40 +13683,40 @@
         <v>5.7</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.37</v>
+        <v>2.26</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.37</v>
+        <v>2.42</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.29</v>
+        <v>2.28</v>
       </c>
       <c r="AY52" t="n">
         <v>9</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.37</v>
+        <v>2.54</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.37</v>
+        <v>2.52</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.33</v>
+        <v>14.5</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.37</v>
+        <v>2.52</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.37</v>
+        <v>2.54</v>
       </c>
       <c r="BF52" t="n">
         <v>18.5</v>
       </c>
       <c r="BG52" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="BH52" t="n">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -13811,13 +13811,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="G53" t="n">
         <v>1000</v>
       </c>
       <c r="H53" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="I53" t="n">
         <v>1000</v>
@@ -13826,7 +13826,7 @@
         <v>1.88</v>
       </c>
       <c r="K53" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -13835,16 +13835,16 @@
         <v>1.06</v>
       </c>
       <c r="N53" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P53" t="n">
         <v>1.25</v>
       </c>
-      <c r="O53" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q53" t="n">
-        <v>1.06</v>
+        <v>1.96</v>
       </c>
       <c r="R53" t="n">
         <v>1.12</v>
@@ -13919,10 +13919,10 @@
         <v>500</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR53" t="n">
         <v>1.03</v>
@@ -13931,10 +13931,10 @@
         <v>1.03</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV53" t="n">
         <v>1.03</v>
@@ -13967,10 +13967,10 @@
         <v>1.03</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH53" t="n">
         <v>1000</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -14092,13 +14092,13 @@
         <v>1.23</v>
       </c>
       <c r="O54" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P54" t="n">
         <v>1.23</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="R54" t="n">
         <v>1.12</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14385,7 @@
         <v>900</v>
       </c>
       <c r="AB55" t="n">
-        <v>27</v>
+        <v>6.8</v>
       </c>
       <c r="AC55" t="n">
         <v>970</v>
@@ -14430,13 +14430,13 @@
         <v>6.4</v>
       </c>
       <c r="AQ55" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR55" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS55" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="AT55" t="n">
         <v>5.1</v>
@@ -14445,10 +14445,10 @@
         <v>5.8</v>
       </c>
       <c r="AV55" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AW55" t="n">
-        <v>4.2</v>
+        <v>2.44</v>
       </c>
       <c r="AX55" t="n">
         <v>8.6</v>
@@ -14457,34 +14457,34 @@
         <v>9</v>
       </c>
       <c r="AZ55" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BA55" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD55" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB55" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD55" t="n">
+      <c r="BE55" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF55" t="n">
         <v>5.9</v>
       </c>
-      <c r="BE55" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG55" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH55" t="n">
         <v>3.65</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="BJ55" t="n">
         <v>1000</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -14660,7 +14660,7 @@
         <v>500</v>
       </c>
       <c r="AI56" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ56" t="n">
         <v>500</v>
@@ -14681,10 +14681,10 @@
         <v>500</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AR56" t="n">
         <v>1.03</v>
@@ -14693,10 +14693,10 @@
         <v>1.03</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV56" t="n">
         <v>1.03</v>
@@ -14729,10 +14729,10 @@
         <v>1.03</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BH56" t="n">
         <v>1000</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -15084,7 +15084,7 @@
         <v>1.62</v>
       </c>
       <c r="G58" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H58" t="n">
         <v>7</v>
@@ -15102,16 +15102,16 @@
         <v>1.54</v>
       </c>
       <c r="M58" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N58" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O58" t="n">
         <v>1.52</v>
       </c>
       <c r="P58" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q58" t="n">
         <v>2.58</v>
@@ -15123,10 +15123,10 @@
         <v>5.4</v>
       </c>
       <c r="T58" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U58" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V58" t="n">
         <v>1.13</v>
@@ -15135,82 +15135,82 @@
         <v>2.34</v>
       </c>
       <c r="X58" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y58" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z58" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA58" t="n">
         <v>700</v>
       </c>
       <c r="AB58" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AC58" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD58" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AE58" t="n">
         <v>700</v>
       </c>
       <c r="AF58" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG58" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AI58" t="n">
         <v>700</v>
       </c>
       <c r="AJ58" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK58" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL58" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM58" t="n">
         <v>700</v>
       </c>
       <c r="AN58" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO58" t="n">
         <v>700</v>
       </c>
       <c r="AP58" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ58" t="n">
         <v>12.5</v>
       </c>
       <c r="AR58" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS58" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT58" t="n">
         <v>4.3</v>
       </c>
       <c r="AU58" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV58" t="n">
         <v>15.5</v>
       </c>
       <c r="AW58" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX58" t="n">
         <v>6.2</v>
@@ -15219,10 +15219,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ58" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BA58" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB58" t="n">
         <v>12.5</v>
@@ -15231,22 +15231,22 @@
         <v>17.5</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE58" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF58" t="n">
         <v>12.5</v>
       </c>
       <c r="BG58" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH58" t="n">
         <v>2.84</v>
       </c>
       <c r="BI58" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ58" t="n">
         <v>14</v>
@@ -15258,7 +15258,7 @@
         <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN58" t="n">
         <v>4</v>
@@ -15267,7 +15267,7 @@
         <v>3.05</v>
       </c>
       <c r="BP58" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ58" t="n">
         <v>6</v>
@@ -15276,13 +15276,13 @@
         <v>42</v>
       </c>
       <c r="BS58" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT58" t="n">
         <v>11</v>
       </c>
       <c r="BU58" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV58" t="n">
         <v>1000</v>
@@ -15294,17 +15294,17 @@
         <v>1000</v>
       </c>
       <c r="BY58" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ58" t="n">
         <v>38</v>
       </c>
       <c r="CA58" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -15338,19 +15338,19 @@
         <v>2.76</v>
       </c>
       <c r="G59" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H59" t="n">
         <v>2.86</v>
       </c>
-      <c r="H59" t="n">
-        <v>2.82</v>
-      </c>
       <c r="I59" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J59" t="n">
         <v>3.35</v>
       </c>
       <c r="K59" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L59" t="n">
         <v>1.46</v>
@@ -15383,10 +15383,10 @@
         <v>2.12</v>
       </c>
       <c r="V59" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W59" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X59" t="n">
         <v>970</v>
@@ -15404,7 +15404,7 @@
         <v>10.5</v>
       </c>
       <c r="AC59" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AD59" t="n">
         <v>16</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -15843,94 +15843,94 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="G61" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="H61" t="n">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J61" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="K61" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
       </c>
       <c r="M61" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N61" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="O61" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="P61" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="R61" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S61" t="n">
-        <v>2.78</v>
+        <v>6.8</v>
       </c>
       <c r="T61" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="U61" t="n">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="V61" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W61" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="X61" t="n">
-        <v>500</v>
+        <v>7</v>
       </c>
       <c r="Y61" t="n">
-        <v>500</v>
+        <v>7.6</v>
       </c>
       <c r="Z61" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AA61" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AB61" t="n">
-        <v>500</v>
+        <v>8.6</v>
       </c>
       <c r="AC61" t="n">
-        <v>500</v>
+        <v>7.4</v>
       </c>
       <c r="AD61" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AE61" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AF61" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AG61" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AH61" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AI61" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ61" t="n">
         <v>500</v>
@@ -15951,34 +15951,34 @@
         <v>500</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AS61" t="n">
         <v>1.03</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU61" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV61" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW61" t="n">
         <v>1.03</v>
       </c>
       <c r="AX61" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY61" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AZ61" t="n">
         <v>1.03</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
         <v>1.24</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="R62" t="n">
         <v>1.12</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -16351,61 +16351,61 @@
         </is>
       </c>
       <c r="F63" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J63" t="n">
         <v>2.62</v>
       </c>
-      <c r="G63" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I63" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2.3</v>
-      </c>
       <c r="K63" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="L63" t="n">
         <v>1.55</v>
       </c>
       <c r="M63" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N63" t="n">
-        <v>1.1</v>
+        <v>2.16</v>
       </c>
       <c r="O63" t="n">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="P63" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S63" t="n">
-        <v>2.68</v>
+        <v>6.4</v>
       </c>
       <c r="T63" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="U63" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V63" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W63" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="X63" t="n">
-        <v>500</v>
+        <v>7.8</v>
       </c>
       <c r="Y63" t="n">
         <v>500</v>
@@ -16459,58 +16459,58 @@
         <v>500</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU63" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV63" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AX63" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AY63" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AZ63" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BA63" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC63" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD63" t="n">
-        <v>1.03</v>
+        <v>2.2</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BF63" t="n">
-        <v>1.08</v>
+        <v>2.2</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.08</v>
+        <v>3.1</v>
       </c>
       <c r="BH63" t="n">
         <v>1000</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -16623,7 +16623,7 @@
         <v>3.5</v>
       </c>
       <c r="L64" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="M64" t="n">
         <v>1.15</v>
@@ -16662,7 +16662,7 @@
         <v>90</v>
       </c>
       <c r="Y64" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z64" t="n">
         <v>500</v>
@@ -16716,55 +16716,55 @@
         <v>5.3</v>
       </c>
       <c r="AQ64" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AU64" t="n">
         <v>5.4</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY64" t="n">
         <v>10</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BF64" t="n">
-        <v>1.69</v>
+        <v>3.4</v>
       </c>
       <c r="BG64" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="BH64" t="n">
         <v>2.54</v>
@@ -16776,13 +16776,13 @@
         <v>1000</v>
       </c>
       <c r="BK64" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BL64" t="n">
         <v>1000</v>
       </c>
       <c r="BM64" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BN64" t="n">
         <v>1000</v>
@@ -16794,7 +16794,7 @@
         <v>1000</v>
       </c>
       <c r="BQ64" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BR64" t="n">
         <v>1000</v>
@@ -16818,17 +16818,17 @@
         <v>1000</v>
       </c>
       <c r="BY64" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BZ64" t="n">
         <v>1000</v>
       </c>
       <c r="CA64" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
         <v>8.4</v>
       </c>
       <c r="Y65" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z65" t="n">
         <v>18.5</v>
@@ -16931,7 +16931,7 @@
         <v>8.4</v>
       </c>
       <c r="AD65" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE65" t="n">
         <v>55</v>
@@ -16973,52 +16973,52 @@
         <v>5.6</v>
       </c>
       <c r="AR65" t="n">
-        <v>3.9</v>
+        <v>14</v>
       </c>
       <c r="AS65" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AU65" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AV65" t="n">
         <v>10.5</v>
       </c>
       <c r="AW65" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX65" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY65" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AY65" t="n">
-        <v>3.95</v>
       </c>
       <c r="AZ65" t="n">
         <v>19.5</v>
       </c>
       <c r="BA65" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB65" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC65" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD65" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE65" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF65" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG65" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BF65" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG65" t="n">
-        <v>4.6</v>
       </c>
       <c r="BH65" t="n">
         <v>2.58</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -17122,10 +17122,10 @@
         <v>3.65</v>
       </c>
       <c r="I66" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J66" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="K66" t="n">
         <v>3.25</v>
@@ -17161,7 +17161,7 @@
         <v>1.68</v>
       </c>
       <c r="V66" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W66" t="n">
         <v>1.64</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -17899,10 +17899,10 @@
         <v>1.13</v>
       </c>
       <c r="N69" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="O69" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P69" t="n">
         <v>1.43</v>
@@ -18040,7 +18040,7 @@
         <v>2.7</v>
       </c>
       <c r="BI69" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BJ69" t="n">
         <v>14.5</v>
@@ -18058,7 +18058,7 @@
         <v>4.3</v>
       </c>
       <c r="BO69" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BP69" t="n">
         <v>15.5</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -18135,7 +18135,7 @@
         <v>1.34</v>
       </c>
       <c r="H70" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I70" t="n">
         <v>12.5</v>
@@ -18153,22 +18153,22 @@
         <v>1.03</v>
       </c>
       <c r="N70" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O70" t="n">
         <v>1.17</v>
       </c>
       <c r="P70" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q70" t="n">
         <v>1.51</v>
       </c>
       <c r="R70" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S70" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T70" t="n">
         <v>1.91</v>
@@ -18183,7 +18183,7 @@
         <v>3.9</v>
       </c>
       <c r="X70" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y70" t="n">
         <v>950</v>
@@ -18198,16 +18198,16 @@
         <v>11.5</v>
       </c>
       <c r="AC70" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AD70" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AE70" t="n">
         <v>180</v>
       </c>
       <c r="AF70" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG70" t="n">
         <v>11</v>
@@ -18225,7 +18225,7 @@
         <v>13.5</v>
       </c>
       <c r="AL70" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM70" t="n">
         <v>150</v>
@@ -18246,7 +18246,7 @@
         <v>12</v>
       </c>
       <c r="AS70" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT70" t="n">
         <v>10</v>
@@ -18258,7 +18258,7 @@
         <v>23</v>
       </c>
       <c r="AW70" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX70" t="n">
         <v>8.4</v>
@@ -18270,7 +18270,7 @@
         <v>21</v>
       </c>
       <c r="BA70" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB70" t="n">
         <v>9.6</v>
@@ -18282,13 +18282,13 @@
         <v>28</v>
       </c>
       <c r="BE70" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF70" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG70" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH70" t="n">
         <v>4.8</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -18637,10 +18637,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G72" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H72" t="n">
         <v>4.2</v>
@@ -18649,10 +18649,10 @@
         <v>4.4</v>
       </c>
       <c r="J72" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K72" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L72" t="n">
         <v>1.01</v>
@@ -18688,7 +18688,7 @@
         <v>1.29</v>
       </c>
       <c r="W72" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X72" t="n">
         <v>12.5</v>
@@ -18715,7 +18715,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG72" t="n">
         <v>12.5</v>
@@ -18754,7 +18754,7 @@
         <v>8</v>
       </c>
       <c r="AS72" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT72" t="n">
         <v>7.2</v>
@@ -18766,7 +18766,7 @@
         <v>15.5</v>
       </c>
       <c r="AW72" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX72" t="n">
         <v>10.5</v>
@@ -18778,10 +18778,10 @@
         <v>17.5</v>
       </c>
       <c r="BA72" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB72" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC72" t="n">
         <v>20</v>
@@ -18790,13 +18790,13 @@
         <v>36</v>
       </c>
       <c r="BE72" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF72" t="n">
         <v>13</v>
       </c>
       <c r="BG72" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH72" t="n">
         <v>3.2</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -18891,22 +18891,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="G73" t="n">
         <v>2.04</v>
       </c>
       <c r="H73" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I73" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>3.8</v>
       </c>
       <c r="K73" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L73" t="n">
         <v>1.25</v>
@@ -18939,7 +18939,7 @@
         <v>2.4</v>
       </c>
       <c r="V73" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W73" t="n">
         <v>1.97</v>
@@ -19023,10 +19023,10 @@
         <v>1.03</v>
       </c>
       <c r="AX73" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY73" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ73" t="n">
         <v>11.5</v>
@@ -19047,7 +19047,7 @@
         <v>1.03</v>
       </c>
       <c r="BF73" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG73" t="n">
         <v>22</v>
@@ -19071,50 +19071,50 @@
         <v>55</v>
       </c>
       <c r="BN73" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO73" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP73" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ73" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR73" t="n">
         <v>23</v>
       </c>
       <c r="BS73" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BT73" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU73" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV73" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BW73" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BX73" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY73" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BZ73" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA73" t="n">
         <v>11.5</v>
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>
@@ -19154,13 +19154,13 @@
         <v>3.85</v>
       </c>
       <c r="I74" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J74" t="n">
         <v>3.7</v>
       </c>
       <c r="K74" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L74" t="n">
         <v>1.32</v>
@@ -19172,37 +19172,37 @@
         <v>4</v>
       </c>
       <c r="O74" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P74" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R74" t="n">
         <v>1.4</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T74" t="n">
         <v>1.73</v>
       </c>
       <c r="U74" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V74" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W74" t="n">
         <v>1.9</v>
       </c>
       <c r="X74" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y74" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z74" t="n">
         <v>36</v>
@@ -19214,7 +19214,7 @@
         <v>11.5</v>
       </c>
       <c r="AC74" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD74" t="n">
         <v>19</v>
@@ -19265,7 +19265,7 @@
         <v>1.03</v>
       </c>
       <c r="AT74" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU74" t="n">
         <v>7</v>
@@ -19280,7 +19280,7 @@
         <v>10</v>
       </c>
       <c r="AY74" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ74" t="n">
         <v>13.5</v>
@@ -19334,7 +19334,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ74" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR74" t="n">
         <v>27</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-06-12 21:32:00</t>
+          <t>2026-06-12 23:51:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="I3" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>5.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>10</v>
+        <v>1.71</v>
       </c>
       <c r="AK3" t="n">
-        <v>13</v>
+        <v>700</v>
       </c>
       <c r="AL3" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AM3" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.9</v>
+        <v>44</v>
       </c>
       <c r="AO3" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="AQ3" t="n">
-        <v>44</v>
+        <v>250</v>
       </c>
       <c r="AR3" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="AS3" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AT3" t="n">
-        <v>10.5</v>
+        <v>3.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>14</v>
+        <v>3.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>38</v>
+        <v>3.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>46</v>
+        <v>3.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>8.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>3.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>80</v>
+        <v>3.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>2.54</v>
       </c>
       <c r="BD3" t="n">
-        <v>29</v>
+        <v>2.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>46</v>
+        <v>2.52</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>48</v>
+        <v>3.15</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -1368,227 +1368,227 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="H4" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="I4" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.54</v>
       </c>
-      <c r="M4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.51</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="n">
         <v>60</v>
       </c>
       <c r="AL4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS4" t="n">
         <v>7</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AT4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>940</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU4" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -1625,13 +1625,13 @@
         <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
         <v>3.55</v>
@@ -1646,13 +1646,13 @@
         <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5" t="n">
         <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -1664,7 +1664,7 @@
         <v>1.95</v>
       </c>
       <c r="U5" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V5" t="n">
         <v>1.29</v>
@@ -1673,7 +1673,7 @@
         <v>1.92</v>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
         <v>13.5</v>
@@ -1682,7 +1682,7 @@
         <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB5" t="n">
         <v>8.199999999999999</v>
@@ -1691,7 +1691,7 @@
         <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
         <v>60</v>
@@ -1706,7 +1706,7 @@
         <v>20</v>
       </c>
       <c r="AI5" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
         <v>25</v>
@@ -1715,40 +1715,40 @@
         <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AP5" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR5" t="n">
         <v>27</v>
       </c>
       <c r="AS5" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AT5" t="n">
         <v>7.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV5" t="n">
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
@@ -1757,92 +1757,92 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
       </c>
       <c r="BD5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE5" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF5" t="n">
         <v>16.5</v>
       </c>
-      <c r="BF5" t="n">
-        <v>16</v>
-      </c>
       <c r="BG5" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BJ5" t="n">
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM5" t="n">
-        <v>16.5</v>
+        <v>120</v>
       </c>
       <c r="BN5" t="n">
         <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BR5" t="n">
         <v>32</v>
       </c>
       <c r="BS5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT5" t="n">
         <v>7.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BV5" t="n">
         <v>38</v>
       </c>
       <c r="BW5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX5" t="n">
         <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ5" t="n">
         <v>32</v>
       </c>
       <c r="CA5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>2.28</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
@@ -1906,7 +1906,7 @@
         <v>2.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
         <v>1.63</v>
@@ -1918,160 +1918,160 @@
         <v>1.56</v>
       </c>
       <c r="U6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
         <v>1.76</v>
       </c>
       <c r="X6" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL6" t="n">
         <v>29</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>32</v>
       </c>
       <c r="AM6" t="n">
         <v>65</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP6" t="n">
         <v>20</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>24</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.5</v>
+        <v>46</v>
       </c>
       <c r="AT6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>12.5</v>
       </c>
-      <c r="AU6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12</v>
-      </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.6</v>
+        <v>26</v>
       </c>
       <c r="BC6" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.5</v>
+        <v>46</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BH6" t="n">
         <v>4.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BN6" t="n">
         <v>5.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP6" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>24</v>
       </c>
       <c r="BS6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT6" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7</v>
       </c>
       <c r="BU6" t="n">
         <v>5.1</v>
@@ -2080,23 +2080,23 @@
         <v>23</v>
       </c>
       <c r="BW6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX6" t="n">
         <v>29</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6" t="n">
         <v>16.5</v>
       </c>
       <c r="CA6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>
@@ -2127,28 +2127,28 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="G7" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I7" t="n">
         <v>4.2</v>
       </c>
-      <c r="I7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="J7" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
         <v>4.3</v>
@@ -2157,52 +2157,52 @@
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R7" t="n">
         <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="X7" t="n">
         <v>19</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB7" t="n">
         <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
         <v>14</v>
@@ -2211,16 +2211,16 @@
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
         <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL7" t="n">
         <v>36</v>
@@ -2232,64 +2232,64 @@
         <v>13</v>
       </c>
       <c r="AO7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP7" t="n">
         <v>15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE7" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI7" t="n">
         <v>3.05</v>
@@ -2298,59 +2298,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN7" t="n">
         <v>4.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP7" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT7" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>8</v>
       </c>
       <c r="BU7" t="n">
         <v>6</v>
       </c>
       <c r="BV7" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-13 18:17:01</t>
+          <t>2026-06-13 20:32:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
@@ -1097,36 +1097,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Colo Colo</t>
+          <t>Nublense</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>65</v>
+        <v>1.38</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1183,10 +1183,10 @@
         <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AF3" t="n">
         <v>1000</v>
@@ -1195,82 +1195,82 @@
         <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.71</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN3" t="n">
-        <v>44</v>
+        <v>210</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP3" t="n">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="AR3" t="n">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="AS3" t="n">
-        <v>250</v>
+        <v>27</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.2</v>
+        <v>25</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.2</v>
+        <v>27</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.2</v>
+        <v>27</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.2</v>
+        <v>27</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.2</v>
+        <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.4</v>
+        <v>27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.54</v>
+        <v>27</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.5</v>
+        <v>22</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.52</v>
+        <v>95</v>
       </c>
       <c r="BF3" t="n">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.15</v>
+        <v>50</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>El Paso Locomotive FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Phoenix Rising FC</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.94</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.61</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.14</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.2</v>
-      </c>
       <c r="S4" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.54</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.42</v>
-      </c>
       <c r="X4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB4" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AC4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>50</v>
       </c>
-      <c r="AF4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>75</v>
-      </c>
       <c r="AK4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN4" t="n">
         <v>60</v>
       </c>
-      <c r="AL4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>75</v>
-      </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
         <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB4" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BC4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>160</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BN4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>320</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD4" t="n">
+      <c r="BT4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>400</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
         <v>6.4</v>
       </c>
-      <c r="BE4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF4" t="n">
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
         <v>6.4</v>
       </c>
-      <c r="BG4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>940</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>65</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>44</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>65</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>44</v>
-      </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,752 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nublense</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Orange County Blues</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="H5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>13</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4.2</v>
       </c>
-      <c r="I5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
+      <c r="BE5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4.1</v>
       </c>
-      <c r="T5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="BG5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>48</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>27</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR5" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="BS5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX5" t="n">
         <v>32</v>
       </c>
-      <c r="AA5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>150</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>120</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ5" t="n">
+      <c r="BY5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>9</v>
       </c>
-      <c r="BR5" t="n">
-        <v>32</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>32</v>
-      </c>
       <c r="CA5" t="n">
-        <v>12.5</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-13 20:32:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>El Paso Locomotive FC</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Phoenix Rising FC</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="X6" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>6</v>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>2026-06-13 20:32:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>US United Soccer League</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Orange County Blues</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X7" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-13 20:32:09</t>
+          <t>2026-06-13 22:47:11</t>
         </is>
       </c>
     </row>
